--- a/nurse_scheduler_template.xlsx
+++ b/nurse_scheduler_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2050D00-9B3C-40B6-8044-E56CBF5530D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DED0B17-88FF-40AA-8FD7-9860DA274524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B332721F-AB2B-4BF1-A12F-4722F279DAC4}"/>
   </bookViews>
@@ -176,7 +176,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-412]General"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -272,14 +272,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
@@ -305,28 +297,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -414,6 +384,26 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9C5700"/>
+      <name val="Dotum"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -821,20 +811,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,55 +851,48 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -925,89 +908,49 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="13" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1017,116 +960,73 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1141,10 +1041,195 @@
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1198,253 +1283,124 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="10" xfId="5" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="3" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="28" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="6" xfId="2" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1767,13 +1723,13 @@
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.44140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="3.6640625" style="29" customWidth="1"/>
+    <col min="4" max="5" width="3.6640625" style="26" customWidth="1"/>
     <col min="6" max="13" width="3.6640625" style="3" customWidth="1"/>
-    <col min="14" max="17" width="3.6640625" style="29" customWidth="1"/>
+    <col min="14" max="17" width="3.6640625" style="26" customWidth="1"/>
     <col min="18" max="18" width="3.6640625" style="3" customWidth="1"/>
-    <col min="19" max="32" width="3.6640625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="3.44140625" style="29" customWidth="1"/>
-    <col min="34" max="34" width="3.5546875" style="29" customWidth="1"/>
+    <col min="19" max="32" width="3.6640625" style="26" customWidth="1"/>
+    <col min="33" max="33" width="3.44140625" style="26" customWidth="1"/>
+    <col min="34" max="34" width="3.5546875" style="26" customWidth="1"/>
     <col min="35" max="35" width="3" style="3" customWidth="1"/>
     <col min="36" max="36" width="3" style="2" customWidth="1"/>
     <col min="37" max="37" width="4.5546875" style="2" customWidth="1"/>
@@ -1783,7 +1739,7 @@
     <col min="41" max="41" width="7.5546875" style="3" customWidth="1"/>
     <col min="42" max="42" width="6.88671875" style="3" customWidth="1"/>
     <col min="43" max="43" width="7.5546875" style="3" customWidth="1"/>
-    <col min="44" max="44" width="5.44140625" style="45" customWidth="1"/>
+    <col min="44" max="44" width="5.44140625" style="40" customWidth="1"/>
     <col min="45" max="765" width="7.5546875" style="3" customWidth="1"/>
     <col min="766" max="766" width="8.88671875" style="3" customWidth="1"/>
     <col min="767" max="767" width="8.88671875" customWidth="1"/>
@@ -1823,93 +1779,93 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
-      <c r="AI1" s="107"/>
-      <c r="AJ1" s="107"/>
-      <c r="AK1" s="107"/>
-      <c r="AL1" s="107"/>
-      <c r="AV1" s="70"/>
-      <c r="AW1" s="70"/>
+      <c r="AI1" s="75"/>
+      <c r="AJ1" s="75"/>
+      <c r="AK1" s="75"/>
+      <c r="AL1" s="75"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
     </row>
     <row r="2" spans="1:766" ht="49.5" customHeight="1">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="114"/>
-      <c r="AG2" s="114"/>
-      <c r="AH2" s="114"/>
-      <c r="AI2" s="114"/>
-      <c r="AJ2" s="114"/>
-      <c r="AK2" s="114"/>
-      <c r="AL2" s="114"/>
-      <c r="AM2" s="114"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="145"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="145"/>
+      <c r="W2" s="145"/>
+      <c r="X2" s="145"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="145"/>
+      <c r="AA2" s="145"/>
+      <c r="AB2" s="145"/>
+      <c r="AC2" s="145"/>
+      <c r="AD2" s="145"/>
+      <c r="AE2" s="145"/>
+      <c r="AF2" s="145"/>
+      <c r="AG2" s="145"/>
+      <c r="AH2" s="145"/>
+      <c r="AI2" s="145"/>
+      <c r="AJ2" s="145"/>
+      <c r="AK2" s="145"/>
+      <c r="AL2" s="145"/>
+      <c r="AM2" s="145"/>
     </row>
     <row r="3" spans="1:766" ht="6" customHeight="1" thickBot="1">
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="103"/>
-      <c r="U3" s="103"/>
-      <c r="V3" s="103"/>
-      <c r="W3" s="103"/>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="103"/>
-      <c r="Z3" s="103"/>
-      <c r="AA3" s="103"/>
-      <c r="AB3" s="103"/>
-      <c r="AC3" s="103"/>
-      <c r="AD3" s="103"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="103"/>
-      <c r="AG3" s="103"/>
-      <c r="AH3" s="103"/>
-      <c r="AI3" s="103"/>
-      <c r="AJ3" s="103"/>
-      <c r="AK3" s="103"/>
-      <c r="AL3" s="103"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="79"/>
+      <c r="Y3" s="79"/>
+      <c r="Z3" s="79"/>
+      <c r="AA3" s="79"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="79"/>
+      <c r="AD3" s="79"/>
+      <c r="AE3" s="79"/>
+      <c r="AF3" s="79"/>
+      <c r="AG3" s="79"/>
+      <c r="AH3" s="79"/>
+      <c r="AI3" s="79"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="79"/>
+      <c r="AL3" s="79"/>
     </row>
     <row r="4" spans="1:766" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="4"/>
@@ -1935,42 +1891,42 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
+      <c r="Z4" s="146"/>
+      <c r="AA4" s="146"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="108"/>
-      <c r="AE4" s="116" t="s">
+      <c r="AD4" s="76"/>
+      <c r="AE4" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="118" t="s">
+      <c r="AF4" s="148"/>
+      <c r="AG4" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="AH4" s="119"/>
-      <c r="AR4" s="45"/>
+      <c r="AH4" s="150"/>
+      <c r="AR4" s="40"/>
     </row>
     <row r="5" spans="1:766" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="122"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="153"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="123" t="s">
+      <c r="H5" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="125"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="156"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1978,16 +1934,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Z5" s="115"/>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115"/>
-      <c r="AC5" s="115"/>
-      <c r="AD5" s="104"/>
-      <c r="AE5" s="126"/>
-      <c r="AF5" s="127"/>
-      <c r="AG5" s="127"/>
-      <c r="AH5" s="128"/>
-      <c r="AR5" s="45" t="s">
+      <c r="Z5" s="146"/>
+      <c r="AA5" s="146"/>
+      <c r="AB5" s="146"/>
+      <c r="AC5" s="146"/>
+      <c r="AD5" s="80"/>
+      <c r="AE5" s="157"/>
+      <c r="AF5" s="158"/>
+      <c r="AG5" s="158"/>
+      <c r="AH5" s="159"/>
+      <c r="AR5" s="40" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2029,129 +1985,129 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
-      <c r="AK6" s="107"/>
-      <c r="AL6" s="107"/>
+      <c r="AK6" s="75"/>
+      <c r="AL6" s="75"/>
     </row>
     <row r="7" spans="1:766" s="9" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="85">
+      <c r="C7" s="140"/>
+      <c r="D7" s="57">
         <v>1</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="57">
         <v>2</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="60">
         <v>3</v>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="60">
         <v>4</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="58">
         <v>5</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="59">
         <v>6</v>
       </c>
-      <c r="J7" s="85">
+      <c r="J7" s="57">
         <v>7</v>
       </c>
-      <c r="K7" s="85">
+      <c r="K7" s="57">
         <v>8</v>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="60">
         <v>9</v>
       </c>
-      <c r="M7" s="88">
+      <c r="M7" s="60">
         <v>10</v>
       </c>
-      <c r="N7" s="88">
+      <c r="N7" s="60">
         <v>11</v>
       </c>
-      <c r="O7" s="87">
+      <c r="O7" s="59">
         <v>12</v>
       </c>
-      <c r="P7" s="87">
+      <c r="P7" s="59">
         <v>13</v>
       </c>
-      <c r="Q7" s="85">
+      <c r="Q7" s="57">
         <v>14</v>
       </c>
-      <c r="R7" s="85">
+      <c r="R7" s="57">
         <v>15</v>
       </c>
-      <c r="S7" s="85">
+      <c r="S7" s="57">
         <v>16</v>
       </c>
-      <c r="T7" s="88">
+      <c r="T7" s="60">
         <v>17</v>
       </c>
-      <c r="U7" s="88">
+      <c r="U7" s="60">
         <v>18</v>
       </c>
-      <c r="V7" s="87">
+      <c r="V7" s="59">
         <v>19</v>
       </c>
-      <c r="W7" s="87">
+      <c r="W7" s="59">
         <v>20</v>
       </c>
-      <c r="X7" s="85">
+      <c r="X7" s="57">
         <v>21</v>
       </c>
-      <c r="Y7" s="85">
+      <c r="Y7" s="57">
         <v>22</v>
       </c>
-      <c r="Z7" s="85">
+      <c r="Z7" s="57">
         <v>23</v>
       </c>
-      <c r="AA7" s="84">
+      <c r="AA7" s="56">
         <v>24</v>
       </c>
-      <c r="AB7" s="84">
+      <c r="AB7" s="56">
         <v>25</v>
       </c>
-      <c r="AC7" s="87">
+      <c r="AC7" s="59">
         <v>26</v>
       </c>
-      <c r="AD7" s="87">
+      <c r="AD7" s="59">
         <v>27</v>
       </c>
-      <c r="AE7" s="85">
+      <c r="AE7" s="57">
         <v>28</v>
       </c>
-      <c r="AF7" s="85">
+      <c r="AF7" s="57">
         <v>29</v>
       </c>
-      <c r="AG7" s="85">
+      <c r="AG7" s="57">
         <v>30</v>
       </c>
-      <c r="AH7" s="88">
+      <c r="AH7" s="60">
         <v>31</v>
       </c>
-      <c r="AI7" s="101" t="s">
+      <c r="AI7" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="AJ7" s="48" t="s">
+      <c r="AJ7" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="AK7" s="101" t="s">
+      <c r="AK7" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="AL7" s="49" t="s">
+      <c r="AL7" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="AM7" s="110" t="s">
+      <c r="AM7" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="AN7" s="111" t="s">
+      <c r="AN7" s="142" t="s">
         <v>13</v>
       </c>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="46"/>
+      <c r="AO7" s="78"/>
+      <c r="AP7" s="41"/>
       <c r="AQ7" s="10"/>
-      <c r="AR7" s="46"/>
+      <c r="AR7" s="41"/>
       <c r="AS7" s="11"/>
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
@@ -2870,117 +2826,117 @@
       <c r="ACF7" s="11"/>
     </row>
     <row r="8" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="85" t="s">
+      <c r="C8" s="143"/>
+      <c r="D8" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="F8" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="I8" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="85" t="s">
+      <c r="J8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="85" t="s">
+      <c r="K8" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="88" t="s">
+      <c r="L8" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="88" t="s">
+      <c r="M8" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="88" t="s">
+      <c r="N8" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="87" t="s">
+      <c r="O8" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="87" t="s">
+      <c r="P8" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="85" t="s">
+      <c r="Q8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="85" t="s">
+      <c r="R8" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="85" t="s">
+      <c r="S8" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="88" t="s">
+      <c r="T8" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="88" t="s">
+      <c r="U8" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="87" t="s">
+      <c r="V8" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="87" t="s">
+      <c r="W8" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="85" t="s">
+      <c r="X8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="89" t="s">
+      <c r="Y8" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="89" t="s">
+      <c r="Z8" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="84" t="s">
+      <c r="AA8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" s="91" t="s">
+      <c r="AB8" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="87" t="s">
+      <c r="AC8" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="AD8" s="87" t="s">
+      <c r="AD8" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="AE8" s="90" t="s">
+      <c r="AE8" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="85" t="s">
+      <c r="AF8" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="AG8" s="85" t="s">
+      <c r="AG8" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="84" t="s">
+      <c r="AH8" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="AI8" s="101"/>
-      <c r="AJ8" s="101"/>
-      <c r="AK8" s="101"/>
-      <c r="AL8" s="50"/>
-      <c r="AM8" s="110"/>
-      <c r="AN8" s="111"/>
-      <c r="AO8" s="102"/>
-      <c r="AP8" s="69" t="s">
+      <c r="AI8" s="77"/>
+      <c r="AJ8" s="77"/>
+      <c r="AK8" s="77"/>
+      <c r="AL8" s="44"/>
+      <c r="AM8" s="141"/>
+      <c r="AN8" s="142"/>
+      <c r="AO8" s="78"/>
+      <c r="AP8" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AQ8" s="46" t="s">
+      <c r="AQ8" s="41" t="s">
         <v>29</v>
       </c>
       <c r="AR8" s="10" t="s">
@@ -3703,52 +3659,52 @@
       <c r="ACF8" s="11"/>
     </row>
     <row r="9" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="65">
+      <c r="A9" s="48">
         <v>1</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="51"/>
+      <c r="B9" s="161"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="13"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="156"/>
-      <c r="M9" s="156"/>
-      <c r="N9" s="156"/>
-      <c r="O9" s="129"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="81"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
-      <c r="R9" s="130"/>
+      <c r="R9" s="82"/>
       <c r="S9" s="16"/>
-      <c r="T9" s="143"/>
-      <c r="U9" s="143"/>
+      <c r="T9" s="91"/>
+      <c r="U9" s="91"/>
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="43"/>
+      <c r="Y9" s="38"/>
       <c r="Z9" s="16"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="129"/>
-      <c r="AD9" s="129"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="43"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="81"/>
+      <c r="AD9" s="81"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="38"/>
       <c r="AG9" s="16"/>
-      <c r="AH9" s="93"/>
+      <c r="AH9" s="65"/>
       <c r="AI9" s="18"/>
       <c r="AJ9" s="18"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="50"/>
-      <c r="AM9" s="52"/>
-      <c r="AN9" s="53"/>
-      <c r="AO9" s="53"/>
-      <c r="AP9" s="46"/>
-      <c r="AQ9" s="10"/>
-      <c r="AR9" s="46"/>
+      <c r="AK9" s="37"/>
+      <c r="AL9" s="43"/>
+      <c r="AM9" s="162"/>
+      <c r="AN9" s="163"/>
+      <c r="AO9" s="163"/>
+      <c r="AP9" s="164"/>
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="164"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
@@ -4465,52 +4421,52 @@
       <c r="ACD9" s="11"/>
     </row>
     <row r="10" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="65">
+      <c r="A10" s="48">
         <v>2</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="51"/>
+      <c r="B10" s="161"/>
+      <c r="C10" s="72"/>
       <c r="D10" s="13"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="144"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="92"/>
       <c r="H10" s="160"/>
-      <c r="I10" s="129"/>
+      <c r="I10" s="81"/>
       <c r="J10" s="13"/>
       <c r="K10" s="16"/>
-      <c r="L10" s="143"/>
-      <c r="M10" s="143"/>
-      <c r="N10" s="143"/>
-      <c r="O10" s="129"/>
-      <c r="P10" s="129"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="81"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
-      <c r="T10" s="143"/>
-      <c r="U10" s="143"/>
-      <c r="V10" s="129"/>
-      <c r="W10" s="129"/>
+      <c r="T10" s="91"/>
+      <c r="U10" s="91"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="43"/>
+      <c r="Y10" s="38"/>
       <c r="Z10" s="16"/>
-      <c r="AA10" s="143"/>
-      <c r="AB10" s="150"/>
-      <c r="AC10" s="129"/>
-      <c r="AD10" s="129"/>
-      <c r="AE10" s="82"/>
-      <c r="AF10" s="43"/>
+      <c r="AA10" s="91"/>
+      <c r="AB10" s="98"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="81"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="38"/>
       <c r="AG10" s="16"/>
-      <c r="AH10" s="92"/>
+      <c r="AH10" s="64"/>
       <c r="AI10" s="18"/>
       <c r="AJ10" s="18"/>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="50"/>
-      <c r="AM10" s="52"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="46"/>
-      <c r="AQ10" s="10"/>
-      <c r="AR10" s="46"/>
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="43"/>
+      <c r="AM10" s="162"/>
+      <c r="AN10" s="163"/>
+      <c r="AO10" s="163"/>
+      <c r="AP10" s="164"/>
+      <c r="AQ10" s="45"/>
+      <c r="AR10" s="164"/>
       <c r="AS10" s="11"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
@@ -5227,52 +5183,52 @@
       <c r="ACD10" s="11"/>
     </row>
     <row r="11" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="65">
+      <c r="A11" s="48">
         <v>3</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="51"/>
+      <c r="B11" s="161"/>
+      <c r="C11" s="72"/>
       <c r="D11" s="13"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="129"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="81"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="143"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="81"/>
+      <c r="P11" s="81"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="16"/>
       <c r="S11" s="13"/>
-      <c r="T11" s="143"/>
-      <c r="U11" s="143"/>
-      <c r="V11" s="129"/>
-      <c r="W11" s="129"/>
+      <c r="T11" s="91"/>
+      <c r="U11" s="91"/>
+      <c r="V11" s="81"/>
+      <c r="W11" s="81"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="150"/>
-      <c r="AC11" s="129"/>
-      <c r="AD11" s="129"/>
-      <c r="AE11" s="82"/>
+      <c r="AA11" s="92"/>
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="54"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
-      <c r="AH11" s="92"/>
+      <c r="AH11" s="64"/>
       <c r="AI11" s="18"/>
       <c r="AJ11" s="18"/>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="56"/>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="55"/>
-      <c r="AO11" s="55"/>
-      <c r="AP11" s="47"/>
-      <c r="AQ11" s="20"/>
-      <c r="AR11" s="47"/>
+      <c r="AK11" s="37"/>
+      <c r="AL11" s="162"/>
+      <c r="AM11" s="162"/>
+      <c r="AN11" s="163"/>
+      <c r="AO11" s="163"/>
+      <c r="AP11" s="164"/>
+      <c r="AQ11" s="45"/>
+      <c r="AR11" s="164"/>
       <c r="AS11" s="11"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
@@ -5989,52 +5945,52 @@
       <c r="ACD11" s="11"/>
     </row>
     <row r="12" spans="1:766" ht="24" customHeight="1">
-      <c r="A12" s="65">
+      <c r="A12" s="48">
         <v>4</v>
       </c>
-      <c r="B12" s="101"/>
-      <c r="C12" s="57"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="13"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="129"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="81"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="144"/>
-      <c r="N12" s="143"/>
-      <c r="O12" s="129"/>
-      <c r="P12" s="129"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="95"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
-      <c r="T12" s="144"/>
-      <c r="U12" s="144"/>
-      <c r="V12" s="129"/>
-      <c r="W12" s="129"/>
+      <c r="T12" s="92"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="144"/>
-      <c r="AB12" s="141"/>
-      <c r="AC12" s="129"/>
-      <c r="AD12" s="129"/>
-      <c r="AE12" s="37"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="92"/>
+      <c r="AB12" s="90"/>
+      <c r="AC12" s="81"/>
+      <c r="AD12" s="81"/>
+      <c r="AE12" s="34"/>
       <c r="AF12" s="16"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="94"/>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="66"/>
       <c r="AI12" s="18"/>
       <c r="AJ12" s="18"/>
-      <c r="AK12" s="58"/>
-      <c r="AL12" s="55"/>
-      <c r="AM12" s="58"/>
-      <c r="AN12" s="55"/>
-      <c r="AO12" s="55"/>
-      <c r="AP12" s="47"/>
-      <c r="AQ12" s="20"/>
-      <c r="AR12" s="47"/>
+      <c r="AK12" s="165"/>
+      <c r="AL12" s="163"/>
+      <c r="AM12" s="165"/>
+      <c r="AN12" s="163"/>
+      <c r="AO12" s="163"/>
+      <c r="AP12" s="164"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="164"/>
       <c r="ACE12"/>
       <c r="ACF12"/>
       <c r="ACG12"/>
@@ -6044,53 +6000,53 @@
       <c r="ACK12"/>
       <c r="ACL12"/>
     </row>
-    <row r="13" spans="1:766" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="65">
+    <row r="13" spans="1:766" ht="24" customHeight="1">
+      <c r="A13" s="48">
         <v>5</v>
       </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="51"/>
+      <c r="B13" s="161"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="129"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="81"/>
       <c r="J13" s="16"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="129"/>
-      <c r="Q13" s="130"/>
-      <c r="R13" s="130"/>
-      <c r="S13" s="130"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="145"/>
-      <c r="V13" s="129"/>
-      <c r="W13" s="129"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="92"/>
+      <c r="U13" s="93"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-      <c r="AA13" s="144"/>
-      <c r="AB13" s="141"/>
-      <c r="AC13" s="129"/>
-      <c r="AD13" s="129"/>
-      <c r="AE13" s="37"/>
+      <c r="AA13" s="92"/>
+      <c r="AB13" s="90"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="81"/>
+      <c r="AE13" s="34"/>
       <c r="AF13" s="16"/>
       <c r="AG13" s="16"/>
-      <c r="AH13" s="94"/>
+      <c r="AH13" s="66"/>
       <c r="AI13" s="18"/>
       <c r="AJ13" s="18"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="56"/>
-      <c r="AM13" s="52"/>
-      <c r="AN13" s="55"/>
-      <c r="AO13" s="55"/>
-      <c r="AP13" s="47"/>
-      <c r="AQ13" s="60"/>
-      <c r="AR13" s="47"/>
+      <c r="AK13" s="37"/>
+      <c r="AL13" s="162"/>
+      <c r="AM13" s="162"/>
+      <c r="AN13" s="163"/>
+      <c r="AO13" s="163"/>
+      <c r="AP13" s="164"/>
+      <c r="AQ13" s="45"/>
+      <c r="AR13" s="164"/>
       <c r="ACE13"/>
       <c r="ACF13"/>
       <c r="ACG13"/>
@@ -6100,53 +6056,53 @@
       <c r="ACK13"/>
       <c r="ACL13"/>
     </row>
-    <row r="14" spans="1:766" ht="24" customHeight="1" thickTop="1">
-      <c r="A14" s="65">
+    <row r="14" spans="1:766" ht="24" customHeight="1">
+      <c r="A14" s="48">
         <v>6</v>
       </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="100"/>
+      <c r="B14" s="161"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="129"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="81"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="129"/>
-      <c r="W14" s="129"/>
+      <c r="T14" s="92"/>
+      <c r="U14" s="92"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="81"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="142"/>
-      <c r="AC14" s="138"/>
-      <c r="AD14" s="129"/>
-      <c r="AE14" s="37"/>
+      <c r="AA14" s="92"/>
+      <c r="AB14" s="166"/>
+      <c r="AC14" s="84"/>
+      <c r="AD14" s="81"/>
+      <c r="AE14" s="34"/>
       <c r="AF14" s="16"/>
       <c r="AG14" s="16"/>
-      <c r="AH14" s="94"/>
+      <c r="AH14" s="66"/>
       <c r="AI14" s="18"/>
       <c r="AJ14" s="18"/>
       <c r="AK14" s="18"/>
-      <c r="AL14" s="56"/>
-      <c r="AM14" s="58"/>
-      <c r="AN14" s="55"/>
-      <c r="AO14" s="55"/>
-      <c r="AP14" s="47"/>
-      <c r="AQ14" s="20"/>
-      <c r="AR14" s="47"/>
+      <c r="AL14" s="162"/>
+      <c r="AM14" s="165"/>
+      <c r="AN14" s="163"/>
+      <c r="AO14" s="163"/>
+      <c r="AP14" s="164"/>
+      <c r="AQ14" s="45"/>
+      <c r="AR14" s="164"/>
       <c r="ACE14"/>
       <c r="ACF14"/>
       <c r="ACG14"/>
@@ -6157,52 +6113,52 @@
       <c r="ACL14"/>
     </row>
     <row r="15" spans="1:766" ht="24" customHeight="1">
-      <c r="A15" s="65">
+      <c r="A15" s="48">
         <v>7</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="156"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="132"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="167"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="168"/>
+      <c r="J15" s="167"/>
       <c r="K15" s="16"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="25"/>
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="92"/>
+      <c r="O15" s="168"/>
+      <c r="P15" s="168"/>
+      <c r="Q15" s="23"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
-      <c r="T15" s="144"/>
-      <c r="U15" s="146"/>
-      <c r="V15" s="129"/>
-      <c r="W15" s="129"/>
+      <c r="T15" s="92"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
-      <c r="AA15" s="144"/>
-      <c r="AB15" s="141"/>
-      <c r="AC15" s="129"/>
-      <c r="AD15" s="129"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="25"/>
+      <c r="AA15" s="92"/>
+      <c r="AB15" s="90"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="81"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="23"/>
       <c r="AG15" s="16"/>
-      <c r="AH15" s="95"/>
+      <c r="AH15" s="67"/>
       <c r="AI15" s="18"/>
       <c r="AJ15" s="18"/>
-      <c r="AK15" s="59"/>
-      <c r="AL15" s="56"/>
-      <c r="AM15" s="52"/>
-      <c r="AN15" s="55"/>
-      <c r="AO15" s="55"/>
-      <c r="AP15" s="47"/>
-      <c r="AQ15" s="60"/>
-      <c r="AR15" s="47"/>
+      <c r="AK15" s="37"/>
+      <c r="AL15" s="162"/>
+      <c r="AM15" s="162"/>
+      <c r="AN15" s="163"/>
+      <c r="AO15" s="163"/>
+      <c r="AP15" s="164"/>
+      <c r="AQ15" s="45"/>
+      <c r="AR15" s="164"/>
       <c r="ACE15"/>
       <c r="ACF15"/>
       <c r="ACG15"/>
@@ -6213,52 +6169,52 @@
       <c r="ACL15"/>
     </row>
     <row r="16" spans="1:766" ht="24" customHeight="1">
-      <c r="A16" s="65">
+      <c r="A16" s="48">
         <v>8</v>
       </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="129"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="81"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
-      <c r="T16" s="143"/>
-      <c r="U16" s="146"/>
-      <c r="V16" s="129"/>
-      <c r="W16" s="129"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="143"/>
-      <c r="AB16" s="141"/>
-      <c r="AC16" s="129"/>
-      <c r="AD16" s="129"/>
-      <c r="AE16" s="83"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="95"/>
+      <c r="T16" s="91"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="91"/>
+      <c r="AB16" s="90"/>
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="55"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="67"/>
       <c r="AI16" s="18"/>
       <c r="AJ16" s="18"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="56"/>
-      <c r="AM16" s="52"/>
-      <c r="AN16" s="55"/>
-      <c r="AO16" s="55"/>
-      <c r="AP16" s="47"/>
-      <c r="AQ16" s="20"/>
-      <c r="AR16" s="47"/>
+      <c r="AK16" s="169"/>
+      <c r="AL16" s="162"/>
+      <c r="AM16" s="162"/>
+      <c r="AN16" s="163"/>
+      <c r="AO16" s="163"/>
+      <c r="AP16" s="164"/>
+      <c r="AQ16" s="45"/>
+      <c r="AR16" s="164"/>
       <c r="ACE16"/>
       <c r="ACF16"/>
       <c r="ACG16"/>
@@ -6269,52 +6225,52 @@
       <c r="ACL16"/>
     </row>
     <row r="17" spans="1:766" ht="24" customHeight="1">
-      <c r="A17" s="65">
+      <c r="A17" s="48">
         <v>1</v>
       </c>
-      <c r="B17" s="101"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="170"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="129"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="81"/>
       <c r="J17" s="13"/>
       <c r="K17" s="16"/>
-      <c r="L17" s="143"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="25"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="23"/>
       <c r="R17" s="16"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="144"/>
-      <c r="U17" s="144"/>
-      <c r="V17" s="129"/>
-      <c r="W17" s="129"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="130"/>
-      <c r="Z17" s="133"/>
-      <c r="AA17" s="144"/>
-      <c r="AB17" s="141"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="129"/>
-      <c r="AE17" s="38"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="92"/>
+      <c r="U17" s="92"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="83"/>
+      <c r="AA17" s="92"/>
+      <c r="AB17" s="90"/>
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="35"/>
       <c r="AF17" s="16"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="95"/>
+      <c r="AG17" s="23"/>
+      <c r="AH17" s="67"/>
       <c r="AI17" s="18"/>
       <c r="AJ17" s="18"/>
-      <c r="AK17" s="41"/>
-      <c r="AL17" s="56"/>
-      <c r="AM17" s="52"/>
-      <c r="AN17" s="55"/>
-      <c r="AO17" s="55"/>
-      <c r="AP17" s="47"/>
-      <c r="AQ17" s="20"/>
-      <c r="AR17" s="47"/>
+      <c r="AK17" s="37"/>
+      <c r="AL17" s="162"/>
+      <c r="AM17" s="162"/>
+      <c r="AN17" s="163"/>
+      <c r="AO17" s="163"/>
+      <c r="AP17" s="164"/>
+      <c r="AQ17" s="45"/>
+      <c r="AR17" s="164"/>
       <c r="ACE17"/>
       <c r="ACF17"/>
       <c r="ACG17"/>
@@ -6325,52 +6281,52 @@
       <c r="ACL17"/>
     </row>
     <row r="18" spans="1:766" ht="24" customHeight="1">
-      <c r="A18" s="65">
+      <c r="A18" s="48">
         <v>1</v>
       </c>
-      <c r="B18" s="169"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="192"/>
-      <c r="I18" s="193"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="172"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="158"/>
-      <c r="M18" s="158"/>
-      <c r="N18" s="158"/>
-      <c r="O18" s="193"/>
-      <c r="P18" s="193"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="106"/>
+      <c r="N18" s="106"/>
+      <c r="O18" s="126"/>
+      <c r="P18" s="126"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
-      <c r="S18" s="194"/>
-      <c r="T18" s="195"/>
-      <c r="U18" s="195"/>
-      <c r="V18" s="196"/>
-      <c r="W18" s="193"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="158"/>
-      <c r="AB18" s="197"/>
-      <c r="AC18" s="193"/>
-      <c r="AD18" s="193"/>
-      <c r="AE18" s="99"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="27"/>
-      <c r="AJ18" s="27"/>
-      <c r="AK18" s="27"/>
-      <c r="AL18" s="71"/>
-      <c r="AM18" s="72"/>
-      <c r="AN18" s="198"/>
-      <c r="AO18" s="198"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="74"/>
-      <c r="AR18" s="62"/>
+      <c r="S18" s="127"/>
+      <c r="T18" s="128"/>
+      <c r="U18" s="128"/>
+      <c r="V18" s="129"/>
+      <c r="W18" s="126"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="106"/>
+      <c r="AB18" s="130"/>
+      <c r="AC18" s="126"/>
+      <c r="AD18" s="126"/>
+      <c r="AE18" s="71"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="68"/>
+      <c r="AI18" s="25"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="25"/>
+      <c r="AL18" s="173"/>
+      <c r="AM18" s="173"/>
+      <c r="AN18" s="174"/>
+      <c r="AO18" s="174"/>
+      <c r="AP18" s="175"/>
+      <c r="AQ18" s="176"/>
+      <c r="AR18" s="175"/>
       <c r="ACE18"/>
       <c r="ACF18"/>
       <c r="ACG18"/>
@@ -6381,52 +6337,52 @@
       <c r="ACL18"/>
     </row>
     <row r="19" spans="1:766" ht="24" customHeight="1">
-      <c r="A19" s="65">
+      <c r="A19" s="48">
         <v>2</v>
       </c>
-      <c r="B19" s="171"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="175"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="173"/>
-      <c r="L19" s="174"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="174"/>
-      <c r="O19" s="179"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="176"/>
-      <c r="R19" s="177"/>
-      <c r="S19" s="173"/>
-      <c r="T19" s="174"/>
-      <c r="U19" s="174"/>
-      <c r="V19" s="179"/>
-      <c r="W19" s="179"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="180"/>
-      <c r="AA19" s="181"/>
-      <c r="AB19" s="182"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="179"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="173"/>
-      <c r="AG19" s="173"/>
-      <c r="AH19" s="185"/>
-      <c r="AI19" s="186"/>
-      <c r="AJ19" s="186"/>
-      <c r="AK19" s="186"/>
-      <c r="AL19" s="187"/>
-      <c r="AM19" s="188"/>
-      <c r="AN19" s="189"/>
-      <c r="AO19" s="189"/>
-      <c r="AP19" s="190"/>
-      <c r="AQ19" s="191"/>
-      <c r="AR19" s="190"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="117"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="114"/>
+      <c r="R19" s="115"/>
+      <c r="S19" s="111"/>
+      <c r="T19" s="112"/>
+      <c r="U19" s="112"/>
+      <c r="V19" s="117"/>
+      <c r="W19" s="117"/>
+      <c r="X19" s="111"/>
+      <c r="Y19" s="111"/>
+      <c r="Z19" s="118"/>
+      <c r="AA19" s="119"/>
+      <c r="AB19" s="120"/>
+      <c r="AC19" s="121"/>
+      <c r="AD19" s="117"/>
+      <c r="AE19" s="122"/>
+      <c r="AF19" s="111"/>
+      <c r="AG19" s="111"/>
+      <c r="AH19" s="123"/>
+      <c r="AI19" s="124"/>
+      <c r="AJ19" s="124"/>
+      <c r="AK19" s="124"/>
+      <c r="AL19" s="179"/>
+      <c r="AM19" s="179"/>
+      <c r="AN19" s="180"/>
+      <c r="AO19" s="180"/>
+      <c r="AP19" s="181"/>
+      <c r="AQ19" s="182"/>
+      <c r="AR19" s="181"/>
       <c r="ACE19"/>
       <c r="ACF19"/>
       <c r="ACG19"/>
@@ -6437,52 +6393,52 @@
       <c r="ACL19"/>
     </row>
     <row r="20" spans="1:766" ht="24" customHeight="1">
-      <c r="A20" s="65">
+      <c r="A20" s="48">
         <v>1</v>
       </c>
-      <c r="B20" s="170"/>
-      <c r="C20" s="199"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="203"/>
-      <c r="J20" s="24"/>
+      <c r="B20" s="183"/>
+      <c r="C20" s="184"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="22"/>
       <c r="K20" s="14"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="162"/>
-      <c r="N20" s="204"/>
-      <c r="O20" s="203"/>
-      <c r="P20" s="203"/>
+      <c r="L20" s="109"/>
+      <c r="M20" s="109"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="134"/>
+      <c r="P20" s="134"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="17"/>
       <c r="S20" s="12"/>
-      <c r="T20" s="205"/>
-      <c r="U20" s="151"/>
-      <c r="V20" s="203"/>
-      <c r="W20" s="203"/>
+      <c r="T20" s="136"/>
+      <c r="U20" s="99"/>
+      <c r="V20" s="134"/>
+      <c r="W20" s="134"/>
       <c r="X20" s="12"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="151"/>
-      <c r="AB20" s="152"/>
-      <c r="AC20" s="203"/>
-      <c r="AD20" s="203"/>
-      <c r="AE20" s="36"/>
-      <c r="AF20" s="140"/>
-      <c r="AG20" s="140"/>
-      <c r="AH20" s="206"/>
+      <c r="AA20" s="99"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="134"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="89"/>
+      <c r="AG20" s="89"/>
+      <c r="AH20" s="137"/>
       <c r="AI20" s="19"/>
       <c r="AJ20" s="19"/>
-      <c r="AK20" s="207"/>
-      <c r="AL20" s="208"/>
-      <c r="AM20" s="209"/>
-      <c r="AN20" s="78"/>
-      <c r="AO20" s="78"/>
-      <c r="AP20" s="79"/>
-      <c r="AQ20" s="210"/>
-      <c r="AR20" s="211"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="185"/>
+      <c r="AM20" s="186"/>
+      <c r="AN20" s="187"/>
+      <c r="AO20" s="187"/>
+      <c r="AP20" s="188"/>
+      <c r="AQ20" s="189"/>
+      <c r="AR20" s="190"/>
       <c r="ACF20"/>
       <c r="ACG20"/>
       <c r="ACH20"/>
@@ -6492,52 +6448,52 @@
       <c r="ACL20"/>
     </row>
     <row r="21" spans="1:766" ht="24" customHeight="1">
-      <c r="A21" s="65">
+      <c r="A21" s="48">
         <v>2</v>
       </c>
-      <c r="B21" s="169"/>
-      <c r="C21" s="51"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="72"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="156"/>
-      <c r="I21" s="129"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="81"/>
       <c r="J21" s="16"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="129"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="13"/>
       <c r="S21" s="16"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="144"/>
-      <c r="V21" s="129"/>
-      <c r="W21" s="129"/>
+      <c r="T21" s="91"/>
+      <c r="U21" s="92"/>
+      <c r="V21" s="81"/>
+      <c r="W21" s="81"/>
       <c r="X21" s="16"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="16"/>
-      <c r="AA21" s="151"/>
-      <c r="AB21" s="152"/>
-      <c r="AC21" s="129"/>
-      <c r="AD21" s="129"/>
-      <c r="AE21" s="36"/>
+      <c r="AA21" s="99"/>
+      <c r="AB21" s="100"/>
+      <c r="AC21" s="81"/>
+      <c r="AD21" s="81"/>
+      <c r="AE21" s="33"/>
       <c r="AF21" s="12"/>
-      <c r="AG21" s="98"/>
-      <c r="AH21" s="97"/>
+      <c r="AG21" s="70"/>
+      <c r="AH21" s="69"/>
       <c r="AI21" s="18"/>
       <c r="AJ21" s="18"/>
-      <c r="AK21" s="214"/>
-      <c r="AL21" s="56"/>
-      <c r="AM21" s="72"/>
-      <c r="AN21" s="73"/>
-      <c r="AO21" s="73"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="20"/>
-      <c r="AR21" s="62"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="162"/>
+      <c r="AM21" s="173"/>
+      <c r="AN21" s="191"/>
+      <c r="AO21" s="191"/>
+      <c r="AP21" s="175"/>
+      <c r="AQ21" s="45"/>
+      <c r="AR21" s="175"/>
       <c r="ACF21"/>
       <c r="ACG21"/>
       <c r="ACH21"/>
@@ -6547,52 +6503,52 @@
       <c r="ACL21"/>
     </row>
     <row r="22" spans="1:766" ht="24" customHeight="1">
-      <c r="A22" s="65">
+      <c r="A22" s="48">
         <v>3</v>
       </c>
-      <c r="B22" s="167"/>
-      <c r="C22" s="168"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="163"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="156"/>
-      <c r="I22" s="129"/>
+      <c r="B22" s="192"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="110"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="81"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="144"/>
-      <c r="M22" s="158"/>
-      <c r="N22" s="158"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="129"/>
-      <c r="Q22" s="21"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="106"/>
+      <c r="N22" s="106"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="20"/>
       <c r="R22" s="15"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="148"/>
-      <c r="U22" s="148"/>
-      <c r="V22" s="135"/>
-      <c r="W22" s="135"/>
-      <c r="X22" s="136"/>
-      <c r="Y22" s="137"/>
-      <c r="Z22" s="136"/>
-      <c r="AA22" s="153"/>
-      <c r="AB22" s="154"/>
-      <c r="AC22" s="135"/>
-      <c r="AD22" s="134"/>
-      <c r="AE22" s="139"/>
-      <c r="AF22" s="140"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="96"/>
+      <c r="U22" s="96"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="86"/>
+      <c r="Y22" s="87"/>
+      <c r="Z22" s="86"/>
+      <c r="AA22" s="101"/>
+      <c r="AB22" s="102"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="84"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="89"/>
       <c r="AG22" s="13"/>
-      <c r="AH22" s="93"/>
+      <c r="AH22" s="65"/>
       <c r="AI22" s="19"/>
-      <c r="AJ22" s="213"/>
-      <c r="AK22" s="212"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="164"/>
-      <c r="AN22" s="165"/>
-      <c r="AO22" s="165"/>
-      <c r="AP22" s="166"/>
-      <c r="AQ22" s="39"/>
-      <c r="AR22" s="47"/>
+      <c r="AJ22" s="139"/>
+      <c r="AK22" s="138"/>
+      <c r="AL22" s="194"/>
+      <c r="AM22" s="195"/>
+      <c r="AN22" s="196"/>
+      <c r="AO22" s="196"/>
+      <c r="AP22" s="197"/>
+      <c r="AQ22" s="198"/>
+      <c r="AR22" s="164"/>
       <c r="ACF22"/>
       <c r="ACG22"/>
       <c r="ACH22"/>
@@ -6602,52 +6558,52 @@
       <c r="ACL22"/>
     </row>
     <row r="23" spans="1:766" ht="24" customHeight="1">
-      <c r="A23" s="65">
+      <c r="A23" s="48">
         <v>4</v>
       </c>
-      <c r="B23" s="170"/>
-      <c r="C23" s="51"/>
+      <c r="B23" s="183"/>
+      <c r="C23" s="72"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="130"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="82"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="143"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="81"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="13"/>
       <c r="S23" s="16"/>
-      <c r="T23" s="147"/>
-      <c r="U23" s="147"/>
-      <c r="V23" s="129"/>
-      <c r="W23" s="129"/>
+      <c r="T23" s="95"/>
+      <c r="U23" s="95"/>
+      <c r="V23" s="81"/>
+      <c r="W23" s="81"/>
       <c r="X23" s="16"/>
       <c r="Y23" s="13"/>
       <c r="Z23" s="16"/>
-      <c r="AA23" s="144"/>
-      <c r="AB23" s="141"/>
-      <c r="AC23" s="129"/>
-      <c r="AD23" s="129"/>
-      <c r="AE23" s="37"/>
+      <c r="AA23" s="92"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="81"/>
+      <c r="AD23" s="81"/>
+      <c r="AE23" s="34"/>
       <c r="AF23" s="16"/>
       <c r="AG23" s="16"/>
-      <c r="AH23" s="92"/>
+      <c r="AH23" s="64"/>
       <c r="AI23" s="19"/>
       <c r="AJ23" s="19"/>
-      <c r="AK23" s="75"/>
-      <c r="AL23" s="76"/>
-      <c r="AM23" s="77"/>
-      <c r="AN23" s="78"/>
-      <c r="AO23" s="78"/>
-      <c r="AP23" s="79"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="47"/>
+      <c r="AK23" s="52"/>
+      <c r="AL23" s="199"/>
+      <c r="AM23" s="199"/>
+      <c r="AN23" s="187"/>
+      <c r="AO23" s="187"/>
+      <c r="AP23" s="188"/>
+      <c r="AQ23" s="200"/>
+      <c r="AR23" s="164"/>
       <c r="ACF23"/>
       <c r="ACG23"/>
       <c r="ACH23"/>
@@ -6657,52 +6613,52 @@
       <c r="ACL23"/>
     </row>
     <row r="24" spans="1:766" ht="24" customHeight="1">
-      <c r="A24" s="65">
+      <c r="A24" s="48">
         <v>5</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="51"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="72"/>
       <c r="D24" s="16"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="156"/>
-      <c r="I24" s="129"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="81"/>
       <c r="J24" s="16"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="143"/>
-      <c r="N24" s="144"/>
-      <c r="O24" s="129"/>
-      <c r="P24" s="129"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="81"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
-      <c r="T24" s="143"/>
-      <c r="U24" s="144"/>
-      <c r="V24" s="129"/>
-      <c r="W24" s="129"/>
+      <c r="T24" s="91"/>
+      <c r="U24" s="92"/>
+      <c r="V24" s="81"/>
+      <c r="W24" s="81"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="13"/>
-      <c r="AA24" s="151"/>
-      <c r="AB24" s="152"/>
-      <c r="AC24" s="129"/>
-      <c r="AD24" s="129"/>
-      <c r="AE24" s="37"/>
+      <c r="AA24" s="99"/>
+      <c r="AB24" s="100"/>
+      <c r="AC24" s="81"/>
+      <c r="AD24" s="81"/>
+      <c r="AE24" s="34"/>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
-      <c r="AH24" s="94"/>
+      <c r="AH24" s="66"/>
       <c r="AI24" s="18"/>
       <c r="AJ24" s="18"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="56"/>
-      <c r="AM24" s="52"/>
-      <c r="AN24" s="55"/>
-      <c r="AO24" s="55"/>
-      <c r="AP24" s="47"/>
-      <c r="AQ24" s="20"/>
-      <c r="AR24" s="47"/>
+      <c r="AK24" s="37"/>
+      <c r="AL24" s="162"/>
+      <c r="AM24" s="162"/>
+      <c r="AN24" s="163"/>
+      <c r="AO24" s="163"/>
+      <c r="AP24" s="164"/>
+      <c r="AQ24" s="45"/>
+      <c r="AR24" s="164"/>
       <c r="ACF24"/>
       <c r="ACG24"/>
       <c r="ACH24"/>
@@ -6712,52 +6668,52 @@
       <c r="ACL24"/>
     </row>
     <row r="25" spans="1:766" ht="24" customHeight="1">
-      <c r="A25" s="65">
+      <c r="A25" s="48">
         <v>1</v>
       </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="42"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="172"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="156"/>
-      <c r="G25" s="156"/>
-      <c r="H25" s="156"/>
-      <c r="I25" s="129"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="104"/>
+      <c r="I25" s="81"/>
       <c r="J25" s="15"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="149"/>
-      <c r="M25" s="159"/>
-      <c r="N25" s="149"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="81"/>
       <c r="Q25" s="15"/>
-      <c r="R25" s="21"/>
+      <c r="R25" s="20"/>
       <c r="S25" s="15"/>
-      <c r="T25" s="149"/>
-      <c r="U25" s="149"/>
-      <c r="V25" s="129"/>
-      <c r="W25" s="129"/>
+      <c r="T25" s="97"/>
+      <c r="U25" s="97"/>
+      <c r="V25" s="81"/>
+      <c r="W25" s="81"/>
       <c r="X25" s="15"/>
-      <c r="Y25" s="21"/>
+      <c r="Y25" s="20"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="149"/>
-      <c r="AB25" s="155"/>
-      <c r="AC25" s="129"/>
-      <c r="AD25" s="129"/>
-      <c r="AE25" s="99"/>
-      <c r="AF25" s="21"/>
+      <c r="AA25" s="97"/>
+      <c r="AB25" s="103"/>
+      <c r="AC25" s="81"/>
+      <c r="AD25" s="81"/>
+      <c r="AE25" s="71"/>
+      <c r="AF25" s="20"/>
       <c r="AG25" s="15"/>
-      <c r="AH25" s="92"/>
+      <c r="AH25" s="64"/>
       <c r="AI25" s="18"/>
       <c r="AJ25" s="18"/>
-      <c r="AK25" s="41"/>
-      <c r="AL25" s="54"/>
-      <c r="AM25" s="52"/>
-      <c r="AN25" s="44"/>
-      <c r="AO25" s="44"/>
-      <c r="AP25" s="68"/>
-      <c r="AQ25" s="20"/>
-      <c r="AR25" s="47"/>
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="43"/>
+      <c r="AM25" s="162"/>
+      <c r="AN25" s="39"/>
+      <c r="AO25" s="39"/>
+      <c r="AP25" s="202"/>
+      <c r="AQ25" s="45"/>
+      <c r="AR25" s="164"/>
       <c r="ACF25"/>
       <c r="ACG25"/>
       <c r="ACH25"/>
@@ -6767,728 +6723,728 @@
       <c r="ACL25"/>
     </row>
     <row r="26" spans="1:766" ht="24" customHeight="1">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="67"/>
-      <c r="X26" s="67"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-      <c r="AA26" s="67"/>
-      <c r="AB26" s="67"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="67"/>
-      <c r="AH26" s="106"/>
-      <c r="AI26" s="106"/>
-      <c r="AJ26" s="106"/>
-      <c r="AK26" s="106"/>
-      <c r="AL26" s="106"/>
-      <c r="AM26" s="106"/>
-      <c r="AN26" s="106"/>
-      <c r="AO26" s="106"/>
-      <c r="AP26" s="106"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="53"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="74"/>
+      <c r="AI26" s="74"/>
+      <c r="AJ26" s="74"/>
+      <c r="AK26" s="74"/>
+      <c r="AL26" s="74"/>
+      <c r="AM26" s="74"/>
+      <c r="AN26" s="74"/>
+      <c r="AO26" s="74"/>
+      <c r="AP26" s="74"/>
     </row>
     <row r="27" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B27" s="63"/>
-      <c r="C27" s="63" t="s">
+      <c r="B27" s="46"/>
+      <c r="C27" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="46">
         <f>COUNTIF(D9:D19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="63">
+      <c r="E27" s="46">
         <f>COUNTIF(E9:E19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="63">
+      <c r="F27" s="46">
         <f>COUNTIF(F9:F19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="G27" s="63">
+      <c r="G27" s="46">
         <f t="shared" ref="F27:AH27" si="0">COUNTIF(G9:G19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="63">
+      <c r="H27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="63">
+      <c r="I27" s="46">
         <f>COUNTIF(I9:I19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="63">
+      <c r="J27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="63">
+      <c r="K27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="63">
+      <c r="L27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M27" s="63">
+      <c r="M27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="63">
+      <c r="N27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="63">
+      <c r="O27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="63">
+      <c r="P27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="63">
+      <c r="Q27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27" s="63">
+      <c r="R27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S27" s="63">
+      <c r="S27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T27" s="63">
+      <c r="T27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U27" s="63">
+      <c r="U27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="63">
+      <c r="V27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="63">
+      <c r="W27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="63">
+      <c r="X27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="63">
+      <c r="Y27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="63">
+      <c r="Z27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="63">
+      <c r="AA27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="63">
+      <c r="AB27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="63">
+      <c r="AC27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="63">
+      <c r="AD27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="63">
+      <c r="AE27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="63">
+      <c r="AF27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="63">
+      <c r="AG27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="32">
+      <c r="AH27" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="106"/>
+      <c r="AI27" s="29"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="29"/>
+      <c r="AL27" s="29"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="29"/>
+      <c r="AO27" s="29"/>
+      <c r="AP27" s="74"/>
     </row>
     <row r="28" spans="1:766" ht="12.75" customHeight="1">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32" t="s">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="29">
         <f t="shared" ref="D28:AH28" si="1">COUNTIF(D9:D19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="29">
         <f>COUNTIF(I9:I19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X28" s="32">
+      <c r="X28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="32">
+      <c r="Y28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="32">
+      <c r="AA28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="32">
+      <c r="AB28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="32">
+      <c r="AC28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="32">
+      <c r="AD28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="32">
+      <c r="AE28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="32">
+      <c r="AF28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="32">
+      <c r="AG28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="32">
+      <c r="AH28" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="32"/>
-      <c r="AP28" s="106"/>
+      <c r="AI28" s="29"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="29"/>
+      <c r="AL28" s="29"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="29"/>
+      <c r="AO28" s="29"/>
+      <c r="AP28" s="74"/>
     </row>
     <row r="29" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32" t="s">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="29">
         <f t="shared" ref="D29:AH29" si="2">COUNTIF(D9:D19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="29">
         <f>COUNTIF(I9:I19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="29">
         <v>2</v>
       </c>
-      <c r="R29" s="32">
+      <c r="R29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T29" s="32">
+      <c r="T29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V29" s="32">
+      <c r="V29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W29" s="32">
+      <c r="W29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X29" s="32">
+      <c r="X29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="32">
+      <c r="Y29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="32">
+      <c r="Z29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="32">
+      <c r="AA29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="32">
+      <c r="AB29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="32">
+      <c r="AC29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="32">
+      <c r="AD29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="32">
+      <c r="AE29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="32">
+      <c r="AF29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="32">
+      <c r="AG29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="32">
+      <c r="AH29" s="29">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="32"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="32"/>
-      <c r="AP29" s="106"/>
+      <c r="AI29" s="29"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="29"/>
+      <c r="AL29" s="29"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="29"/>
+      <c r="AO29" s="29"/>
+      <c r="AP29" s="74"/>
     </row>
     <row r="30" spans="1:766" ht="12" customHeight="1">
-      <c r="A30" s="33"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="29">
         <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="29">
         <f>COUNTIF(N9:N25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T30" s="32">
+      <c r="T30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X30" s="32">
+      <c r="X30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y30" s="32">
+      <c r="Y30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="32">
+      <c r="Z30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="32">
+      <c r="AD30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="32">
+      <c r="AE30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="32">
+      <c r="AF30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="32">
+      <c r="AG30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="32">
+      <c r="AH30" s="29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="32"/>
-      <c r="AP30" s="106"/>
+      <c r="AI30" s="29"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="29"/>
+      <c r="AL30" s="29"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="29"/>
+      <c r="AO30" s="29"/>
+      <c r="AP30" s="74"/>
     </row>
     <row r="31" spans="1:766">
-      <c r="A31" s="33"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="35"/>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
-      <c r="AF31" s="35"/>
-      <c r="AG31" s="35"/>
-      <c r="AH31" s="35"/>
-      <c r="AI31" s="35"/>
-      <c r="AJ31" s="35"/>
-      <c r="AK31" s="35"/>
-      <c r="AL31" s="107"/>
-      <c r="AO31" s="105"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
+      <c r="AA31" s="32"/>
+      <c r="AB31" s="32"/>
+      <c r="AC31" s="32"/>
+      <c r="AD31" s="32"/>
+      <c r="AE31" s="32"/>
+      <c r="AF31" s="32"/>
+      <c r="AG31" s="32"/>
+      <c r="AH31" s="32"/>
+      <c r="AI31" s="32"/>
+      <c r="AJ31" s="32"/>
+      <c r="AK31" s="32"/>
+      <c r="AL31" s="75"/>
+      <c r="AO31" s="73"/>
     </row>
     <row r="32" spans="1:766">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="33"/>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="33"/>
-      <c r="Y32" s="33"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33"/>
-      <c r="AC32" s="33"/>
-      <c r="AD32" s="33"/>
-      <c r="AE32" s="33"/>
-      <c r="AF32" s="33"/>
-      <c r="AG32" s="33"/>
-      <c r="AH32" s="33"/>
-      <c r="AI32" s="33"/>
-      <c r="AJ32" s="33"/>
-      <c r="AK32" s="33"/>
-      <c r="AL32" s="107"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
+      <c r="AG32" s="30"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="30"/>
+      <c r="AJ32" s="30"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="75"/>
     </row>
     <row r="33" spans="1:767" s="2" customFormat="1">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="33"/>
-      <c r="AA33" s="33"/>
-      <c r="AB33" s="33"/>
-      <c r="AC33" s="33"/>
-      <c r="AD33" s="33"/>
-      <c r="AE33" s="33"/>
-      <c r="AF33" s="33"/>
-      <c r="AG33" s="33"/>
-      <c r="AH33" s="33"/>
-      <c r="AI33" s="33"/>
-      <c r="AJ33" s="33"/>
-      <c r="AK33" s="33"/>
-      <c r="AL33" s="107"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="30"/>
+      <c r="R33" s="30"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="30"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="30"/>
+      <c r="X33" s="30"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="30"/>
+      <c r="AA33" s="30"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="30"/>
+      <c r="AD33" s="30"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="30"/>
+      <c r="AG33" s="30"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="30"/>
+      <c r="AJ33" s="30"/>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="75"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
-      <c r="AR33" s="45"/>
+      <c r="AR33" s="40"/>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -8214,50 +8170,50 @@
       <c r="ACM33"/>
     </row>
     <row r="34" spans="1:767" s="2" customFormat="1">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
-      <c r="AK34" s="33"/>
-      <c r="AL34" s="107"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="30"/>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="75"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="45"/>
+      <c r="AR34" s="40"/>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
@@ -8983,50 +8939,50 @@
       <c r="ACM34"/>
     </row>
     <row r="35" spans="1:767" s="2" customFormat="1">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="33"/>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="33"/>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="33"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="33"/>
-      <c r="AC35" s="33"/>
-      <c r="AD35" s="33"/>
-      <c r="AE35" s="33"/>
-      <c r="AF35" s="33"/>
-      <c r="AG35" s="33"/>
-      <c r="AH35" s="33"/>
-      <c r="AI35" s="33"/>
-      <c r="AJ35" s="33"/>
-      <c r="AK35" s="33"/>
-      <c r="AL35" s="107"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="30"/>
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="75"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
-      <c r="AR35" s="45"/>
+      <c r="AR35" s="40"/>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
@@ -9752,50 +9708,50 @@
       <c r="ACM35"/>
     </row>
     <row r="36" spans="1:767" s="2" customFormat="1">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
-      <c r="AD36" s="33"/>
-      <c r="AE36" s="33"/>
-      <c r="AF36" s="33"/>
-      <c r="AG36" s="33"/>
-      <c r="AH36" s="33"/>
-      <c r="AI36" s="33"/>
-      <c r="AJ36" s="33"/>
-      <c r="AK36" s="33"/>
-      <c r="AL36" s="107"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="30"/>
+      <c r="AH36" s="30"/>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="30"/>
+      <c r="AK36" s="30"/>
+      <c r="AL36" s="75"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
-      <c r="AR36" s="45"/>
+      <c r="AR36" s="40"/>
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
@@ -10521,50 +10477,50 @@
       <c r="ACM36"/>
     </row>
     <row r="37" spans="1:767" s="2" customFormat="1">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="33"/>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="33"/>
-      <c r="Y37" s="33"/>
-      <c r="Z37" s="33"/>
-      <c r="AA37" s="33"/>
-      <c r="AB37" s="33"/>
-      <c r="AC37" s="33"/>
-      <c r="AD37" s="33"/>
-      <c r="AE37" s="33"/>
-      <c r="AF37" s="33"/>
-      <c r="AG37" s="33"/>
-      <c r="AH37" s="33"/>
-      <c r="AI37" s="33"/>
-      <c r="AJ37" s="33"/>
-      <c r="AK37" s="33"/>
-      <c r="AL37" s="107"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="AH37" s="30"/>
+      <c r="AI37" s="30"/>
+      <c r="AJ37" s="30"/>
+      <c r="AK37" s="30"/>
+      <c r="AL37" s="75"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
-      <c r="AR37" s="45"/>
+      <c r="AR37" s="40"/>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
@@ -11290,50 +11246,50 @@
       <c r="ACM37"/>
     </row>
     <row r="38" spans="1:767" s="2" customFormat="1">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="33"/>
-      <c r="Y38" s="33"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="33"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
-      <c r="AD38" s="33"/>
-      <c r="AE38" s="33"/>
-      <c r="AF38" s="33"/>
-      <c r="AG38" s="33"/>
-      <c r="AH38" s="33"/>
-      <c r="AI38" s="33"/>
-      <c r="AJ38" s="33"/>
-      <c r="AK38" s="33"/>
-      <c r="AL38" s="107"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="30"/>
+      <c r="AH38" s="30"/>
+      <c r="AI38" s="30"/>
+      <c r="AJ38" s="30"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="75"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
-      <c r="AR38" s="45"/>
+      <c r="AR38" s="40"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
@@ -12059,50 +12015,50 @@
       <c r="ACM38"/>
     </row>
     <row r="39" spans="1:767" s="2" customFormat="1">
-      <c r="A39" s="33"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-      <c r="Z39" s="33"/>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
-      <c r="AE39" s="33"/>
-      <c r="AF39" s="33"/>
-      <c r="AG39" s="33"/>
-      <c r="AH39" s="33"/>
-      <c r="AI39" s="33"/>
-      <c r="AJ39" s="33"/>
-      <c r="AK39" s="33"/>
-      <c r="AL39" s="107"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="S39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AH39" s="30"/>
+      <c r="AI39" s="30"/>
+      <c r="AJ39" s="30"/>
+      <c r="AK39" s="30"/>
+      <c r="AL39" s="75"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
-      <c r="AR39" s="45"/>
+      <c r="AR39" s="40"/>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
@@ -12828,50 +12784,50 @@
       <c r="ACM39"/>
     </row>
     <row r="40" spans="1:767" s="2" customFormat="1">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="33"/>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="33"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
-      <c r="AD40" s="33"/>
-      <c r="AE40" s="33"/>
-      <c r="AF40" s="33"/>
-      <c r="AG40" s="33"/>
-      <c r="AH40" s="33"/>
-      <c r="AI40" s="33"/>
-      <c r="AJ40" s="33"/>
-      <c r="AK40" s="33"/>
-      <c r="AL40" s="107"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
+      <c r="AG40" s="30"/>
+      <c r="AH40" s="30"/>
+      <c r="AI40" s="30"/>
+      <c r="AJ40" s="30"/>
+      <c r="AK40" s="30"/>
+      <c r="AL40" s="75"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
-      <c r="AR40" s="45"/>
+      <c r="AR40" s="40"/>
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
@@ -13597,50 +13553,50 @@
       <c r="ACM40"/>
     </row>
     <row r="41" spans="1:767" s="2" customFormat="1">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="33"/>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-      <c r="Z41" s="33"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
-      <c r="AD41" s="33"/>
-      <c r="AE41" s="33"/>
-      <c r="AF41" s="33"/>
-      <c r="AG41" s="33"/>
-      <c r="AH41" s="33"/>
-      <c r="AI41" s="33"/>
-      <c r="AJ41" s="33"/>
-      <c r="AK41" s="33"/>
-      <c r="AL41" s="107"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="30"/>
+      <c r="R41" s="30"/>
+      <c r="S41" s="30"/>
+      <c r="T41" s="30"/>
+      <c r="U41" s="30"/>
+      <c r="V41" s="30"/>
+      <c r="W41" s="30"/>
+      <c r="X41" s="30"/>
+      <c r="Y41" s="30"/>
+      <c r="Z41" s="30"/>
+      <c r="AA41" s="30"/>
+      <c r="AB41" s="30"/>
+      <c r="AC41" s="30"/>
+      <c r="AD41" s="30"/>
+      <c r="AE41" s="30"/>
+      <c r="AF41" s="30"/>
+      <c r="AG41" s="30"/>
+      <c r="AH41" s="30"/>
+      <c r="AI41" s="30"/>
+      <c r="AJ41" s="30"/>
+      <c r="AK41" s="30"/>
+      <c r="AL41" s="75"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
-      <c r="AR41" s="45"/>
+      <c r="AR41" s="40"/>
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
@@ -14366,50 +14322,50 @@
       <c r="ACM41"/>
     </row>
     <row r="42" spans="1:767" s="2" customFormat="1">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
-      <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
-      <c r="AG42" s="33"/>
-      <c r="AH42" s="33"/>
-      <c r="AI42" s="33"/>
-      <c r="AJ42" s="33"/>
-      <c r="AK42" s="33"/>
-      <c r="AL42" s="107"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="30"/>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="30"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="30"/>
+      <c r="AF42" s="30"/>
+      <c r="AG42" s="30"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="30"/>
+      <c r="AJ42" s="30"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="75"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
-      <c r="AR42" s="45"/>
+      <c r="AR42" s="40"/>
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
@@ -15135,50 +15091,50 @@
       <c r="ACM42"/>
     </row>
     <row r="43" spans="1:767" s="2" customFormat="1">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="33"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="33"/>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-      <c r="Z43" s="33"/>
-      <c r="AA43" s="33"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="33"/>
-      <c r="AD43" s="33"/>
-      <c r="AE43" s="33"/>
-      <c r="AF43" s="33"/>
-      <c r="AG43" s="33"/>
-      <c r="AH43" s="33"/>
-      <c r="AI43" s="33"/>
-      <c r="AJ43" s="33"/>
-      <c r="AK43" s="33"/>
-      <c r="AL43" s="107"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
+      <c r="AG43" s="30"/>
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="75"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
-      <c r="AR43" s="45"/>
+      <c r="AR43" s="40"/>
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
@@ -15904,50 +15860,50 @@
       <c r="ACM43"/>
     </row>
     <row r="44" spans="1:767" s="2" customFormat="1">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="33"/>
-      <c r="Z44" s="33"/>
-      <c r="AA44" s="33"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
-      <c r="AD44" s="33"/>
-      <c r="AE44" s="33"/>
-      <c r="AF44" s="33"/>
-      <c r="AG44" s="33"/>
-      <c r="AH44" s="33"/>
-      <c r="AI44" s="33"/>
-      <c r="AJ44" s="33"/>
-      <c r="AK44" s="33"/>
-      <c r="AL44" s="107"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="30"/>
+      <c r="X44" s="30"/>
+      <c r="Y44" s="30"/>
+      <c r="Z44" s="30"/>
+      <c r="AA44" s="30"/>
+      <c r="AB44" s="30"/>
+      <c r="AC44" s="30"/>
+      <c r="AD44" s="30"/>
+      <c r="AE44" s="30"/>
+      <c r="AF44" s="30"/>
+      <c r="AG44" s="30"/>
+      <c r="AH44" s="30"/>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
+      <c r="AK44" s="30"/>
+      <c r="AL44" s="75"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
-      <c r="AR44" s="45"/>
+      <c r="AR44" s="40"/>
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
@@ -16673,50 +16629,50 @@
       <c r="ACM44"/>
     </row>
     <row r="45" spans="1:767" s="2" customFormat="1">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-      <c r="M45" s="33"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="33"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="33"/>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="33"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
-      <c r="AE45" s="33"/>
-      <c r="AF45" s="33"/>
-      <c r="AG45" s="33"/>
-      <c r="AH45" s="33"/>
-      <c r="AI45" s="33"/>
-      <c r="AJ45" s="33"/>
-      <c r="AK45" s="33"/>
-      <c r="AL45" s="107"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="30"/>
+      <c r="X45" s="30"/>
+      <c r="Y45" s="30"/>
+      <c r="Z45" s="30"/>
+      <c r="AA45" s="30"/>
+      <c r="AB45" s="30"/>
+      <c r="AC45" s="30"/>
+      <c r="AD45" s="30"/>
+      <c r="AE45" s="30"/>
+      <c r="AF45" s="30"/>
+      <c r="AG45" s="30"/>
+      <c r="AH45" s="30"/>
+      <c r="AI45" s="30"/>
+      <c r="AJ45" s="30"/>
+      <c r="AK45" s="30"/>
+      <c r="AL45" s="75"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
-      <c r="AR45" s="45"/>
+      <c r="AR45" s="40"/>
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
@@ -17442,50 +17398,50 @@
       <c r="ACM45"/>
     </row>
     <row r="46" spans="1:767" s="2" customFormat="1">
-      <c r="A46" s="33"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
-      <c r="V46" s="33"/>
-      <c r="W46" s="33"/>
-      <c r="X46" s="33"/>
-      <c r="Y46" s="33"/>
-      <c r="Z46" s="33"/>
-      <c r="AA46" s="33"/>
-      <c r="AB46" s="33"/>
-      <c r="AC46" s="33"/>
-      <c r="AD46" s="33"/>
-      <c r="AE46" s="33"/>
-      <c r="AF46" s="33"/>
-      <c r="AG46" s="33"/>
-      <c r="AH46" s="33"/>
-      <c r="AI46" s="33"/>
-      <c r="AJ46" s="33"/>
-      <c r="AK46" s="33"/>
-      <c r="AL46" s="107"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
+      <c r="AG46" s="30"/>
+      <c r="AH46" s="30"/>
+      <c r="AI46" s="30"/>
+      <c r="AJ46" s="30"/>
+      <c r="AK46" s="30"/>
+      <c r="AL46" s="75"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
-      <c r="AR46" s="45"/>
+      <c r="AR46" s="40"/>
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
@@ -18211,50 +18167,50 @@
       <c r="ACM46"/>
     </row>
     <row r="47" spans="1:767" s="2" customFormat="1">
-      <c r="A47" s="33"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="33"/>
-      <c r="Y47" s="33"/>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="33"/>
-      <c r="AB47" s="33"/>
-      <c r="AC47" s="33"/>
-      <c r="AD47" s="33"/>
-      <c r="AE47" s="33"/>
-      <c r="AF47" s="33"/>
-      <c r="AG47" s="33"/>
-      <c r="AH47" s="33"/>
-      <c r="AI47" s="33"/>
-      <c r="AJ47" s="33"/>
-      <c r="AK47" s="33"/>
-      <c r="AL47" s="107"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30"/>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="30"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
+      <c r="AH47" s="30"/>
+      <c r="AI47" s="30"/>
+      <c r="AJ47" s="30"/>
+      <c r="AK47" s="30"/>
+      <c r="AL47" s="75"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
-      <c r="AR47" s="45"/>
+      <c r="AR47" s="40"/>
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
@@ -18980,50 +18936,50 @@
       <c r="ACM47"/>
     </row>
     <row r="48" spans="1:767" s="2" customFormat="1">
-      <c r="A48" s="33"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
-      <c r="Y48" s="33"/>
-      <c r="Z48" s="33"/>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
-      <c r="AG48" s="33"/>
-      <c r="AH48" s="33"/>
-      <c r="AI48" s="33"/>
-      <c r="AJ48" s="33"/>
-      <c r="AK48" s="33"/>
-      <c r="AL48" s="107"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="30"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="30"/>
+      <c r="AI48" s="30"/>
+      <c r="AJ48" s="30"/>
+      <c r="AK48" s="30"/>
+      <c r="AL48" s="75"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
-      <c r="AR48" s="45"/>
+      <c r="AR48" s="40"/>
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
@@ -19749,50 +19705,50 @@
       <c r="ACM48"/>
     </row>
     <row r="49" spans="1:767" s="2" customFormat="1">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="33"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
-      <c r="Y49" s="33"/>
-      <c r="Z49" s="33"/>
-      <c r="AA49" s="33"/>
-      <c r="AB49" s="33"/>
-      <c r="AC49" s="33"/>
-      <c r="AD49" s="33"/>
-      <c r="AE49" s="33"/>
-      <c r="AF49" s="33"/>
-      <c r="AG49" s="33"/>
-      <c r="AH49" s="33"/>
-      <c r="AI49" s="33"/>
-      <c r="AJ49" s="33"/>
-      <c r="AK49" s="33"/>
-      <c r="AL49" s="107"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
+      <c r="AG49" s="30"/>
+      <c r="AH49" s="30"/>
+      <c r="AI49" s="30"/>
+      <c r="AJ49" s="30"/>
+      <c r="AK49" s="30"/>
+      <c r="AL49" s="75"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
-      <c r="AR49" s="45"/>
+      <c r="AR49" s="40"/>
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
@@ -20518,50 +20474,50 @@
       <c r="ACM49"/>
     </row>
     <row r="50" spans="1:767" s="2" customFormat="1">
-      <c r="A50" s="33"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33"/>
-      <c r="S50" s="33"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
-      <c r="Y50" s="33"/>
-      <c r="Z50" s="33"/>
-      <c r="AA50" s="33"/>
-      <c r="AB50" s="33"/>
-      <c r="AC50" s="33"/>
-      <c r="AD50" s="33"/>
-      <c r="AE50" s="33"/>
-      <c r="AF50" s="33"/>
-      <c r="AG50" s="33"/>
-      <c r="AH50" s="33"/>
-      <c r="AI50" s="33"/>
-      <c r="AJ50" s="33"/>
-      <c r="AK50" s="33"/>
-      <c r="AL50" s="107"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="S50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="30"/>
+      <c r="X50" s="30"/>
+      <c r="Y50" s="30"/>
+      <c r="Z50" s="30"/>
+      <c r="AA50" s="30"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+      <c r="AE50" s="30"/>
+      <c r="AF50" s="30"/>
+      <c r="AG50" s="30"/>
+      <c r="AH50" s="30"/>
+      <c r="AI50" s="30"/>
+      <c r="AJ50" s="30"/>
+      <c r="AK50" s="30"/>
+      <c r="AL50" s="75"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
       <c r="AO50" s="3"/>
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
-      <c r="AR50" s="45"/>
+      <c r="AR50" s="40"/>
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>

--- a/nurse_scheduler_template.xlsx
+++ b/nurse_scheduler_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DED0B17-88FF-40AA-8FD7-9860DA274524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D05FA16A-3CCF-479C-9982-CD938AD07CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B332721F-AB2B-4BF1-A12F-4722F279DAC4}"/>
   </bookViews>
@@ -726,21 +726,6 @@
       </diagonal>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -805,6 +790,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -824,7 +824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,47 +853,11 @@
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -914,27 +878,6 @@
     <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -950,7 +893,6 @@
     <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -965,14 +907,8 @@
     </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1001,31 +937,6 @@
     <xf numFmtId="176" fontId="22" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1038,6 +949,11 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1050,178 +966,8 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1283,124 +1029,318 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+      <alignment indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1723,13 +1663,13 @@
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.44140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="3.6640625" style="26" customWidth="1"/>
+    <col min="4" max="5" width="3.6640625" style="14" customWidth="1"/>
     <col min="6" max="13" width="3.6640625" style="3" customWidth="1"/>
-    <col min="14" max="17" width="3.6640625" style="26" customWidth="1"/>
+    <col min="14" max="17" width="3.6640625" style="14" customWidth="1"/>
     <col min="18" max="18" width="3.6640625" style="3" customWidth="1"/>
-    <col min="19" max="32" width="3.6640625" style="26" customWidth="1"/>
-    <col min="33" max="33" width="3.44140625" style="26" customWidth="1"/>
-    <col min="34" max="34" width="3.5546875" style="26" customWidth="1"/>
+    <col min="19" max="32" width="3.6640625" style="14" customWidth="1"/>
+    <col min="33" max="33" width="3.44140625" style="14" customWidth="1"/>
+    <col min="34" max="34" width="3.5546875" style="14" customWidth="1"/>
     <col min="35" max="35" width="3" style="3" customWidth="1"/>
     <col min="36" max="36" width="3" style="2" customWidth="1"/>
     <col min="37" max="37" width="4.5546875" style="2" customWidth="1"/>
@@ -1739,7 +1679,7 @@
     <col min="41" max="41" width="7.5546875" style="3" customWidth="1"/>
     <col min="42" max="42" width="6.88671875" style="3" customWidth="1"/>
     <col min="43" max="43" width="7.5546875" style="3" customWidth="1"/>
-    <col min="44" max="44" width="5.44140625" style="40" customWidth="1"/>
+    <col min="44" max="44" width="5.44140625" style="21" customWidth="1"/>
     <col min="45" max="765" width="7.5546875" style="3" customWidth="1"/>
     <col min="766" max="766" width="8.88671875" style="3" customWidth="1"/>
     <col min="767" max="767" width="8.88671875" customWidth="1"/>
@@ -1779,93 +1719,93 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
-      <c r="AI1" s="75"/>
-      <c r="AJ1" s="75"/>
-      <c r="AK1" s="75"/>
-      <c r="AL1" s="75"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
+      <c r="AI1" s="44"/>
+      <c r="AJ1" s="44"/>
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44"/>
+      <c r="AV1" s="31"/>
+      <c r="AW1" s="31"/>
     </row>
     <row r="2" spans="1:766" ht="49.5" customHeight="1">
-      <c r="B2" s="144" t="s">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
-      <c r="L2" s="145"/>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
-      <c r="U2" s="145"/>
-      <c r="V2" s="145"/>
-      <c r="W2" s="145"/>
-      <c r="X2" s="145"/>
-      <c r="Y2" s="145"/>
-      <c r="Z2" s="145"/>
-      <c r="AA2" s="145"/>
-      <c r="AB2" s="145"/>
-      <c r="AC2" s="145"/>
-      <c r="AD2" s="145"/>
-      <c r="AE2" s="145"/>
-      <c r="AF2" s="145"/>
-      <c r="AG2" s="145"/>
-      <c r="AH2" s="145"/>
-      <c r="AI2" s="145"/>
-      <c r="AJ2" s="145"/>
-      <c r="AK2" s="145"/>
-      <c r="AL2" s="145"/>
-      <c r="AM2" s="145"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="59"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="59"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="59"/>
+      <c r="AD2" s="59"/>
+      <c r="AE2" s="59"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="59"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
+      <c r="AM2" s="59"/>
     </row>
     <row r="3" spans="1:766" ht="6" customHeight="1" thickBot="1">
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
-      <c r="V3" s="79"/>
-      <c r="W3" s="79"/>
-      <c r="X3" s="79"/>
-      <c r="Y3" s="79"/>
-      <c r="Z3" s="79"/>
-      <c r="AA3" s="79"/>
-      <c r="AB3" s="79"/>
-      <c r="AC3" s="79"/>
-      <c r="AD3" s="79"/>
-      <c r="AE3" s="79"/>
-      <c r="AF3" s="79"/>
-      <c r="AG3" s="79"/>
-      <c r="AH3" s="79"/>
-      <c r="AI3" s="79"/>
-      <c r="AJ3" s="79"/>
-      <c r="AK3" s="79"/>
-      <c r="AL3" s="79"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="51"/>
     </row>
     <row r="4" spans="1:766" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="4"/>
@@ -1891,42 +1831,42 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
-      <c r="Z4" s="146"/>
-      <c r="AA4" s="146"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="60"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="147" t="s">
+      <c r="AD4" s="45"/>
+      <c r="AE4" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="AF4" s="148"/>
-      <c r="AG4" s="149" t="s">
+      <c r="AF4" s="62"/>
+      <c r="AG4" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="AH4" s="150"/>
-      <c r="AR4" s="40"/>
+      <c r="AH4" s="64"/>
+      <c r="AR4" s="21"/>
     </row>
     <row r="5" spans="1:766" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="153"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="67"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="154" t="s">
+      <c r="H5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="156"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="70"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1934,16 +1874,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Z5" s="146"/>
-      <c r="AA5" s="146"/>
-      <c r="AB5" s="146"/>
-      <c r="AC5" s="146"/>
-      <c r="AD5" s="80"/>
-      <c r="AE5" s="157"/>
-      <c r="AF5" s="158"/>
-      <c r="AG5" s="158"/>
-      <c r="AH5" s="159"/>
-      <c r="AR5" s="40" t="s">
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="60"/>
+      <c r="AB5" s="60"/>
+      <c r="AC5" s="60"/>
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="72"/>
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="73"/>
+      <c r="AR5" s="21" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1985,129 +1925,129 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
-      <c r="AK6" s="75"/>
-      <c r="AL6" s="75"/>
+      <c r="AK6" s="44"/>
+      <c r="AL6" s="44"/>
     </row>
     <row r="7" spans="1:766" s="9" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B7" s="140" t="s">
+      <c r="B7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="57">
+      <c r="C7" s="54"/>
+      <c r="D7" s="35">
         <v>1</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="35">
         <v>2</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="38">
         <v>3</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="38">
         <v>4</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="36">
         <v>5</v>
       </c>
-      <c r="I7" s="59">
+      <c r="I7" s="37">
         <v>6</v>
       </c>
-      <c r="J7" s="57">
+      <c r="J7" s="35">
         <v>7</v>
       </c>
-      <c r="K7" s="57">
+      <c r="K7" s="35">
         <v>8</v>
       </c>
-      <c r="L7" s="60">
+      <c r="L7" s="38">
         <v>9</v>
       </c>
-      <c r="M7" s="60">
+      <c r="M7" s="38">
         <v>10</v>
       </c>
-      <c r="N7" s="60">
+      <c r="N7" s="38">
         <v>11</v>
       </c>
-      <c r="O7" s="59">
+      <c r="O7" s="37">
         <v>12</v>
       </c>
-      <c r="P7" s="59">
+      <c r="P7" s="37">
         <v>13</v>
       </c>
-      <c r="Q7" s="57">
+      <c r="Q7" s="35">
         <v>14</v>
       </c>
-      <c r="R7" s="57">
+      <c r="R7" s="35">
         <v>15</v>
       </c>
-      <c r="S7" s="57">
+      <c r="S7" s="35">
         <v>16</v>
       </c>
-      <c r="T7" s="60">
+      <c r="T7" s="38">
         <v>17</v>
       </c>
-      <c r="U7" s="60">
+      <c r="U7" s="38">
         <v>18</v>
       </c>
-      <c r="V7" s="59">
+      <c r="V7" s="37">
         <v>19</v>
       </c>
-      <c r="W7" s="59">
+      <c r="W7" s="37">
         <v>20</v>
       </c>
-      <c r="X7" s="57">
+      <c r="X7" s="35">
         <v>21</v>
       </c>
-      <c r="Y7" s="57">
+      <c r="Y7" s="35">
         <v>22</v>
       </c>
-      <c r="Z7" s="57">
+      <c r="Z7" s="35">
         <v>23</v>
       </c>
-      <c r="AA7" s="56">
+      <c r="AA7" s="34">
         <v>24</v>
       </c>
-      <c r="AB7" s="56">
+      <c r="AB7" s="34">
         <v>25</v>
       </c>
-      <c r="AC7" s="59">
+      <c r="AC7" s="37">
         <v>26</v>
       </c>
-      <c r="AD7" s="59">
+      <c r="AD7" s="37">
         <v>27</v>
       </c>
-      <c r="AE7" s="57">
+      <c r="AE7" s="35">
         <v>28</v>
       </c>
-      <c r="AF7" s="57">
+      <c r="AF7" s="35">
         <v>29</v>
       </c>
-      <c r="AG7" s="57">
+      <c r="AG7" s="35">
         <v>30</v>
       </c>
-      <c r="AH7" s="60">
+      <c r="AH7" s="38">
         <v>31</v>
       </c>
-      <c r="AI7" s="77" t="s">
+      <c r="AI7" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AJ7" s="42" t="s">
+      <c r="AJ7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AK7" s="77" t="s">
+      <c r="AK7" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="AL7" s="43" t="s">
+      <c r="AL7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AM7" s="141" t="s">
+      <c r="AM7" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="AN7" s="142" t="s">
+      <c r="AN7" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="AO7" s="78"/>
-      <c r="AP7" s="41"/>
+      <c r="AO7" s="50"/>
+      <c r="AP7" s="22"/>
       <c r="AQ7" s="10"/>
-      <c r="AR7" s="41"/>
+      <c r="AR7" s="22"/>
       <c r="AS7" s="11"/>
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
@@ -2826,117 +2766,117 @@
       <c r="ACF7" s="11"/>
     </row>
     <row r="8" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="143"/>
-      <c r="D8" s="57" t="s">
+      <c r="C8" s="57"/>
+      <c r="D8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="E8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="59" t="s">
+      <c r="I8" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="57" t="s">
+      <c r="J8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="57" t="s">
+      <c r="K8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="60" t="s">
+      <c r="L8" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="60" t="s">
+      <c r="M8" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="60" t="s">
+      <c r="N8" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="59" t="s">
+      <c r="O8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="59" t="s">
+      <c r="P8" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="57" t="s">
+      <c r="Q8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="57" t="s">
+      <c r="R8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="57" t="s">
+      <c r="S8" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="60" t="s">
+      <c r="T8" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="60" t="s">
+      <c r="U8" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="59" t="s">
+      <c r="V8" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="59" t="s">
+      <c r="W8" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="57" t="s">
+      <c r="X8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="61" t="s">
+      <c r="Y8" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="61" t="s">
+      <c r="Z8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="56" t="s">
+      <c r="AA8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" s="63" t="s">
+      <c r="AB8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="59" t="s">
+      <c r="AC8" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="AD8" s="59" t="s">
+      <c r="AD8" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AE8" s="62" t="s">
+      <c r="AE8" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="57" t="s">
+      <c r="AF8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="AG8" s="57" t="s">
+      <c r="AG8" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="56" t="s">
+      <c r="AH8" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="AI8" s="77"/>
-      <c r="AJ8" s="77"/>
-      <c r="AK8" s="77"/>
-      <c r="AL8" s="44"/>
-      <c r="AM8" s="141"/>
-      <c r="AN8" s="142"/>
-      <c r="AO8" s="78"/>
-      <c r="AP8" s="50" t="s">
+      <c r="AI8" s="49"/>
+      <c r="AJ8" s="49"/>
+      <c r="AK8" s="49"/>
+      <c r="AL8" s="25"/>
+      <c r="AM8" s="55"/>
+      <c r="AN8" s="56"/>
+      <c r="AO8" s="50"/>
+      <c r="AP8" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="AQ8" s="41" t="s">
+      <c r="AQ8" s="22" t="s">
         <v>29</v>
       </c>
       <c r="AR8" s="10" t="s">
@@ -3659,52 +3599,52 @@
       <c r="ACF8" s="11"/>
     </row>
     <row r="9" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="48">
+      <c r="A9" s="28">
         <v>1</v>
       </c>
-      <c r="B9" s="161"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="104"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="104"/>
-      <c r="O9" s="81"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="91"/>
-      <c r="U9" s="91"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="98"/>
-      <c r="AB9" s="98"/>
-      <c r="AC9" s="81"/>
-      <c r="AD9" s="81"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="16"/>
-      <c r="AH9" s="65"/>
-      <c r="AI9" s="18"/>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="43"/>
-      <c r="AM9" s="162"/>
-      <c r="AN9" s="163"/>
-      <c r="AO9" s="163"/>
-      <c r="AP9" s="164"/>
-      <c r="AQ9" s="45"/>
-      <c r="AR9" s="164"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="12"/>
+      <c r="Y9" s="79"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="80"/>
+      <c r="AB9" s="80"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="81"/>
+      <c r="AF9" s="79"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="82"/>
+      <c r="AI9" s="83"/>
+      <c r="AJ9" s="83"/>
+      <c r="AK9" s="84"/>
+      <c r="AL9" s="85"/>
+      <c r="AM9" s="86"/>
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="88"/>
+      <c r="AQ9" s="88"/>
+      <c r="AR9" s="88"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
@@ -4421,52 +4361,52 @@
       <c r="ACD9" s="11"/>
     </row>
     <row r="10" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="28">
         <v>2</v>
       </c>
-      <c r="B10" s="161"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="81"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="91"/>
-      <c r="U10" s="91"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="81"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="91"/>
-      <c r="AB10" s="98"/>
-      <c r="AC10" s="81"/>
-      <c r="AD10" s="81"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="38"/>
-      <c r="AG10" s="16"/>
-      <c r="AH10" s="64"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="43"/>
-      <c r="AM10" s="162"/>
-      <c r="AN10" s="163"/>
-      <c r="AO10" s="163"/>
-      <c r="AP10" s="164"/>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="164"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="76"/>
+      <c r="S10" s="76"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="76"/>
+      <c r="W10" s="76"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="79"/>
+      <c r="Z10" s="76"/>
+      <c r="AA10" s="47"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="76"/>
+      <c r="AD10" s="76"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="79"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="91"/>
+      <c r="AI10" s="83"/>
+      <c r="AJ10" s="83"/>
+      <c r="AK10" s="84"/>
+      <c r="AL10" s="85"/>
+      <c r="AM10" s="86"/>
+      <c r="AN10" s="87"/>
+      <c r="AO10" s="87"/>
+      <c r="AP10" s="88"/>
+      <c r="AQ10" s="88"/>
+      <c r="AR10" s="88"/>
       <c r="AS10" s="11"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
@@ -5183,52 +5123,52 @@
       <c r="ACD10" s="11"/>
     </row>
     <row r="11" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="28">
         <v>3</v>
       </c>
-      <c r="B11" s="161"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="91"/>
-      <c r="U11" s="91"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="92"/>
-      <c r="AB11" s="98"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="64"/>
-      <c r="AI11" s="18"/>
-      <c r="AJ11" s="18"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="162"/>
-      <c r="AM11" s="162"/>
-      <c r="AN11" s="163"/>
-      <c r="AO11" s="163"/>
-      <c r="AP11" s="164"/>
-      <c r="AQ11" s="45"/>
-      <c r="AR11" s="164"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="78"/>
+      <c r="L11" s="92"/>
+      <c r="M11" s="92"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="76"/>
+      <c r="W11" s="76"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="76"/>
+      <c r="Z11" s="76"/>
+      <c r="AA11" s="89"/>
+      <c r="AB11" s="80"/>
+      <c r="AC11" s="76"/>
+      <c r="AD11" s="76"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="91"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="84"/>
+      <c r="AL11" s="86"/>
+      <c r="AM11" s="86"/>
+      <c r="AN11" s="87"/>
+      <c r="AO11" s="87"/>
+      <c r="AP11" s="88"/>
+      <c r="AQ11" s="88"/>
+      <c r="AR11" s="88"/>
       <c r="AS11" s="11"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
@@ -5945,52 +5885,52 @@
       <c r="ACD11" s="11"/>
     </row>
     <row r="12" spans="1:766" ht="24" customHeight="1">
-      <c r="A12" s="48">
+      <c r="A12" s="28">
         <v>4</v>
       </c>
-      <c r="B12" s="161"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
-      <c r="V12" s="81"/>
-      <c r="W12" s="81"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="92"/>
-      <c r="AB12" s="90"/>
-      <c r="AC12" s="81"/>
-      <c r="AD12" s="81"/>
-      <c r="AE12" s="34"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="23"/>
-      <c r="AH12" s="66"/>
-      <c r="AI12" s="18"/>
-      <c r="AJ12" s="18"/>
-      <c r="AK12" s="165"/>
-      <c r="AL12" s="163"/>
-      <c r="AM12" s="165"/>
-      <c r="AN12" s="163"/>
-      <c r="AO12" s="163"/>
-      <c r="AP12" s="164"/>
-      <c r="AQ12" s="45"/>
-      <c r="AR12" s="164"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="89"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="76"/>
+      <c r="S12" s="76"/>
+      <c r="T12" s="89"/>
+      <c r="U12" s="89"/>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76"/>
+      <c r="X12" s="76"/>
+      <c r="Y12" s="76"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="89"/>
+      <c r="AB12" s="94"/>
+      <c r="AC12" s="76"/>
+      <c r="AD12" s="76"/>
+      <c r="AE12" s="95"/>
+      <c r="AF12" s="76"/>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="96"/>
+      <c r="AI12" s="83"/>
+      <c r="AJ12" s="83"/>
+      <c r="AK12" s="97"/>
+      <c r="AL12" s="87"/>
+      <c r="AM12" s="97"/>
+      <c r="AN12" s="87"/>
+      <c r="AO12" s="87"/>
+      <c r="AP12" s="88"/>
+      <c r="AQ12" s="88"/>
+      <c r="AR12" s="88"/>
       <c r="ACE12"/>
       <c r="ACF12"/>
       <c r="ACG12"/>
@@ -6001,52 +5941,52 @@
       <c r="ACL12"/>
     </row>
     <row r="13" spans="1:766" ht="24" customHeight="1">
-      <c r="A13" s="48">
+      <c r="A13" s="28">
         <v>5</v>
       </c>
-      <c r="B13" s="161"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="93"/>
-      <c r="V13" s="81"/>
-      <c r="W13" s="81"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="92"/>
-      <c r="AB13" s="90"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="34"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="66"/>
-      <c r="AI13" s="18"/>
-      <c r="AJ13" s="18"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="162"/>
-      <c r="AM13" s="162"/>
-      <c r="AN13" s="163"/>
-      <c r="AO13" s="163"/>
-      <c r="AP13" s="164"/>
-      <c r="AQ13" s="45"/>
-      <c r="AR13" s="164"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="76"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="89"/>
+      <c r="M13" s="89"/>
+      <c r="N13" s="89"/>
+      <c r="O13" s="76"/>
+      <c r="P13" s="76"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="89"/>
+      <c r="U13" s="184"/>
+      <c r="V13" s="76"/>
+      <c r="W13" s="76"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="76"/>
+      <c r="Z13" s="76"/>
+      <c r="AA13" s="89"/>
+      <c r="AB13" s="94"/>
+      <c r="AC13" s="76"/>
+      <c r="AD13" s="76"/>
+      <c r="AE13" s="95"/>
+      <c r="AF13" s="76"/>
+      <c r="AG13" s="76"/>
+      <c r="AH13" s="96"/>
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="83"/>
+      <c r="AK13" s="84"/>
+      <c r="AL13" s="86"/>
+      <c r="AM13" s="86"/>
+      <c r="AN13" s="87"/>
+      <c r="AO13" s="87"/>
+      <c r="AP13" s="88"/>
+      <c r="AQ13" s="88"/>
+      <c r="AR13" s="88"/>
       <c r="ACE13"/>
       <c r="ACF13"/>
       <c r="ACG13"/>
@@ -6057,52 +5997,52 @@
       <c r="ACL13"/>
     </row>
     <row r="14" spans="1:766" ht="24" customHeight="1">
-      <c r="A14" s="48">
+      <c r="A14" s="28">
         <v>6</v>
       </c>
-      <c r="B14" s="161"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="92"/>
-      <c r="M14" s="92"/>
-      <c r="N14" s="92"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="92"/>
-      <c r="U14" s="92"/>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="92"/>
-      <c r="AB14" s="166"/>
-      <c r="AC14" s="84"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="66"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="18"/>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="162"/>
-      <c r="AM14" s="165"/>
-      <c r="AN14" s="163"/>
-      <c r="AO14" s="163"/>
-      <c r="AP14" s="164"/>
-      <c r="AQ14" s="45"/>
-      <c r="AR14" s="164"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="89"/>
+      <c r="N14" s="89"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="76"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="76"/>
+      <c r="T14" s="89"/>
+      <c r="U14" s="147"/>
+      <c r="V14" s="76"/>
+      <c r="W14" s="76"/>
+      <c r="X14" s="76"/>
+      <c r="Y14" s="76"/>
+      <c r="Z14" s="76"/>
+      <c r="AA14" s="89"/>
+      <c r="AB14" s="98"/>
+      <c r="AC14" s="78"/>
+      <c r="AD14" s="76"/>
+      <c r="AE14" s="95"/>
+      <c r="AF14" s="76"/>
+      <c r="AG14" s="76"/>
+      <c r="AH14" s="96"/>
+      <c r="AI14" s="83"/>
+      <c r="AJ14" s="83"/>
+      <c r="AK14" s="83"/>
+      <c r="AL14" s="86"/>
+      <c r="AM14" s="97"/>
+      <c r="AN14" s="87"/>
+      <c r="AO14" s="87"/>
+      <c r="AP14" s="88"/>
+      <c r="AQ14" s="88"/>
+      <c r="AR14" s="88"/>
       <c r="ACE14"/>
       <c r="ACF14"/>
       <c r="ACG14"/>
@@ -6113,52 +6053,52 @@
       <c r="ACL14"/>
     </row>
     <row r="15" spans="1:766" ht="24" customHeight="1">
-      <c r="A15" s="48">
+      <c r="A15" s="28">
         <v>7</v>
       </c>
-      <c r="B15" s="161"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="168"/>
-      <c r="J15" s="167"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="92"/>
-      <c r="N15" s="92"/>
-      <c r="O15" s="168"/>
-      <c r="P15" s="168"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="92"/>
-      <c r="U15" s="94"/>
-      <c r="V15" s="81"/>
-      <c r="W15" s="81"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="92"/>
-      <c r="AB15" s="90"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="23"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="67"/>
-      <c r="AI15" s="18"/>
-      <c r="AJ15" s="18"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="162"/>
-      <c r="AM15" s="162"/>
-      <c r="AN15" s="163"/>
-      <c r="AO15" s="163"/>
-      <c r="AP15" s="164"/>
-      <c r="AQ15" s="45"/>
-      <c r="AR15" s="164"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="100"/>
+      <c r="P15" s="100"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="76"/>
+      <c r="S15" s="76"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="101"/>
+      <c r="V15" s="76"/>
+      <c r="W15" s="76"/>
+      <c r="X15" s="76"/>
+      <c r="Y15" s="76"/>
+      <c r="Z15" s="76"/>
+      <c r="AA15" s="89"/>
+      <c r="AB15" s="94"/>
+      <c r="AC15" s="76"/>
+      <c r="AD15" s="76"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="76"/>
+      <c r="AH15" s="102"/>
+      <c r="AI15" s="83"/>
+      <c r="AJ15" s="83"/>
+      <c r="AK15" s="84"/>
+      <c r="AL15" s="86"/>
+      <c r="AM15" s="86"/>
+      <c r="AN15" s="87"/>
+      <c r="AO15" s="87"/>
+      <c r="AP15" s="88"/>
+      <c r="AQ15" s="88"/>
+      <c r="AR15" s="88"/>
       <c r="ACE15"/>
       <c r="ACF15"/>
       <c r="ACG15"/>
@@ -6169,52 +6109,52 @@
       <c r="ACL15"/>
     </row>
     <row r="16" spans="1:766" ht="24" customHeight="1">
-      <c r="A16" s="48">
+      <c r="A16" s="28">
         <v>8</v>
       </c>
-      <c r="B16" s="161"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="92"/>
-      <c r="M16" s="92"/>
-      <c r="N16" s="92"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="81"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="91"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="81"/>
-      <c r="W16" s="81"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="91"/>
-      <c r="AB16" s="90"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="55"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="67"/>
-      <c r="AI16" s="18"/>
-      <c r="AJ16" s="18"/>
-      <c r="AK16" s="169"/>
-      <c r="AL16" s="162"/>
-      <c r="AM16" s="162"/>
-      <c r="AN16" s="163"/>
-      <c r="AO16" s="163"/>
-      <c r="AP16" s="164"/>
-      <c r="AQ16" s="45"/>
-      <c r="AR16" s="164"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="89"/>
+      <c r="M16" s="89"/>
+      <c r="N16" s="89"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="101"/>
+      <c r="V16" s="76"/>
+      <c r="W16" s="76"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="47"/>
+      <c r="AB16" s="94"/>
+      <c r="AC16" s="76"/>
+      <c r="AD16" s="76"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="13"/>
+      <c r="AG16" s="13"/>
+      <c r="AH16" s="102"/>
+      <c r="AI16" s="83"/>
+      <c r="AJ16" s="83"/>
+      <c r="AK16" s="103"/>
+      <c r="AL16" s="86"/>
+      <c r="AM16" s="86"/>
+      <c r="AN16" s="87"/>
+      <c r="AO16" s="87"/>
+      <c r="AP16" s="88"/>
+      <c r="AQ16" s="88"/>
+      <c r="AR16" s="88"/>
       <c r="ACE16"/>
       <c r="ACF16"/>
       <c r="ACG16"/>
@@ -6225,52 +6165,52 @@
       <c r="ACL16"/>
     </row>
     <row r="17" spans="1:766" ht="24" customHeight="1">
-      <c r="A17" s="48">
+      <c r="A17" s="28">
         <v>1</v>
       </c>
-      <c r="B17" s="161"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="92"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="81"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="92"/>
-      <c r="U17" s="92"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="81"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="82"/>
-      <c r="Z17" s="83"/>
-      <c r="AA17" s="92"/>
-      <c r="AB17" s="90"/>
-      <c r="AC17" s="81"/>
-      <c r="AD17" s="81"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="23"/>
-      <c r="AH17" s="67"/>
-      <c r="AI17" s="18"/>
-      <c r="AJ17" s="18"/>
-      <c r="AK17" s="37"/>
-      <c r="AL17" s="162"/>
-      <c r="AM17" s="162"/>
-      <c r="AN17" s="163"/>
-      <c r="AO17" s="163"/>
-      <c r="AP17" s="164"/>
-      <c r="AQ17" s="45"/>
-      <c r="AR17" s="164"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="104"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="76"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="47"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="89"/>
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="76"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="89"/>
+      <c r="U17" s="89"/>
+      <c r="V17" s="76"/>
+      <c r="W17" s="76"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="78"/>
+      <c r="Z17" s="105"/>
+      <c r="AA17" s="89"/>
+      <c r="AB17" s="94"/>
+      <c r="AC17" s="76"/>
+      <c r="AD17" s="76"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="13"/>
+      <c r="AH17" s="102"/>
+      <c r="AI17" s="83"/>
+      <c r="AJ17" s="83"/>
+      <c r="AK17" s="84"/>
+      <c r="AL17" s="86"/>
+      <c r="AM17" s="86"/>
+      <c r="AN17" s="87"/>
+      <c r="AO17" s="87"/>
+      <c r="AP17" s="88"/>
+      <c r="AQ17" s="88"/>
+      <c r="AR17" s="88"/>
       <c r="ACE17"/>
       <c r="ACF17"/>
       <c r="ACG17"/>
@@ -6281,52 +6221,52 @@
       <c r="ACL17"/>
     </row>
     <row r="18" spans="1:766" ht="24" customHeight="1">
-      <c r="A18" s="48">
+      <c r="A18" s="28">
         <v>1</v>
       </c>
-      <c r="B18" s="171"/>
-      <c r="C18" s="172"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="106"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="126"/>
-      <c r="P18" s="126"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="128"/>
-      <c r="U18" s="128"/>
-      <c r="V18" s="129"/>
-      <c r="W18" s="126"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="106"/>
-      <c r="AB18" s="130"/>
-      <c r="AC18" s="126"/>
-      <c r="AD18" s="126"/>
-      <c r="AE18" s="71"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="25"/>
-      <c r="AJ18" s="25"/>
-      <c r="AK18" s="25"/>
-      <c r="AL18" s="173"/>
-      <c r="AM18" s="173"/>
-      <c r="AN18" s="174"/>
-      <c r="AO18" s="174"/>
-      <c r="AP18" s="175"/>
-      <c r="AQ18" s="176"/>
-      <c r="AR18" s="175"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="107"/>
+      <c r="P18" s="107"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
+      <c r="S18" s="111"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="107"/>
+      <c r="X18" s="107"/>
+      <c r="Y18" s="107"/>
+      <c r="Z18" s="107"/>
+      <c r="AA18" s="108"/>
+      <c r="AB18" s="113"/>
+      <c r="AC18" s="107"/>
+      <c r="AD18" s="107"/>
+      <c r="AE18" s="114"/>
+      <c r="AF18" s="107"/>
+      <c r="AG18" s="107"/>
+      <c r="AH18" s="115"/>
+      <c r="AI18" s="116"/>
+      <c r="AJ18" s="116"/>
+      <c r="AK18" s="116"/>
+      <c r="AL18" s="117"/>
+      <c r="AM18" s="117"/>
+      <c r="AN18" s="118"/>
+      <c r="AO18" s="118"/>
+      <c r="AP18" s="119"/>
+      <c r="AQ18" s="119"/>
+      <c r="AR18" s="119"/>
       <c r="ACE18"/>
       <c r="ACF18"/>
       <c r="ACG18"/>
@@ -6337,52 +6277,52 @@
       <c r="ACL18"/>
     </row>
     <row r="19" spans="1:766" ht="24" customHeight="1">
-      <c r="A19" s="48">
+      <c r="A19" s="28">
         <v>2</v>
       </c>
-      <c r="B19" s="177"/>
-      <c r="C19" s="178"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="117"/>
-      <c r="P19" s="117"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="111"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="117"/>
-      <c r="W19" s="117"/>
-      <c r="X19" s="111"/>
-      <c r="Y19" s="111"/>
-      <c r="Z19" s="118"/>
-      <c r="AA19" s="119"/>
-      <c r="AB19" s="120"/>
-      <c r="AC19" s="121"/>
-      <c r="AD19" s="117"/>
-      <c r="AE19" s="122"/>
-      <c r="AF19" s="111"/>
-      <c r="AG19" s="111"/>
-      <c r="AH19" s="123"/>
-      <c r="AI19" s="124"/>
-      <c r="AJ19" s="124"/>
-      <c r="AK19" s="124"/>
-      <c r="AL19" s="179"/>
-      <c r="AM19" s="179"/>
-      <c r="AN19" s="180"/>
-      <c r="AO19" s="180"/>
-      <c r="AP19" s="181"/>
-      <c r="AQ19" s="182"/>
-      <c r="AR19" s="181"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="125"/>
+      <c r="K19" s="122"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="122"/>
+      <c r="P19" s="122"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="125"/>
+      <c r="S19" s="122"/>
+      <c r="T19" s="123"/>
+      <c r="U19" s="123"/>
+      <c r="V19" s="122"/>
+      <c r="W19" s="122"/>
+      <c r="X19" s="122"/>
+      <c r="Y19" s="122"/>
+      <c r="Z19" s="127"/>
+      <c r="AA19" s="128"/>
+      <c r="AB19" s="129"/>
+      <c r="AC19" s="127"/>
+      <c r="AD19" s="122"/>
+      <c r="AE19" s="130"/>
+      <c r="AF19" s="122"/>
+      <c r="AG19" s="122"/>
+      <c r="AH19" s="131"/>
+      <c r="AI19" s="132"/>
+      <c r="AJ19" s="132"/>
+      <c r="AK19" s="132"/>
+      <c r="AL19" s="133"/>
+      <c r="AM19" s="133"/>
+      <c r="AN19" s="134"/>
+      <c r="AO19" s="134"/>
+      <c r="AP19" s="135"/>
+      <c r="AQ19" s="135"/>
+      <c r="AR19" s="135"/>
       <c r="ACE19"/>
       <c r="ACF19"/>
       <c r="ACG19"/>
@@ -6393,52 +6333,52 @@
       <c r="ACL19"/>
     </row>
     <row r="20" spans="1:766" ht="24" customHeight="1">
-      <c r="A20" s="48">
+      <c r="A20" s="28">
         <v>1</v>
       </c>
-      <c r="B20" s="183"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="133"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="109"/>
-      <c r="M20" s="109"/>
-      <c r="N20" s="135"/>
-      <c r="O20" s="134"/>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="12"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="136"/>
-      <c r="U20" s="99"/>
-      <c r="V20" s="134"/>
-      <c r="W20" s="134"/>
-      <c r="X20" s="12"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="12"/>
-      <c r="AA20" s="99"/>
-      <c r="AB20" s="100"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="134"/>
-      <c r="AE20" s="33"/>
-      <c r="AF20" s="89"/>
-      <c r="AG20" s="89"/>
-      <c r="AH20" s="137"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="185"/>
-      <c r="AM20" s="186"/>
-      <c r="AN20" s="187"/>
-      <c r="AO20" s="187"/>
-      <c r="AP20" s="188"/>
-      <c r="AQ20" s="189"/>
-      <c r="AR20" s="190"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="143"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="140"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="141"/>
+      <c r="T20" s="146"/>
+      <c r="U20" s="147"/>
+      <c r="V20" s="141"/>
+      <c r="W20" s="141"/>
+      <c r="X20" s="141"/>
+      <c r="Y20" s="145"/>
+      <c r="Z20" s="141"/>
+      <c r="AA20" s="147"/>
+      <c r="AB20" s="148"/>
+      <c r="AC20" s="141"/>
+      <c r="AD20" s="141"/>
+      <c r="AE20" s="149"/>
+      <c r="AF20" s="150"/>
+      <c r="AG20" s="150"/>
+      <c r="AH20" s="151"/>
+      <c r="AI20" s="152"/>
+      <c r="AJ20" s="152"/>
+      <c r="AK20" s="152"/>
+      <c r="AL20" s="153"/>
+      <c r="AM20" s="154"/>
+      <c r="AN20" s="155"/>
+      <c r="AO20" s="155"/>
+      <c r="AP20" s="156"/>
+      <c r="AQ20" s="156"/>
+      <c r="AR20" s="157"/>
       <c r="ACF20"/>
       <c r="ACG20"/>
       <c r="ACH20"/>
@@ -6448,52 +6388,52 @@
       <c r="ACL20"/>
     </row>
     <row r="21" spans="1:766" ht="24" customHeight="1">
-      <c r="A21" s="48">
+      <c r="A21" s="28">
         <v>2</v>
       </c>
-      <c r="B21" s="171"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="91"/>
-      <c r="U21" s="92"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="81"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="99"/>
-      <c r="AB21" s="100"/>
-      <c r="AC21" s="81"/>
-      <c r="AD21" s="81"/>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="18"/>
-      <c r="AJ21" s="18"/>
-      <c r="AK21" s="25"/>
-      <c r="AL21" s="162"/>
-      <c r="AM21" s="173"/>
-      <c r="AN21" s="191"/>
-      <c r="AO21" s="191"/>
-      <c r="AP21" s="175"/>
-      <c r="AQ21" s="45"/>
-      <c r="AR21" s="175"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="89"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="76"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="76"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="76"/>
+      <c r="W21" s="76"/>
+      <c r="X21" s="76"/>
+      <c r="Y21" s="141"/>
+      <c r="Z21" s="76"/>
+      <c r="AA21" s="147"/>
+      <c r="AB21" s="148"/>
+      <c r="AC21" s="76"/>
+      <c r="AD21" s="76"/>
+      <c r="AE21" s="149"/>
+      <c r="AF21" s="141"/>
+      <c r="AG21" s="158"/>
+      <c r="AH21" s="159"/>
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="116"/>
+      <c r="AL21" s="86"/>
+      <c r="AM21" s="117"/>
+      <c r="AN21" s="160"/>
+      <c r="AO21" s="160"/>
+      <c r="AP21" s="119"/>
+      <c r="AQ21" s="88"/>
+      <c r="AR21" s="119"/>
       <c r="ACF21"/>
       <c r="ACG21"/>
       <c r="ACH21"/>
@@ -6503,52 +6443,52 @@
       <c r="ACL21"/>
     </row>
     <row r="22" spans="1:766" ht="24" customHeight="1">
-      <c r="A22" s="48">
+      <c r="A22" s="28">
         <v>3</v>
       </c>
-      <c r="B22" s="192"/>
-      <c r="C22" s="193"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="110"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="106"/>
-      <c r="N22" s="106"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="96"/>
-      <c r="U22" s="96"/>
-      <c r="V22" s="85"/>
-      <c r="W22" s="85"/>
-      <c r="X22" s="86"/>
-      <c r="Y22" s="87"/>
-      <c r="Z22" s="86"/>
-      <c r="AA22" s="101"/>
-      <c r="AB22" s="102"/>
-      <c r="AC22" s="85"/>
-      <c r="AD22" s="84"/>
-      <c r="AE22" s="88"/>
-      <c r="AF22" s="89"/>
-      <c r="AG22" s="13"/>
-      <c r="AH22" s="65"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="139"/>
-      <c r="AK22" s="138"/>
-      <c r="AL22" s="194"/>
-      <c r="AM22" s="195"/>
-      <c r="AN22" s="196"/>
-      <c r="AO22" s="196"/>
-      <c r="AP22" s="197"/>
-      <c r="AQ22" s="198"/>
-      <c r="AR22" s="164"/>
+      <c r="B22" s="161"/>
+      <c r="C22" s="162"/>
+      <c r="D22" s="163"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="164"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="108"/>
+      <c r="N22" s="108"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="76"/>
+      <c r="Q22" s="107"/>
+      <c r="R22" s="110"/>
+      <c r="S22" s="107"/>
+      <c r="T22" s="166"/>
+      <c r="U22" s="166"/>
+      <c r="V22" s="167"/>
+      <c r="W22" s="167"/>
+      <c r="X22" s="167"/>
+      <c r="Y22" s="168"/>
+      <c r="Z22" s="167"/>
+      <c r="AA22" s="169"/>
+      <c r="AB22" s="170"/>
+      <c r="AC22" s="167"/>
+      <c r="AD22" s="78"/>
+      <c r="AE22" s="171"/>
+      <c r="AF22" s="150"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="82"/>
+      <c r="AI22" s="152"/>
+      <c r="AJ22" s="172"/>
+      <c r="AK22" s="173"/>
+      <c r="AL22" s="174"/>
+      <c r="AM22" s="175"/>
+      <c r="AN22" s="176"/>
+      <c r="AO22" s="176"/>
+      <c r="AP22" s="177"/>
+      <c r="AQ22" s="178"/>
+      <c r="AR22" s="88"/>
       <c r="ACF22"/>
       <c r="ACG22"/>
       <c r="ACH22"/>
@@ -6558,52 +6498,52 @@
       <c r="ACL22"/>
     </row>
     <row r="23" spans="1:766" ht="24" customHeight="1">
-      <c r="A23" s="48">
+      <c r="A23" s="28">
         <v>4</v>
       </c>
-      <c r="B23" s="183"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="95"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="95"/>
-      <c r="U23" s="95"/>
-      <c r="V23" s="81"/>
-      <c r="W23" s="81"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="92"/>
-      <c r="AB23" s="90"/>
-      <c r="AC23" s="81"/>
-      <c r="AD23" s="81"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="16"/>
-      <c r="AG23" s="16"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="19"/>
-      <c r="AK23" s="52"/>
-      <c r="AL23" s="199"/>
-      <c r="AM23" s="199"/>
-      <c r="AN23" s="187"/>
-      <c r="AO23" s="187"/>
-      <c r="AP23" s="188"/>
-      <c r="AQ23" s="200"/>
-      <c r="AR23" s="164"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="76"/>
+      <c r="Q23" s="76"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="76"/>
+      <c r="T23" s="93"/>
+      <c r="U23" s="93"/>
+      <c r="V23" s="76"/>
+      <c r="W23" s="76"/>
+      <c r="X23" s="76"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="76"/>
+      <c r="AA23" s="89"/>
+      <c r="AB23" s="94"/>
+      <c r="AC23" s="76"/>
+      <c r="AD23" s="76"/>
+      <c r="AE23" s="95"/>
+      <c r="AF23" s="76"/>
+      <c r="AG23" s="76"/>
+      <c r="AH23" s="91"/>
+      <c r="AI23" s="152"/>
+      <c r="AJ23" s="152"/>
+      <c r="AK23" s="179"/>
+      <c r="AL23" s="180"/>
+      <c r="AM23" s="180"/>
+      <c r="AN23" s="155"/>
+      <c r="AO23" s="155"/>
+      <c r="AP23" s="156"/>
+      <c r="AQ23" s="156"/>
+      <c r="AR23" s="88"/>
       <c r="ACF23"/>
       <c r="ACG23"/>
       <c r="ACH23"/>
@@ -6613,52 +6553,52 @@
       <c r="ACL23"/>
     </row>
     <row r="24" spans="1:766" ht="24" customHeight="1">
-      <c r="A24" s="48">
+      <c r="A24" s="28">
         <v>5</v>
       </c>
-      <c r="B24" s="161"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="91"/>
-      <c r="U24" s="92"/>
-      <c r="V24" s="81"/>
-      <c r="W24" s="81"/>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="12"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="99"/>
-      <c r="AB24" s="100"/>
-      <c r="AC24" s="81"/>
-      <c r="AD24" s="81"/>
-      <c r="AE24" s="34"/>
-      <c r="AF24" s="12"/>
-      <c r="AG24" s="12"/>
-      <c r="AH24" s="66"/>
-      <c r="AI24" s="18"/>
-      <c r="AJ24" s="18"/>
-      <c r="AK24" s="37"/>
-      <c r="AL24" s="162"/>
-      <c r="AM24" s="162"/>
-      <c r="AN24" s="163"/>
-      <c r="AO24" s="163"/>
-      <c r="AP24" s="164"/>
-      <c r="AQ24" s="45"/>
-      <c r="AR24" s="164"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="163"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
+      <c r="S24" s="76"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="76"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="141"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="147"/>
+      <c r="AB24" s="148"/>
+      <c r="AC24" s="76"/>
+      <c r="AD24" s="76"/>
+      <c r="AE24" s="95"/>
+      <c r="AF24" s="141"/>
+      <c r="AG24" s="141"/>
+      <c r="AH24" s="96"/>
+      <c r="AI24" s="83"/>
+      <c r="AJ24" s="83"/>
+      <c r="AK24" s="84"/>
+      <c r="AL24" s="86"/>
+      <c r="AM24" s="86"/>
+      <c r="AN24" s="87"/>
+      <c r="AO24" s="87"/>
+      <c r="AP24" s="88"/>
+      <c r="AQ24" s="88"/>
+      <c r="AR24" s="88"/>
       <c r="ACF24"/>
       <c r="ACG24"/>
       <c r="ACH24"/>
@@ -6668,52 +6608,52 @@
       <c r="ACL24"/>
     </row>
     <row r="25" spans="1:766" ht="24" customHeight="1">
-      <c r="A25" s="48">
+      <c r="A25" s="28">
         <v>1</v>
       </c>
-      <c r="B25" s="201"/>
-      <c r="C25" s="172"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="97"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="97"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="97"/>
-      <c r="U25" s="97"/>
-      <c r="V25" s="81"/>
-      <c r="W25" s="81"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="97"/>
-      <c r="AB25" s="103"/>
-      <c r="AC25" s="81"/>
-      <c r="AD25" s="81"/>
-      <c r="AE25" s="71"/>
-      <c r="AF25" s="20"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="37"/>
-      <c r="AL25" s="43"/>
-      <c r="AM25" s="162"/>
-      <c r="AN25" s="39"/>
-      <c r="AO25" s="39"/>
-      <c r="AP25" s="202"/>
-      <c r="AQ25" s="45"/>
-      <c r="AR25" s="164"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="165"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="165"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="110"/>
+      <c r="R25" s="107"/>
+      <c r="S25" s="110"/>
+      <c r="T25" s="165"/>
+      <c r="U25" s="165"/>
+      <c r="V25" s="76"/>
+      <c r="W25" s="76"/>
+      <c r="X25" s="110"/>
+      <c r="Y25" s="107"/>
+      <c r="Z25" s="110"/>
+      <c r="AA25" s="165"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="76"/>
+      <c r="AD25" s="76"/>
+      <c r="AE25" s="114"/>
+      <c r="AF25" s="107"/>
+      <c r="AG25" s="110"/>
+      <c r="AH25" s="91"/>
+      <c r="AI25" s="83"/>
+      <c r="AJ25" s="83"/>
+      <c r="AK25" s="84"/>
+      <c r="AL25" s="85"/>
+      <c r="AM25" s="86"/>
+      <c r="AN25" s="182"/>
+      <c r="AO25" s="182"/>
+      <c r="AP25" s="183"/>
+      <c r="AQ25" s="88"/>
+      <c r="AR25" s="88"/>
       <c r="ACF25"/>
       <c r="ACG25"/>
       <c r="ACH25"/>
@@ -6723,728 +6663,728 @@
       <c r="ACL25"/>
     </row>
     <row r="26" spans="1:766" ht="24" customHeight="1">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="49"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="49"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="53"/>
-      <c r="AD26" s="53"/>
-      <c r="AE26" s="49"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="74"/>
-      <c r="AI26" s="74"/>
-      <c r="AJ26" s="74"/>
-      <c r="AK26" s="74"/>
-      <c r="AL26" s="74"/>
-      <c r="AM26" s="74"/>
-      <c r="AN26" s="74"/>
-      <c r="AO26" s="74"/>
-      <c r="AP26" s="74"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="29"/>
+      <c r="AF26" s="29"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="43"/>
+      <c r="AN26" s="43"/>
+      <c r="AO26" s="43"/>
+      <c r="AP26" s="43"/>
     </row>
     <row r="27" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B27" s="46"/>
-      <c r="C27" s="46" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="26">
         <f>COUNTIF(D9:D19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="46">
+      <c r="E27" s="26">
         <f>COUNTIF(E9:E19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="46">
+      <c r="F27" s="26">
         <f>COUNTIF(F9:F19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="G27" s="46">
+      <c r="G27" s="26">
         <f t="shared" ref="F27:AH27" si="0">COUNTIF(G9:G19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="46">
+      <c r="H27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="46">
+      <c r="I27" s="26">
         <f>COUNTIF(I9:I19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="46">
+      <c r="J27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="46">
+      <c r="L27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M27" s="46">
+      <c r="M27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="46">
+      <c r="N27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="46">
+      <c r="O27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="46">
+      <c r="P27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="46">
+      <c r="Q27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27" s="46">
+      <c r="R27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S27" s="46">
+      <c r="S27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T27" s="46">
+      <c r="T27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U27" s="46">
+      <c r="U27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="46">
+      <c r="V27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="46">
+      <c r="W27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="46">
+      <c r="X27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="46">
+      <c r="Y27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="46">
+      <c r="Z27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="46">
+      <c r="AA27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="46">
+      <c r="AB27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="46">
+      <c r="AC27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="46">
+      <c r="AD27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="46">
+      <c r="AE27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="46">
+      <c r="AF27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="46">
+      <c r="AG27" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="29">
+      <c r="AH27" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="29"/>
-      <c r="AJ27" s="29"/>
-      <c r="AK27" s="29"/>
-      <c r="AL27" s="29"/>
-      <c r="AM27" s="29"/>
-      <c r="AN27" s="29"/>
-      <c r="AO27" s="29"/>
-      <c r="AP27" s="74"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="17"/>
+      <c r="AL27" s="17"/>
+      <c r="AM27" s="17"/>
+      <c r="AN27" s="17"/>
+      <c r="AO27" s="17"/>
+      <c r="AP27" s="43"/>
     </row>
     <row r="28" spans="1:766" ht="12.75" customHeight="1">
-      <c r="B28" s="29"/>
-      <c r="C28" s="29" t="s">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="17">
         <f t="shared" ref="D28:AH28" si="1">COUNTIF(D9:D19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="17">
         <f>COUNTIF(I9:I19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M28" s="29">
+      <c r="M28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="29">
+      <c r="N28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O28" s="29">
+      <c r="O28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P28" s="29">
+      <c r="P28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="29">
+      <c r="Q28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="29">
+      <c r="R28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S28" s="29">
+      <c r="S28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T28" s="29">
+      <c r="T28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="29">
+      <c r="U28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V28" s="29">
+      <c r="V28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="29">
+      <c r="W28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X28" s="29">
+      <c r="X28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="29">
+      <c r="Y28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="29">
+      <c r="Z28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="29">
+      <c r="AA28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="29">
+      <c r="AB28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="29">
+      <c r="AC28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="29">
+      <c r="AD28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="29">
+      <c r="AE28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="29">
+      <c r="AF28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="29">
+      <c r="AG28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="29">
+      <c r="AH28" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="29"/>
-      <c r="AJ28" s="29"/>
-      <c r="AK28" s="29"/>
-      <c r="AL28" s="29"/>
-      <c r="AM28" s="29"/>
-      <c r="AN28" s="29"/>
-      <c r="AO28" s="29"/>
-      <c r="AP28" s="74"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="17"/>
+      <c r="AM28" s="17"/>
+      <c r="AN28" s="17"/>
+      <c r="AO28" s="17"/>
+      <c r="AP28" s="43"/>
     </row>
     <row r="29" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B29" s="29"/>
-      <c r="C29" s="29" t="s">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="17">
         <f t="shared" ref="D29:AH29" si="2">COUNTIF(D9:D19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="29">
+      <c r="G29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="17">
         <f>COUNTIF(I9:I19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M29" s="29">
+      <c r="M29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="29">
+      <c r="O29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="29">
+      <c r="Q29" s="17">
         <v>2</v>
       </c>
-      <c r="R29" s="29">
+      <c r="R29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="29">
+      <c r="S29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T29" s="29">
+      <c r="T29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U29" s="29">
+      <c r="U29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V29" s="29">
+      <c r="V29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W29" s="29">
+      <c r="W29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X29" s="29">
+      <c r="X29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="29">
+      <c r="Y29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="29">
+      <c r="Z29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="29">
+      <c r="AA29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="29">
+      <c r="AB29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="29">
+      <c r="AC29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="29">
+      <c r="AD29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="29">
+      <c r="AE29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="29">
+      <c r="AF29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="29">
+      <c r="AG29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="29">
+      <c r="AH29" s="17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="29"/>
-      <c r="AJ29" s="29"/>
-      <c r="AK29" s="29"/>
-      <c r="AL29" s="29"/>
-      <c r="AM29" s="29"/>
-      <c r="AN29" s="29"/>
-      <c r="AO29" s="29"/>
-      <c r="AP29" s="74"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="17"/>
+      <c r="AL29" s="17"/>
+      <c r="AM29" s="17"/>
+      <c r="AN29" s="17"/>
+      <c r="AO29" s="17"/>
+      <c r="AP29" s="43"/>
     </row>
     <row r="30" spans="1:766" ht="12" customHeight="1">
-      <c r="A30" s="30"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="17">
         <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="17">
         <f>COUNTIF(N9:N25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="29">
+      <c r="Q30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="29">
+      <c r="R30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S30" s="29">
+      <c r="S30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T30" s="29">
+      <c r="T30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="29">
+      <c r="U30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V30" s="29">
+      <c r="V30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W30" s="29">
+      <c r="W30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X30" s="29">
+      <c r="X30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y30" s="29">
+      <c r="Y30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="29">
+      <c r="Z30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="29">
+      <c r="AA30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="29">
+      <c r="AB30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="29">
+      <c r="AC30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="29">
+      <c r="AD30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="29">
+      <c r="AE30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="29">
+      <c r="AF30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="29">
+      <c r="AG30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="29">
+      <c r="AH30" s="17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="29"/>
-      <c r="AJ30" s="29"/>
-      <c r="AK30" s="29"/>
-      <c r="AL30" s="29"/>
-      <c r="AM30" s="29"/>
-      <c r="AN30" s="29"/>
-      <c r="AO30" s="29"/>
-      <c r="AP30" s="74"/>
+      <c r="AI30" s="17"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="17"/>
+      <c r="AL30" s="17"/>
+      <c r="AM30" s="17"/>
+      <c r="AN30" s="17"/>
+      <c r="AO30" s="17"/>
+      <c r="AP30" s="43"/>
     </row>
     <row r="31" spans="1:766">
-      <c r="A31" s="30"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="32"/>
-      <c r="X31" s="32"/>
-      <c r="Y31" s="32"/>
-      <c r="Z31" s="32"/>
-      <c r="AA31" s="32"/>
-      <c r="AB31" s="32"/>
-      <c r="AC31" s="32"/>
-      <c r="AD31" s="32"/>
-      <c r="AE31" s="32"/>
-      <c r="AF31" s="32"/>
-      <c r="AG31" s="32"/>
-      <c r="AH31" s="32"/>
-      <c r="AI31" s="32"/>
-      <c r="AJ31" s="32"/>
-      <c r="AK31" s="32"/>
-      <c r="AL31" s="75"/>
-      <c r="AO31" s="73"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
+      <c r="AG31" s="20"/>
+      <c r="AH31" s="20"/>
+      <c r="AI31" s="20"/>
+      <c r="AJ31" s="20"/>
+      <c r="AK31" s="20"/>
+      <c r="AL31" s="44"/>
+      <c r="AO31" s="42"/>
     </row>
     <row r="32" spans="1:766">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
-      <c r="AG32" s="30"/>
-      <c r="AH32" s="30"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="30"/>
-      <c r="AK32" s="30"/>
-      <c r="AL32" s="75"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Y32" s="18"/>
+      <c r="Z32" s="18"/>
+      <c r="AA32" s="18"/>
+      <c r="AB32" s="18"/>
+      <c r="AC32" s="18"/>
+      <c r="AD32" s="18"/>
+      <c r="AE32" s="18"/>
+      <c r="AF32" s="18"/>
+      <c r="AG32" s="18"/>
+      <c r="AH32" s="18"/>
+      <c r="AI32" s="18"/>
+      <c r="AJ32" s="18"/>
+      <c r="AK32" s="18"/>
+      <c r="AL32" s="44"/>
     </row>
     <row r="33" spans="1:767" s="2" customFormat="1">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="30"/>
-      <c r="Q33" s="30"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="30"/>
-      <c r="V33" s="30"/>
-      <c r="W33" s="30"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="30"/>
-      <c r="AD33" s="30"/>
-      <c r="AE33" s="30"/>
-      <c r="AF33" s="30"/>
-      <c r="AG33" s="30"/>
-      <c r="AH33" s="30"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="30"/>
-      <c r="AK33" s="30"/>
-      <c r="AL33" s="75"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="18"/>
+      <c r="Z33" s="18"/>
+      <c r="AA33" s="18"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="18"/>
+      <c r="AE33" s="18"/>
+      <c r="AF33" s="18"/>
+      <c r="AG33" s="18"/>
+      <c r="AH33" s="18"/>
+      <c r="AI33" s="18"/>
+      <c r="AJ33" s="18"/>
+      <c r="AK33" s="18"/>
+      <c r="AL33" s="44"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
-      <c r="AR33" s="40"/>
+      <c r="AR33" s="21"/>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -8170,50 +8110,50 @@
       <c r="ACM33"/>
     </row>
     <row r="34" spans="1:767" s="2" customFormat="1">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="30"/>
-      <c r="Z34" s="30"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="30"/>
-      <c r="AF34" s="30"/>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="30"/>
-      <c r="AL34" s="75"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Y34" s="18"/>
+      <c r="Z34" s="18"/>
+      <c r="AA34" s="18"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="18"/>
+      <c r="AE34" s="18"/>
+      <c r="AF34" s="18"/>
+      <c r="AG34" s="18"/>
+      <c r="AH34" s="18"/>
+      <c r="AI34" s="18"/>
+      <c r="AJ34" s="18"/>
+      <c r="AK34" s="18"/>
+      <c r="AL34" s="44"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="40"/>
+      <c r="AR34" s="21"/>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
@@ -8939,50 +8879,50 @@
       <c r="ACM34"/>
     </row>
     <row r="35" spans="1:767" s="2" customFormat="1">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
-      <c r="AD35" s="30"/>
-      <c r="AE35" s="30"/>
-      <c r="AF35" s="30"/>
-      <c r="AG35" s="30"/>
-      <c r="AH35" s="30"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="30"/>
-      <c r="AK35" s="30"/>
-      <c r="AL35" s="75"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
+      <c r="R35" s="18"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="18"/>
+      <c r="AA35" s="18"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="18"/>
+      <c r="AE35" s="18"/>
+      <c r="AF35" s="18"/>
+      <c r="AG35" s="18"/>
+      <c r="AH35" s="18"/>
+      <c r="AI35" s="18"/>
+      <c r="AJ35" s="18"/>
+      <c r="AK35" s="18"/>
+      <c r="AL35" s="44"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
-      <c r="AR35" s="40"/>
+      <c r="AR35" s="21"/>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
@@ -9708,50 +9648,50 @@
       <c r="ACM35"/>
     </row>
     <row r="36" spans="1:767" s="2" customFormat="1">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="30"/>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
-      <c r="AC36" s="30"/>
-      <c r="AD36" s="30"/>
-      <c r="AE36" s="30"/>
-      <c r="AF36" s="30"/>
-      <c r="AG36" s="30"/>
-      <c r="AH36" s="30"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="30"/>
-      <c r="AK36" s="30"/>
-      <c r="AL36" s="75"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="18"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="18"/>
+      <c r="V36" s="18"/>
+      <c r="W36" s="18"/>
+      <c r="X36" s="18"/>
+      <c r="Y36" s="18"/>
+      <c r="Z36" s="18"/>
+      <c r="AA36" s="18"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
+      <c r="AF36" s="18"/>
+      <c r="AG36" s="18"/>
+      <c r="AH36" s="18"/>
+      <c r="AI36" s="18"/>
+      <c r="AJ36" s="18"/>
+      <c r="AK36" s="18"/>
+      <c r="AL36" s="44"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
-      <c r="AR36" s="40"/>
+      <c r="AR36" s="21"/>
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
@@ -10477,50 +10417,50 @@
       <c r="ACM36"/>
     </row>
     <row r="37" spans="1:767" s="2" customFormat="1">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="75"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="18"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="18"/>
+      <c r="V37" s="18"/>
+      <c r="W37" s="18"/>
+      <c r="X37" s="18"/>
+      <c r="Y37" s="18"/>
+      <c r="Z37" s="18"/>
+      <c r="AA37" s="18"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="18"/>
+      <c r="AE37" s="18"/>
+      <c r="AF37" s="18"/>
+      <c r="AG37" s="18"/>
+      <c r="AH37" s="18"/>
+      <c r="AI37" s="18"/>
+      <c r="AJ37" s="18"/>
+      <c r="AK37" s="18"/>
+      <c r="AL37" s="44"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
-      <c r="AR37" s="40"/>
+      <c r="AR37" s="21"/>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
@@ -11246,50 +11186,50 @@
       <c r="ACM37"/>
     </row>
     <row r="38" spans="1:767" s="2" customFormat="1">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
-      <c r="AA38" s="30"/>
-      <c r="AB38" s="30"/>
-      <c r="AC38" s="30"/>
-      <c r="AD38" s="30"/>
-      <c r="AE38" s="30"/>
-      <c r="AF38" s="30"/>
-      <c r="AG38" s="30"/>
-      <c r="AH38" s="30"/>
-      <c r="AI38" s="30"/>
-      <c r="AJ38" s="30"/>
-      <c r="AK38" s="30"/>
-      <c r="AL38" s="75"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="18"/>
+      <c r="R38" s="18"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="18"/>
+      <c r="V38" s="18"/>
+      <c r="W38" s="18"/>
+      <c r="X38" s="18"/>
+      <c r="Y38" s="18"/>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="18"/>
+      <c r="AE38" s="18"/>
+      <c r="AF38" s="18"/>
+      <c r="AG38" s="18"/>
+      <c r="AH38" s="18"/>
+      <c r="AI38" s="18"/>
+      <c r="AJ38" s="18"/>
+      <c r="AK38" s="18"/>
+      <c r="AL38" s="44"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
-      <c r="AR38" s="40"/>
+      <c r="AR38" s="21"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
@@ -12015,50 +11955,50 @@
       <c r="ACM38"/>
     </row>
     <row r="39" spans="1:767" s="2" customFormat="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
-      <c r="W39" s="30"/>
-      <c r="X39" s="30"/>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
-      <c r="AC39" s="30"/>
-      <c r="AD39" s="30"/>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
-      <c r="AI39" s="30"/>
-      <c r="AJ39" s="30"/>
-      <c r="AK39" s="30"/>
-      <c r="AL39" s="75"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
+      <c r="V39" s="18"/>
+      <c r="W39" s="18"/>
+      <c r="X39" s="18"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="18"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
+      <c r="AF39" s="18"/>
+      <c r="AG39" s="18"/>
+      <c r="AH39" s="18"/>
+      <c r="AI39" s="18"/>
+      <c r="AJ39" s="18"/>
+      <c r="AK39" s="18"/>
+      <c r="AL39" s="44"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
-      <c r="AR39" s="40"/>
+      <c r="AR39" s="21"/>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
@@ -12784,50 +12724,50 @@
       <c r="ACM39"/>
     </row>
     <row r="40" spans="1:767" s="2" customFormat="1">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
-      <c r="AE40" s="30"/>
-      <c r="AF40" s="30"/>
-      <c r="AG40" s="30"/>
-      <c r="AH40" s="30"/>
-      <c r="AI40" s="30"/>
-      <c r="AJ40" s="30"/>
-      <c r="AK40" s="30"/>
-      <c r="AL40" s="75"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="18"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="18"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="18"/>
+      <c r="AI40" s="18"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="18"/>
+      <c r="AL40" s="44"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
-      <c r="AR40" s="40"/>
+      <c r="AR40" s="21"/>
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
@@ -13553,50 +13493,50 @@
       <c r="ACM40"/>
     </row>
     <row r="41" spans="1:767" s="2" customFormat="1">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="30"/>
-      <c r="P41" s="30"/>
-      <c r="Q41" s="30"/>
-      <c r="R41" s="30"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="30"/>
-      <c r="U41" s="30"/>
-      <c r="V41" s="30"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="30"/>
-      <c r="Y41" s="30"/>
-      <c r="Z41" s="30"/>
-      <c r="AA41" s="30"/>
-      <c r="AB41" s="30"/>
-      <c r="AC41" s="30"/>
-      <c r="AD41" s="30"/>
-      <c r="AE41" s="30"/>
-      <c r="AF41" s="30"/>
-      <c r="AG41" s="30"/>
-      <c r="AH41" s="30"/>
-      <c r="AI41" s="30"/>
-      <c r="AJ41" s="30"/>
-      <c r="AK41" s="30"/>
-      <c r="AL41" s="75"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="18"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
+      <c r="AF41" s="18"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="18"/>
+      <c r="AI41" s="18"/>
+      <c r="AJ41" s="18"/>
+      <c r="AK41" s="18"/>
+      <c r="AL41" s="44"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
-      <c r="AR41" s="40"/>
+      <c r="AR41" s="21"/>
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
@@ -14322,50 +14262,50 @@
       <c r="ACM41"/>
     </row>
     <row r="42" spans="1:767" s="2" customFormat="1">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="30"/>
-      <c r="P42" s="30"/>
-      <c r="Q42" s="30"/>
-      <c r="R42" s="30"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="30"/>
-      <c r="U42" s="30"/>
-      <c r="V42" s="30"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="30"/>
-      <c r="Y42" s="30"/>
-      <c r="Z42" s="30"/>
-      <c r="AA42" s="30"/>
-      <c r="AB42" s="30"/>
-      <c r="AC42" s="30"/>
-      <c r="AD42" s="30"/>
-      <c r="AE42" s="30"/>
-      <c r="AF42" s="30"/>
-      <c r="AG42" s="30"/>
-      <c r="AH42" s="30"/>
-      <c r="AI42" s="30"/>
-      <c r="AJ42" s="30"/>
-      <c r="AK42" s="30"/>
-      <c r="AL42" s="75"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="18"/>
+      <c r="R42" s="18"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="18"/>
+      <c r="V42" s="18"/>
+      <c r="W42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="18"/>
+      <c r="Z42" s="18"/>
+      <c r="AA42" s="18"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="18"/>
+      <c r="AE42" s="18"/>
+      <c r="AF42" s="18"/>
+      <c r="AG42" s="18"/>
+      <c r="AH42" s="18"/>
+      <c r="AI42" s="18"/>
+      <c r="AJ42" s="18"/>
+      <c r="AK42" s="18"/>
+      <c r="AL42" s="44"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
-      <c r="AR42" s="40"/>
+      <c r="AR42" s="21"/>
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
@@ -15091,50 +15031,50 @@
       <c r="ACM42"/>
     </row>
     <row r="43" spans="1:767" s="2" customFormat="1">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
-      <c r="AE43" s="30"/>
-      <c r="AF43" s="30"/>
-      <c r="AG43" s="30"/>
-      <c r="AH43" s="30"/>
-      <c r="AI43" s="30"/>
-      <c r="AJ43" s="30"/>
-      <c r="AK43" s="30"/>
-      <c r="AL43" s="75"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
+      <c r="AB43" s="18"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="18"/>
+      <c r="AE43" s="18"/>
+      <c r="AF43" s="18"/>
+      <c r="AG43" s="18"/>
+      <c r="AH43" s="18"/>
+      <c r="AI43" s="18"/>
+      <c r="AJ43" s="18"/>
+      <c r="AK43" s="18"/>
+      <c r="AL43" s="44"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
-      <c r="AR43" s="40"/>
+      <c r="AR43" s="21"/>
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
@@ -15860,50 +15800,50 @@
       <c r="ACM43"/>
     </row>
     <row r="44" spans="1:767" s="2" customFormat="1">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="30"/>
-      <c r="P44" s="30"/>
-      <c r="Q44" s="30"/>
-      <c r="R44" s="30"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="30"/>
-      <c r="U44" s="30"/>
-      <c r="V44" s="30"/>
-      <c r="W44" s="30"/>
-      <c r="X44" s="30"/>
-      <c r="Y44" s="30"/>
-      <c r="Z44" s="30"/>
-      <c r="AA44" s="30"/>
-      <c r="AB44" s="30"/>
-      <c r="AC44" s="30"/>
-      <c r="AD44" s="30"/>
-      <c r="AE44" s="30"/>
-      <c r="AF44" s="30"/>
-      <c r="AG44" s="30"/>
-      <c r="AH44" s="30"/>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="30"/>
-      <c r="AK44" s="30"/>
-      <c r="AL44" s="75"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="18"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="18"/>
+      <c r="AE44" s="18"/>
+      <c r="AF44" s="18"/>
+      <c r="AG44" s="18"/>
+      <c r="AH44" s="18"/>
+      <c r="AI44" s="18"/>
+      <c r="AJ44" s="18"/>
+      <c r="AK44" s="18"/>
+      <c r="AL44" s="44"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
-      <c r="AR44" s="40"/>
+      <c r="AR44" s="21"/>
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
@@ -16629,50 +16569,50 @@
       <c r="ACM44"/>
     </row>
     <row r="45" spans="1:767" s="2" customFormat="1">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="30"/>
-      <c r="O45" s="30"/>
-      <c r="P45" s="30"/>
-      <c r="Q45" s="30"/>
-      <c r="R45" s="30"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="30"/>
-      <c r="U45" s="30"/>
-      <c r="V45" s="30"/>
-      <c r="W45" s="30"/>
-      <c r="X45" s="30"/>
-      <c r="Y45" s="30"/>
-      <c r="Z45" s="30"/>
-      <c r="AA45" s="30"/>
-      <c r="AB45" s="30"/>
-      <c r="AC45" s="30"/>
-      <c r="AD45" s="30"/>
-      <c r="AE45" s="30"/>
-      <c r="AF45" s="30"/>
-      <c r="AG45" s="30"/>
-      <c r="AH45" s="30"/>
-      <c r="AI45" s="30"/>
-      <c r="AJ45" s="30"/>
-      <c r="AK45" s="30"/>
-      <c r="AL45" s="75"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="18"/>
+      <c r="AF45" s="18"/>
+      <c r="AG45" s="18"/>
+      <c r="AH45" s="18"/>
+      <c r="AI45" s="18"/>
+      <c r="AJ45" s="18"/>
+      <c r="AK45" s="18"/>
+      <c r="AL45" s="44"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
-      <c r="AR45" s="40"/>
+      <c r="AR45" s="21"/>
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
@@ -17398,50 +17338,50 @@
       <c r="ACM45"/>
     </row>
     <row r="46" spans="1:767" s="2" customFormat="1">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
-      <c r="AE46" s="30"/>
-      <c r="AF46" s="30"/>
-      <c r="AG46" s="30"/>
-      <c r="AH46" s="30"/>
-      <c r="AI46" s="30"/>
-      <c r="AJ46" s="30"/>
-      <c r="AK46" s="30"/>
-      <c r="AL46" s="75"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="18"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="18"/>
+      <c r="Z46" s="18"/>
+      <c r="AA46" s="18"/>
+      <c r="AB46" s="18"/>
+      <c r="AC46" s="18"/>
+      <c r="AD46" s="18"/>
+      <c r="AE46" s="18"/>
+      <c r="AF46" s="18"/>
+      <c r="AG46" s="18"/>
+      <c r="AH46" s="18"/>
+      <c r="AI46" s="18"/>
+      <c r="AJ46" s="18"/>
+      <c r="AK46" s="18"/>
+      <c r="AL46" s="44"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
-      <c r="AR46" s="40"/>
+      <c r="AR46" s="21"/>
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
@@ -18167,50 +18107,50 @@
       <c r="ACM46"/>
     </row>
     <row r="47" spans="1:767" s="2" customFormat="1">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
-      <c r="S47" s="30"/>
-      <c r="T47" s="30"/>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="30"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="30"/>
-      <c r="AD47" s="30"/>
-      <c r="AE47" s="30"/>
-      <c r="AF47" s="30"/>
-      <c r="AG47" s="30"/>
-      <c r="AH47" s="30"/>
-      <c r="AI47" s="30"/>
-      <c r="AJ47" s="30"/>
-      <c r="AK47" s="30"/>
-      <c r="AL47" s="75"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="18"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="18"/>
+      <c r="AE47" s="18"/>
+      <c r="AF47" s="18"/>
+      <c r="AG47" s="18"/>
+      <c r="AH47" s="18"/>
+      <c r="AI47" s="18"/>
+      <c r="AJ47" s="18"/>
+      <c r="AK47" s="18"/>
+      <c r="AL47" s="44"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
-      <c r="AR47" s="40"/>
+      <c r="AR47" s="21"/>
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
@@ -18936,50 +18876,50 @@
       <c r="ACM47"/>
     </row>
     <row r="48" spans="1:767" s="2" customFormat="1">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="S48" s="30"/>
-      <c r="T48" s="30"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="30"/>
-      <c r="X48" s="30"/>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
-      <c r="AD48" s="30"/>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AH48" s="30"/>
-      <c r="AI48" s="30"/>
-      <c r="AJ48" s="30"/>
-      <c r="AK48" s="30"/>
-      <c r="AL48" s="75"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="18"/>
+      <c r="V48" s="18"/>
+      <c r="W48" s="18"/>
+      <c r="X48" s="18"/>
+      <c r="Y48" s="18"/>
+      <c r="Z48" s="18"/>
+      <c r="AA48" s="18"/>
+      <c r="AB48" s="18"/>
+      <c r="AC48" s="18"/>
+      <c r="AD48" s="18"/>
+      <c r="AE48" s="18"/>
+      <c r="AF48" s="18"/>
+      <c r="AG48" s="18"/>
+      <c r="AH48" s="18"/>
+      <c r="AI48" s="18"/>
+      <c r="AJ48" s="18"/>
+      <c r="AK48" s="18"/>
+      <c r="AL48" s="44"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
-      <c r="AR48" s="40"/>
+      <c r="AR48" s="21"/>
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
@@ -19705,50 +19645,50 @@
       <c r="ACM48"/>
     </row>
     <row r="49" spans="1:767" s="2" customFormat="1">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
-      <c r="AG49" s="30"/>
-      <c r="AH49" s="30"/>
-      <c r="AI49" s="30"/>
-      <c r="AJ49" s="30"/>
-      <c r="AK49" s="30"/>
-      <c r="AL49" s="75"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="18"/>
+      <c r="V49" s="18"/>
+      <c r="W49" s="18"/>
+      <c r="X49" s="18"/>
+      <c r="Y49" s="18"/>
+      <c r="Z49" s="18"/>
+      <c r="AA49" s="18"/>
+      <c r="AB49" s="18"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="18"/>
+      <c r="AE49" s="18"/>
+      <c r="AF49" s="18"/>
+      <c r="AG49" s="18"/>
+      <c r="AH49" s="18"/>
+      <c r="AI49" s="18"/>
+      <c r="AJ49" s="18"/>
+      <c r="AK49" s="18"/>
+      <c r="AL49" s="44"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
-      <c r="AR49" s="40"/>
+      <c r="AR49" s="21"/>
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
@@ -20474,50 +20414,50 @@
       <c r="ACM49"/>
     </row>
     <row r="50" spans="1:767" s="2" customFormat="1">
-      <c r="A50" s="30"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-      <c r="K50" s="30"/>
-      <c r="L50" s="30"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30"/>
-      <c r="O50" s="30"/>
-      <c r="P50" s="30"/>
-      <c r="Q50" s="30"/>
-      <c r="R50" s="30"/>
-      <c r="S50" s="30"/>
-      <c r="T50" s="30"/>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
-      <c r="W50" s="30"/>
-      <c r="X50" s="30"/>
-      <c r="Y50" s="30"/>
-      <c r="Z50" s="30"/>
-      <c r="AA50" s="30"/>
-      <c r="AB50" s="30"/>
-      <c r="AC50" s="30"/>
-      <c r="AD50" s="30"/>
-      <c r="AE50" s="30"/>
-      <c r="AF50" s="30"/>
-      <c r="AG50" s="30"/>
-      <c r="AH50" s="30"/>
-      <c r="AI50" s="30"/>
-      <c r="AJ50" s="30"/>
-      <c r="AK50" s="30"/>
-      <c r="AL50" s="75"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="18"/>
+      <c r="V50" s="18"/>
+      <c r="W50" s="18"/>
+      <c r="X50" s="18"/>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="18"/>
+      <c r="AA50" s="18"/>
+      <c r="AB50" s="18"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="18"/>
+      <c r="AE50" s="18"/>
+      <c r="AF50" s="18"/>
+      <c r="AG50" s="18"/>
+      <c r="AH50" s="18"/>
+      <c r="AI50" s="18"/>
+      <c r="AJ50" s="18"/>
+      <c r="AK50" s="18"/>
+      <c r="AL50" s="44"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
       <c r="AO50" s="3"/>
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
-      <c r="AR50" s="40"/>
+      <c r="AR50" s="21"/>
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>

--- a/nurse_scheduler_template.xlsx
+++ b/nurse_scheduler_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D05FA16A-3CCF-479C-9982-CD938AD07CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A966DE56-6147-4528-B1E5-52A89A86012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B332721F-AB2B-4BF1-A12F-4722F279DAC4}"/>
   </bookViews>
@@ -824,7 +824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -853,11 +853,41 @@
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -877,6 +907,27 @@
     </xf>
     <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -907,11 +958,14 @@
     </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="22" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -928,13 +982,34 @@
     <xf numFmtId="176" fontId="21" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="21" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="22" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -949,11 +1024,132 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -966,8 +1162,92 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1029,318 +1309,65 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1663,13 +1690,13 @@
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.44140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="3.6640625" style="14" customWidth="1"/>
+    <col min="4" max="5" width="3.6640625" style="24" customWidth="1"/>
     <col min="6" max="13" width="3.6640625" style="3" customWidth="1"/>
-    <col min="14" max="17" width="3.6640625" style="14" customWidth="1"/>
+    <col min="14" max="17" width="3.6640625" style="24" customWidth="1"/>
     <col min="18" max="18" width="3.6640625" style="3" customWidth="1"/>
-    <col min="19" max="32" width="3.6640625" style="14" customWidth="1"/>
-    <col min="33" max="33" width="3.44140625" style="14" customWidth="1"/>
-    <col min="34" max="34" width="3.5546875" style="14" customWidth="1"/>
+    <col min="19" max="32" width="3.6640625" style="24" customWidth="1"/>
+    <col min="33" max="33" width="3.44140625" style="24" customWidth="1"/>
+    <col min="34" max="34" width="3.5546875" style="24" customWidth="1"/>
     <col min="35" max="35" width="3" style="3" customWidth="1"/>
     <col min="36" max="36" width="3" style="2" customWidth="1"/>
     <col min="37" max="37" width="4.5546875" style="2" customWidth="1"/>
@@ -1679,7 +1706,7 @@
     <col min="41" max="41" width="7.5546875" style="3" customWidth="1"/>
     <col min="42" max="42" width="6.88671875" style="3" customWidth="1"/>
     <col min="43" max="43" width="7.5546875" style="3" customWidth="1"/>
-    <col min="44" max="44" width="5.44140625" style="21" customWidth="1"/>
+    <col min="44" max="44" width="5.44140625" style="38" customWidth="1"/>
     <col min="45" max="765" width="7.5546875" style="3" customWidth="1"/>
     <col min="766" max="766" width="8.88671875" style="3" customWidth="1"/>
     <col min="767" max="767" width="8.88671875" customWidth="1"/>
@@ -1719,93 +1746,93 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="44"/>
-      <c r="AL1" s="44"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AV1" s="48"/>
+      <c r="AW1" s="48"/>
     </row>
     <row r="2" spans="1:766" ht="49.5" customHeight="1">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="151"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="151"/>
+      <c r="X2" s="151"/>
+      <c r="Y2" s="151"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="151"/>
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="151"/>
+      <c r="AF2" s="151"/>
+      <c r="AG2" s="151"/>
+      <c r="AH2" s="151"/>
+      <c r="AI2" s="151"/>
+      <c r="AJ2" s="151"/>
+      <c r="AK2" s="151"/>
+      <c r="AL2" s="151"/>
+      <c r="AM2" s="151"/>
     </row>
     <row r="3" spans="1:766" ht="6" customHeight="1" thickBot="1">
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="51"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="51"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
-      <c r="AL3" s="51"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="115"/>
+      <c r="T3" s="115"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
     </row>
     <row r="4" spans="1:766" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="4"/>
@@ -1831,42 +1858,42 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
-      <c r="Z4" s="60"/>
-      <c r="AA4" s="60"/>
+      <c r="Z4" s="152"/>
+      <c r="AA4" s="152"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="45"/>
-      <c r="AE4" s="61" t="s">
+      <c r="AD4" s="70"/>
+      <c r="AE4" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="AF4" s="62"/>
-      <c r="AG4" s="63" t="s">
+      <c r="AF4" s="154"/>
+      <c r="AG4" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="AH4" s="64"/>
-      <c r="AR4" s="21"/>
+      <c r="AH4" s="156"/>
+      <c r="AR4" s="38"/>
     </row>
     <row r="5" spans="1:766" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="67"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="159"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="70"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="161"/>
+      <c r="P5" s="161"/>
+      <c r="Q5" s="162"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1874,16 +1901,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="60"/>
-      <c r="AB5" s="60"/>
-      <c r="AC5" s="60"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="71"/>
-      <c r="AF5" s="72"/>
-      <c r="AG5" s="72"/>
-      <c r="AH5" s="73"/>
-      <c r="AR5" s="21" t="s">
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="116"/>
+      <c r="AE5" s="163"/>
+      <c r="AF5" s="164"/>
+      <c r="AG5" s="164"/>
+      <c r="AH5" s="165"/>
+      <c r="AR5" s="38" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1925,129 +1952,129 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
-      <c r="AK6" s="44"/>
-      <c r="AL6" s="44"/>
+      <c r="AK6" s="69"/>
+      <c r="AL6" s="69"/>
     </row>
     <row r="7" spans="1:766" s="9" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="35">
+      <c r="C7" s="146"/>
+      <c r="D7" s="53">
         <v>1</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="53">
         <v>2</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="56">
         <v>3</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="56">
         <v>4</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="54">
         <v>5</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="55">
         <v>6</v>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="53">
         <v>7</v>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="53">
         <v>8</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="56">
         <v>9</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="56">
         <v>10</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="56">
         <v>11</v>
       </c>
-      <c r="O7" s="37">
+      <c r="O7" s="55">
         <v>12</v>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="55">
         <v>13</v>
       </c>
-      <c r="Q7" s="35">
+      <c r="Q7" s="53">
         <v>14</v>
       </c>
-      <c r="R7" s="35">
+      <c r="R7" s="53">
         <v>15</v>
       </c>
-      <c r="S7" s="35">
+      <c r="S7" s="53">
         <v>16</v>
       </c>
-      <c r="T7" s="38">
+      <c r="T7" s="56">
         <v>17</v>
       </c>
-      <c r="U7" s="38">
+      <c r="U7" s="56">
         <v>18</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="55">
         <v>19</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="55">
         <v>20</v>
       </c>
-      <c r="X7" s="35">
+      <c r="X7" s="53">
         <v>21</v>
       </c>
-      <c r="Y7" s="35">
+      <c r="Y7" s="53">
         <v>22</v>
       </c>
-      <c r="Z7" s="35">
+      <c r="Z7" s="53">
         <v>23</v>
       </c>
-      <c r="AA7" s="34">
+      <c r="AA7" s="52">
         <v>24</v>
       </c>
-      <c r="AB7" s="34">
+      <c r="AB7" s="52">
         <v>25</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="55">
         <v>26</v>
       </c>
-      <c r="AD7" s="37">
+      <c r="AD7" s="55">
         <v>27</v>
       </c>
-      <c r="AE7" s="35">
+      <c r="AE7" s="53">
         <v>28</v>
       </c>
-      <c r="AF7" s="35">
+      <c r="AF7" s="53">
         <v>29</v>
       </c>
-      <c r="AG7" s="35">
+      <c r="AG7" s="53">
         <v>30</v>
       </c>
-      <c r="AH7" s="38">
+      <c r="AH7" s="56">
         <v>31</v>
       </c>
-      <c r="AI7" s="49" t="s">
+      <c r="AI7" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="AJ7" s="23" t="s">
+      <c r="AJ7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AK7" s="49" t="s">
+      <c r="AK7" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="AL7" s="24" t="s">
+      <c r="AL7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="AM7" s="55" t="s">
+      <c r="AM7" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="AN7" s="56" t="s">
+      <c r="AN7" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="AO7" s="50"/>
-      <c r="AP7" s="22"/>
+      <c r="AO7" s="114"/>
+      <c r="AP7" s="39"/>
       <c r="AQ7" s="10"/>
-      <c r="AR7" s="22"/>
+      <c r="AR7" s="39"/>
       <c r="AS7" s="11"/>
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
@@ -2766,117 +2793,117 @@
       <c r="ACF7" s="11"/>
     </row>
     <row r="8" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="149" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="35" t="s">
+      <c r="C8" s="149"/>
+      <c r="D8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="183" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="37" t="s">
+      <c r="I8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="38" t="s">
+      <c r="M8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="38" t="s">
+      <c r="N8" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="37" t="s">
+      <c r="O8" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="37" t="s">
+      <c r="P8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="35" t="s">
+      <c r="Q8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="35" t="s">
+      <c r="R8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="35" t="s">
+      <c r="S8" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="38" t="s">
+      <c r="T8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="38" t="s">
+      <c r="U8" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="37" t="s">
+      <c r="V8" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="37" t="s">
+      <c r="W8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="35" t="s">
+      <c r="X8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="39" t="s">
+      <c r="Y8" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="39" t="s">
+      <c r="Z8" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="34" t="s">
+      <c r="AA8" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" s="41" t="s">
+      <c r="AB8" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="37" t="s">
+      <c r="AC8" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="AD8" s="37" t="s">
+      <c r="AD8" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="AE8" s="40" t="s">
+      <c r="AE8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="35" t="s">
+      <c r="AF8" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="AG8" s="35" t="s">
+      <c r="AG8" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="34" t="s">
+      <c r="AH8" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="AI8" s="49"/>
-      <c r="AJ8" s="49"/>
-      <c r="AK8" s="49"/>
-      <c r="AL8" s="25"/>
-      <c r="AM8" s="55"/>
-      <c r="AN8" s="56"/>
-      <c r="AO8" s="50"/>
-      <c r="AP8" s="30" t="s">
+      <c r="AI8" s="113"/>
+      <c r="AJ8" s="113"/>
+      <c r="AK8" s="113"/>
+      <c r="AL8" s="42"/>
+      <c r="AM8" s="147"/>
+      <c r="AN8" s="148"/>
+      <c r="AO8" s="114"/>
+      <c r="AP8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AQ8" s="22" t="s">
+      <c r="AQ8" s="39" t="s">
         <v>29</v>
       </c>
       <c r="AR8" s="10" t="s">
@@ -3599,52 +3626,52 @@
       <c r="ACF8" s="11"/>
     </row>
     <row r="9" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="28">
+      <c r="A9" s="45">
         <v>1</v>
       </c>
-      <c r="B9" s="74"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="78"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="12"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="79"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="80"/>
-      <c r="AB9" s="80"/>
-      <c r="AC9" s="76"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="81"/>
-      <c r="AF9" s="79"/>
-      <c r="AG9" s="76"/>
-      <c r="AH9" s="82"/>
-      <c r="AI9" s="83"/>
-      <c r="AJ9" s="83"/>
-      <c r="AK9" s="84"/>
-      <c r="AL9" s="85"/>
-      <c r="AM9" s="86"/>
-      <c r="AN9" s="87"/>
-      <c r="AO9" s="87"/>
-      <c r="AP9" s="88"/>
-      <c r="AQ9" s="88"/>
-      <c r="AR9" s="88"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="166"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="166"/>
+      <c r="M9" s="166"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="78"/>
+      <c r="U9" s="78"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="41"/>
+      <c r="AM9" s="118"/>
+      <c r="AN9" s="167"/>
+      <c r="AO9" s="167"/>
+      <c r="AP9" s="119"/>
+      <c r="AQ9" s="119"/>
+      <c r="AR9" s="119"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
@@ -4361,52 +4388,52 @@
       <c r="ACD9" s="11"/>
     </row>
     <row r="10" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="28">
+      <c r="A10" s="45">
         <v>2</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="89"/>
-      <c r="H10" s="90"/>
-      <c r="I10" s="76"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="76"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="76"/>
-      <c r="S10" s="76"/>
-      <c r="T10" s="47"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="76"/>
-      <c r="W10" s="76"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="79"/>
-      <c r="Z10" s="76"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="80"/>
-      <c r="AC10" s="76"/>
-      <c r="AD10" s="76"/>
-      <c r="AE10" s="81"/>
-      <c r="AF10" s="79"/>
-      <c r="AG10" s="76"/>
-      <c r="AH10" s="91"/>
-      <c r="AI10" s="83"/>
-      <c r="AJ10" s="83"/>
-      <c r="AK10" s="84"/>
-      <c r="AL10" s="85"/>
-      <c r="AM10" s="86"/>
-      <c r="AN10" s="87"/>
-      <c r="AO10" s="87"/>
-      <c r="AP10" s="88"/>
-      <c r="AQ10" s="88"/>
-      <c r="AR10" s="88"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="168"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="78"/>
+      <c r="AB10" s="84"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="51"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="59"/>
+      <c r="AI10" s="18"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="118"/>
+      <c r="AN10" s="167"/>
+      <c r="AO10" s="167"/>
+      <c r="AP10" s="119"/>
+      <c r="AQ10" s="119"/>
+      <c r="AR10" s="119"/>
       <c r="AS10" s="11"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
@@ -5123,52 +5150,52 @@
       <c r="ACD10" s="11"/>
     </row>
     <row r="11" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="28">
+      <c r="A11" s="45">
         <v>3</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="92"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="47"/>
-      <c r="U11" s="47"/>
-      <c r="V11" s="76"/>
-      <c r="W11" s="76"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="76"/>
-      <c r="Z11" s="76"/>
-      <c r="AA11" s="89"/>
-      <c r="AB11" s="80"/>
-      <c r="AC11" s="76"/>
-      <c r="AD11" s="76"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="91"/>
-      <c r="AI11" s="83"/>
-      <c r="AJ11" s="83"/>
-      <c r="AK11" s="84"/>
-      <c r="AL11" s="86"/>
-      <c r="AM11" s="86"/>
-      <c r="AN11" s="87"/>
-      <c r="AO11" s="87"/>
-      <c r="AP11" s="88"/>
-      <c r="AQ11" s="88"/>
-      <c r="AR11" s="88"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="78"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="79"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="51"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="59"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="18"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="118"/>
+      <c r="AM11" s="118"/>
+      <c r="AN11" s="167"/>
+      <c r="AO11" s="167"/>
+      <c r="AP11" s="119"/>
+      <c r="AQ11" s="119"/>
+      <c r="AR11" s="119"/>
       <c r="AS11" s="11"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
@@ -5885,52 +5912,52 @@
       <c r="ACD11" s="11"/>
     </row>
     <row r="12" spans="1:766" ht="24" customHeight="1">
-      <c r="A12" s="28">
+      <c r="A12" s="45">
         <v>4</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="89"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="76"/>
-      <c r="Q12" s="76"/>
-      <c r="R12" s="76"/>
-      <c r="S12" s="76"/>
-      <c r="T12" s="89"/>
-      <c r="U12" s="89"/>
-      <c r="V12" s="76"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-      <c r="Y12" s="76"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="89"/>
-      <c r="AB12" s="94"/>
-      <c r="AC12" s="76"/>
-      <c r="AD12" s="76"/>
-      <c r="AE12" s="95"/>
-      <c r="AF12" s="76"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="96"/>
-      <c r="AI12" s="83"/>
-      <c r="AJ12" s="83"/>
-      <c r="AK12" s="97"/>
-      <c r="AL12" s="87"/>
-      <c r="AM12" s="97"/>
-      <c r="AN12" s="87"/>
-      <c r="AO12" s="87"/>
-      <c r="AP12" s="88"/>
-      <c r="AQ12" s="88"/>
-      <c r="AR12" s="88"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="79"/>
+      <c r="AB12" s="77"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="22"/>
+      <c r="AH12" s="61"/>
+      <c r="AI12" s="18"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="120"/>
+      <c r="AL12" s="167"/>
+      <c r="AM12" s="120"/>
+      <c r="AN12" s="167"/>
+      <c r="AO12" s="167"/>
+      <c r="AP12" s="119"/>
+      <c r="AQ12" s="119"/>
+      <c r="AR12" s="119"/>
       <c r="ACE12"/>
       <c r="ACF12"/>
       <c r="ACG12"/>
@@ -5941,52 +5968,52 @@
       <c r="ACL12"/>
     </row>
     <row r="13" spans="1:766" ht="24" customHeight="1">
-      <c r="A13" s="28">
+      <c r="A13" s="45">
         <v>5</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="76"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="89"/>
-      <c r="U13" s="184"/>
-      <c r="V13" s="76"/>
-      <c r="W13" s="76"/>
-      <c r="X13" s="12"/>
-      <c r="Y13" s="76"/>
-      <c r="Z13" s="76"/>
-      <c r="AA13" s="89"/>
-      <c r="AB13" s="94"/>
-      <c r="AC13" s="76"/>
-      <c r="AD13" s="76"/>
-      <c r="AE13" s="95"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="96"/>
-      <c r="AI13" s="83"/>
-      <c r="AJ13" s="83"/>
-      <c r="AK13" s="84"/>
-      <c r="AL13" s="86"/>
-      <c r="AM13" s="86"/>
-      <c r="AN13" s="87"/>
-      <c r="AO13" s="87"/>
-      <c r="AP13" s="88"/>
-      <c r="AQ13" s="88"/>
-      <c r="AR13" s="88"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="170"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="79"/>
+      <c r="AB13" s="77"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="61"/>
+      <c r="AI13" s="18"/>
+      <c r="AJ13" s="18"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="118"/>
+      <c r="AN13" s="167"/>
+      <c r="AO13" s="167"/>
+      <c r="AP13" s="119"/>
+      <c r="AQ13" s="119"/>
+      <c r="AR13" s="119"/>
       <c r="ACE13"/>
       <c r="ACF13"/>
       <c r="ACG13"/>
@@ -5997,52 +6024,52 @@
       <c r="ACL13"/>
     </row>
     <row r="14" spans="1:766" ht="24" customHeight="1">
-      <c r="A14" s="28">
+      <c r="A14" s="45">
         <v>6</v>
       </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="89"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="76"/>
-      <c r="P14" s="76"/>
-      <c r="Q14" s="76"/>
-      <c r="R14" s="76"/>
-      <c r="S14" s="76"/>
-      <c r="T14" s="89"/>
-      <c r="U14" s="147"/>
-      <c r="V14" s="76"/>
-      <c r="W14" s="76"/>
-      <c r="X14" s="76"/>
-      <c r="Y14" s="76"/>
-      <c r="Z14" s="76"/>
-      <c r="AA14" s="89"/>
-      <c r="AB14" s="98"/>
-      <c r="AC14" s="78"/>
-      <c r="AD14" s="76"/>
-      <c r="AE14" s="95"/>
-      <c r="AF14" s="76"/>
-      <c r="AG14" s="76"/>
-      <c r="AH14" s="96"/>
-      <c r="AI14" s="83"/>
-      <c r="AJ14" s="83"/>
-      <c r="AK14" s="83"/>
-      <c r="AL14" s="86"/>
-      <c r="AM14" s="97"/>
-      <c r="AN14" s="87"/>
-      <c r="AO14" s="87"/>
-      <c r="AP14" s="88"/>
-      <c r="AQ14" s="88"/>
-      <c r="AR14" s="88"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="166"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="121"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="61"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="118"/>
+      <c r="AM14" s="120"/>
+      <c r="AN14" s="167"/>
+      <c r="AO14" s="167"/>
+      <c r="AP14" s="119"/>
+      <c r="AQ14" s="119"/>
+      <c r="AR14" s="119"/>
       <c r="ACE14"/>
       <c r="ACF14"/>
       <c r="ACG14"/>
@@ -6053,52 +6080,52 @@
       <c r="ACL14"/>
     </row>
     <row r="15" spans="1:766" ht="24" customHeight="1">
-      <c r="A15" s="28">
+      <c r="A15" s="45">
         <v>7</v>
       </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="100"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="76"/>
-      <c r="S15" s="76"/>
-      <c r="T15" s="89"/>
-      <c r="U15" s="101"/>
-      <c r="V15" s="76"/>
-      <c r="W15" s="76"/>
-      <c r="X15" s="76"/>
-      <c r="Y15" s="76"/>
-      <c r="Z15" s="76"/>
-      <c r="AA15" s="89"/>
-      <c r="AB15" s="94"/>
-      <c r="AC15" s="76"/>
-      <c r="AD15" s="76"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="171"/>
+      <c r="P15" s="171"/>
+      <c r="Q15" s="22"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="79"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="77"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
       <c r="AE15" s="33"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="76"/>
-      <c r="AH15" s="102"/>
-      <c r="AI15" s="83"/>
-      <c r="AJ15" s="83"/>
-      <c r="AK15" s="84"/>
-      <c r="AL15" s="86"/>
-      <c r="AM15" s="86"/>
-      <c r="AN15" s="87"/>
-      <c r="AO15" s="87"/>
-      <c r="AP15" s="88"/>
-      <c r="AQ15" s="88"/>
-      <c r="AR15" s="88"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="18"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="118"/>
+      <c r="AN15" s="167"/>
+      <c r="AO15" s="167"/>
+      <c r="AP15" s="119"/>
+      <c r="AQ15" s="119"/>
+      <c r="AR15" s="119"/>
       <c r="ACE15"/>
       <c r="ACF15"/>
       <c r="ACG15"/>
@@ -6109,52 +6136,52 @@
       <c r="ACL15"/>
     </row>
     <row r="16" spans="1:766" ht="24" customHeight="1">
-      <c r="A16" s="28">
+      <c r="A16" s="45">
         <v>8</v>
       </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="75"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="89"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="89"/>
-      <c r="O16" s="76"/>
-      <c r="P16" s="76"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="101"/>
-      <c r="V16" s="76"/>
-      <c r="W16" s="76"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="94"/>
-      <c r="AC16" s="76"/>
-      <c r="AD16" s="76"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="78"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
       <c r="AE16" s="33"/>
-      <c r="AF16" s="13"/>
-      <c r="AG16" s="13"/>
-      <c r="AH16" s="102"/>
-      <c r="AI16" s="83"/>
-      <c r="AJ16" s="83"/>
-      <c r="AK16" s="103"/>
-      <c r="AL16" s="86"/>
-      <c r="AM16" s="86"/>
-      <c r="AN16" s="87"/>
-      <c r="AO16" s="87"/>
-      <c r="AP16" s="88"/>
-      <c r="AQ16" s="88"/>
-      <c r="AR16" s="88"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="18"/>
+      <c r="AJ16" s="18"/>
+      <c r="AK16" s="123"/>
+      <c r="AL16" s="118"/>
+      <c r="AM16" s="118"/>
+      <c r="AN16" s="167"/>
+      <c r="AO16" s="167"/>
+      <c r="AP16" s="119"/>
+      <c r="AQ16" s="119"/>
+      <c r="AR16" s="119"/>
       <c r="ACE16"/>
       <c r="ACF16"/>
       <c r="ACG16"/>
@@ -6165,52 +6192,52 @@
       <c r="ACL16"/>
     </row>
     <row r="17" spans="1:766" ht="24" customHeight="1">
-      <c r="A17" s="28">
+      <c r="A17" s="45">
         <v>1</v>
       </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="89"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="89"/>
-      <c r="O17" s="76"/>
-      <c r="P17" s="76"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="76"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="89"/>
-      <c r="U17" s="89"/>
-      <c r="V17" s="76"/>
-      <c r="W17" s="76"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="78"/>
-      <c r="Z17" s="105"/>
-      <c r="AA17" s="89"/>
-      <c r="AB17" s="94"/>
-      <c r="AC17" s="76"/>
-      <c r="AD17" s="76"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="79"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="79"/>
+      <c r="AB17" s="77"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
       <c r="AE17" s="33"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="13"/>
-      <c r="AH17" s="102"/>
-      <c r="AI17" s="83"/>
-      <c r="AJ17" s="83"/>
-      <c r="AK17" s="84"/>
-      <c r="AL17" s="86"/>
-      <c r="AM17" s="86"/>
-      <c r="AN17" s="87"/>
-      <c r="AO17" s="87"/>
-      <c r="AP17" s="88"/>
-      <c r="AQ17" s="88"/>
-      <c r="AR17" s="88"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="22"/>
+      <c r="AH17" s="62"/>
+      <c r="AI17" s="18"/>
+      <c r="AJ17" s="18"/>
+      <c r="AK17" s="35"/>
+      <c r="AL17" s="118"/>
+      <c r="AM17" s="118"/>
+      <c r="AN17" s="167"/>
+      <c r="AO17" s="167"/>
+      <c r="AP17" s="119"/>
+      <c r="AQ17" s="119"/>
+      <c r="AR17" s="119"/>
       <c r="ACE17"/>
       <c r="ACF17"/>
       <c r="ACG17"/>
@@ -6221,52 +6248,52 @@
       <c r="ACL17"/>
     </row>
     <row r="18" spans="1:766" ht="24" customHeight="1">
-      <c r="A18" s="28">
+      <c r="A18" s="45">
         <v>1</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="111"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="111"/>
-      <c r="W18" s="107"/>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="107"/>
-      <c r="Z18" s="107"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="107"/>
-      <c r="AD18" s="107"/>
-      <c r="AE18" s="114"/>
-      <c r="AF18" s="107"/>
-      <c r="AG18" s="107"/>
-      <c r="AH18" s="115"/>
-      <c r="AI18" s="116"/>
-      <c r="AJ18" s="116"/>
-      <c r="AK18" s="116"/>
-      <c r="AL18" s="117"/>
-      <c r="AM18" s="117"/>
-      <c r="AN18" s="118"/>
-      <c r="AO18" s="118"/>
-      <c r="AP18" s="119"/>
-      <c r="AQ18" s="119"/>
-      <c r="AR18" s="119"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="104"/>
+      <c r="U18" s="104"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="105"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="65"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="63"/>
+      <c r="AI18" s="23"/>
+      <c r="AJ18" s="23"/>
+      <c r="AK18" s="23"/>
+      <c r="AL18" s="127"/>
+      <c r="AM18" s="127"/>
+      <c r="AN18" s="128"/>
+      <c r="AO18" s="128"/>
+      <c r="AP18" s="129"/>
+      <c r="AQ18" s="129"/>
+      <c r="AR18" s="129"/>
       <c r="ACE18"/>
       <c r="ACF18"/>
       <c r="ACG18"/>
@@ -6277,52 +6304,52 @@
       <c r="ACL18"/>
     </row>
     <row r="19" spans="1:766" ht="24" customHeight="1">
-      <c r="A19" s="28">
+      <c r="A19" s="45">
         <v>2</v>
       </c>
-      <c r="B19" s="120"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="124"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="122"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="122"/>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="125"/>
-      <c r="S19" s="122"/>
-      <c r="T19" s="123"/>
-      <c r="U19" s="123"/>
-      <c r="V19" s="122"/>
-      <c r="W19" s="122"/>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="122"/>
-      <c r="Z19" s="127"/>
-      <c r="AA19" s="128"/>
-      <c r="AB19" s="129"/>
-      <c r="AC19" s="127"/>
-      <c r="AD19" s="122"/>
-      <c r="AE19" s="130"/>
-      <c r="AF19" s="122"/>
-      <c r="AG19" s="122"/>
-      <c r="AH19" s="131"/>
-      <c r="AI19" s="132"/>
-      <c r="AJ19" s="132"/>
-      <c r="AK19" s="132"/>
-      <c r="AL19" s="133"/>
-      <c r="AM19" s="133"/>
-      <c r="AN19" s="134"/>
-      <c r="AO19" s="134"/>
-      <c r="AP19" s="135"/>
-      <c r="AQ19" s="135"/>
-      <c r="AR19" s="135"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="93"/>
+      <c r="Q19" s="173"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="93"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="93"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="93"/>
+      <c r="Z19" s="97"/>
+      <c r="AA19" s="98"/>
+      <c r="AB19" s="99"/>
+      <c r="AC19" s="97"/>
+      <c r="AD19" s="93"/>
+      <c r="AE19" s="100"/>
+      <c r="AF19" s="93"/>
+      <c r="AG19" s="93"/>
+      <c r="AH19" s="101"/>
+      <c r="AI19" s="102"/>
+      <c r="AJ19" s="102"/>
+      <c r="AK19" s="102"/>
+      <c r="AL19" s="132"/>
+      <c r="AM19" s="132"/>
+      <c r="AN19" s="174"/>
+      <c r="AO19" s="174"/>
+      <c r="AP19" s="133"/>
+      <c r="AQ19" s="133"/>
+      <c r="AR19" s="133"/>
       <c r="ACE19"/>
       <c r="ACF19"/>
       <c r="ACG19"/>
@@ -6333,52 +6360,52 @@
       <c r="ACL19"/>
     </row>
     <row r="20" spans="1:766" ht="24" customHeight="1">
-      <c r="A20" s="28">
+      <c r="A20" s="45">
         <v>1</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="137"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="142"/>
-      <c r="K20" s="143"/>
-      <c r="L20" s="140"/>
-      <c r="M20" s="140"/>
-      <c r="N20" s="144"/>
-      <c r="O20" s="141"/>
-      <c r="P20" s="141"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="145"/>
-      <c r="S20" s="141"/>
-      <c r="T20" s="146"/>
-      <c r="U20" s="147"/>
-      <c r="V20" s="141"/>
-      <c r="W20" s="141"/>
-      <c r="X20" s="141"/>
-      <c r="Y20" s="145"/>
-      <c r="Z20" s="141"/>
-      <c r="AA20" s="147"/>
-      <c r="AB20" s="148"/>
-      <c r="AC20" s="141"/>
-      <c r="AD20" s="141"/>
-      <c r="AE20" s="149"/>
-      <c r="AF20" s="150"/>
-      <c r="AG20" s="150"/>
-      <c r="AH20" s="151"/>
-      <c r="AI20" s="152"/>
-      <c r="AJ20" s="152"/>
-      <c r="AK20" s="152"/>
-      <c r="AL20" s="153"/>
-      <c r="AM20" s="154"/>
-      <c r="AN20" s="155"/>
-      <c r="AO20" s="155"/>
-      <c r="AP20" s="156"/>
-      <c r="AQ20" s="156"/>
-      <c r="AR20" s="157"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="175"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="108"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="86"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="76"/>
+      <c r="AG20" s="76"/>
+      <c r="AH20" s="110"/>
+      <c r="AI20" s="19"/>
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="136"/>
+      <c r="AM20" s="137"/>
+      <c r="AN20" s="176"/>
+      <c r="AO20" s="176"/>
+      <c r="AP20" s="138"/>
+      <c r="AQ20" s="138"/>
+      <c r="AR20" s="139"/>
       <c r="ACF20"/>
       <c r="ACG20"/>
       <c r="ACH20"/>
@@ -6388,52 +6415,52 @@
       <c r="ACL20"/>
     </row>
     <row r="21" spans="1:766" ht="24" customHeight="1">
-      <c r="A21" s="28">
+      <c r="A21" s="45">
         <v>2</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="89"/>
-      <c r="O21" s="76"/>
-      <c r="P21" s="76"/>
-      <c r="Q21" s="76"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="76"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="76"/>
-      <c r="W21" s="76"/>
-      <c r="X21" s="76"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="76"/>
-      <c r="AA21" s="147"/>
-      <c r="AB21" s="148"/>
-      <c r="AC21" s="76"/>
-      <c r="AD21" s="76"/>
-      <c r="AE21" s="149"/>
-      <c r="AF21" s="141"/>
-      <c r="AG21" s="158"/>
-      <c r="AH21" s="159"/>
-      <c r="AI21" s="83"/>
-      <c r="AJ21" s="83"/>
-      <c r="AK21" s="116"/>
-      <c r="AL21" s="86"/>
-      <c r="AM21" s="117"/>
-      <c r="AN21" s="160"/>
-      <c r="AO21" s="160"/>
-      <c r="AP21" s="119"/>
-      <c r="AQ21" s="88"/>
-      <c r="AR21" s="119"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="86"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="31"/>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="177"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="18"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="23"/>
+      <c r="AL21" s="118"/>
+      <c r="AM21" s="127"/>
+      <c r="AN21" s="178"/>
+      <c r="AO21" s="178"/>
+      <c r="AP21" s="129"/>
+      <c r="AQ21" s="119"/>
+      <c r="AR21" s="129"/>
       <c r="ACF21"/>
       <c r="ACG21"/>
       <c r="ACH21"/>
@@ -6443,52 +6470,52 @@
       <c r="ACL21"/>
     </row>
     <row r="22" spans="1:766" ht="24" customHeight="1">
-      <c r="A22" s="28">
+      <c r="A22" s="45">
         <v>3</v>
       </c>
-      <c r="B22" s="161"/>
-      <c r="C22" s="162"/>
-      <c r="D22" s="163"/>
-      <c r="E22" s="163"/>
-      <c r="F22" s="164"/>
-      <c r="G22" s="165"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="89"/>
-      <c r="M22" s="108"/>
-      <c r="N22" s="108"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="76"/>
-      <c r="Q22" s="107"/>
-      <c r="R22" s="110"/>
-      <c r="S22" s="107"/>
-      <c r="T22" s="166"/>
-      <c r="U22" s="166"/>
-      <c r="V22" s="167"/>
-      <c r="W22" s="167"/>
-      <c r="X22" s="167"/>
-      <c r="Y22" s="168"/>
-      <c r="Z22" s="167"/>
-      <c r="AA22" s="169"/>
-      <c r="AB22" s="170"/>
-      <c r="AC22" s="167"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="171"/>
-      <c r="AF22" s="150"/>
-      <c r="AG22" s="12"/>
-      <c r="AH22" s="82"/>
-      <c r="AI22" s="152"/>
-      <c r="AJ22" s="172"/>
-      <c r="AK22" s="173"/>
-      <c r="AL22" s="174"/>
-      <c r="AM22" s="175"/>
-      <c r="AN22" s="176"/>
-      <c r="AO22" s="176"/>
-      <c r="AP22" s="177"/>
-      <c r="AQ22" s="178"/>
-      <c r="AR22" s="88"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="73"/>
+      <c r="AD22" s="71"/>
+      <c r="AE22" s="75"/>
+      <c r="AF22" s="76"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="19"/>
+      <c r="AJ22" s="112"/>
+      <c r="AK22" s="111"/>
+      <c r="AL22" s="142"/>
+      <c r="AM22" s="143"/>
+      <c r="AN22" s="179"/>
+      <c r="AO22" s="179"/>
+      <c r="AP22" s="180"/>
+      <c r="AQ22" s="181"/>
+      <c r="AR22" s="119"/>
       <c r="ACF22"/>
       <c r="ACG22"/>
       <c r="ACH22"/>
@@ -6498,52 +6525,52 @@
       <c r="ACL22"/>
     </row>
     <row r="23" spans="1:766" ht="24" customHeight="1">
-      <c r="A23" s="28">
+      <c r="A23" s="45">
         <v>4</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="93"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="76"/>
-      <c r="P23" s="76"/>
-      <c r="Q23" s="76"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="76"/>
-      <c r="T23" s="93"/>
-      <c r="U23" s="93"/>
-      <c r="V23" s="76"/>
-      <c r="W23" s="76"/>
-      <c r="X23" s="76"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="76"/>
-      <c r="AA23" s="89"/>
-      <c r="AB23" s="94"/>
-      <c r="AC23" s="76"/>
-      <c r="AD23" s="76"/>
-      <c r="AE23" s="95"/>
-      <c r="AF23" s="76"/>
-      <c r="AG23" s="76"/>
-      <c r="AH23" s="91"/>
-      <c r="AI23" s="152"/>
-      <c r="AJ23" s="152"/>
-      <c r="AK23" s="179"/>
-      <c r="AL23" s="180"/>
-      <c r="AM23" s="180"/>
-      <c r="AN23" s="155"/>
-      <c r="AO23" s="155"/>
-      <c r="AP23" s="156"/>
-      <c r="AQ23" s="156"/>
-      <c r="AR23" s="88"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="81"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="79"/>
+      <c r="AB23" s="77"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="59"/>
+      <c r="AI23" s="19"/>
+      <c r="AJ23" s="19"/>
+      <c r="AK23" s="49"/>
+      <c r="AL23" s="144"/>
+      <c r="AM23" s="144"/>
+      <c r="AN23" s="176"/>
+      <c r="AO23" s="176"/>
+      <c r="AP23" s="138"/>
+      <c r="AQ23" s="138"/>
+      <c r="AR23" s="119"/>
       <c r="ACF23"/>
       <c r="ACG23"/>
       <c r="ACH23"/>
@@ -6553,52 +6580,52 @@
       <c r="ACL23"/>
     </row>
     <row r="24" spans="1:766" ht="24" customHeight="1">
-      <c r="A24" s="28">
+      <c r="A24" s="45">
         <v>5</v>
       </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="163"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
-      <c r="Q24" s="76"/>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="89"/>
-      <c r="V24" s="76"/>
-      <c r="W24" s="76"/>
-      <c r="X24" s="12"/>
-      <c r="Y24" s="141"/>
-      <c r="Z24" s="12"/>
-      <c r="AA24" s="147"/>
-      <c r="AB24" s="148"/>
-      <c r="AC24" s="76"/>
-      <c r="AD24" s="76"/>
-      <c r="AE24" s="95"/>
-      <c r="AF24" s="141"/>
-      <c r="AG24" s="141"/>
-      <c r="AH24" s="96"/>
-      <c r="AI24" s="83"/>
-      <c r="AJ24" s="83"/>
-      <c r="AK24" s="84"/>
-      <c r="AL24" s="86"/>
-      <c r="AM24" s="86"/>
-      <c r="AN24" s="87"/>
-      <c r="AO24" s="87"/>
-      <c r="AP24" s="88"/>
-      <c r="AQ24" s="88"/>
-      <c r="AR24" s="88"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="86"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="61"/>
+      <c r="AI24" s="18"/>
+      <c r="AJ24" s="18"/>
+      <c r="AK24" s="35"/>
+      <c r="AL24" s="118"/>
+      <c r="AM24" s="118"/>
+      <c r="AN24" s="167"/>
+      <c r="AO24" s="167"/>
+      <c r="AP24" s="119"/>
+      <c r="AQ24" s="119"/>
+      <c r="AR24" s="119"/>
       <c r="ACF24"/>
       <c r="ACG24"/>
       <c r="ACH24"/>
@@ -6608,52 +6635,52 @@
       <c r="ACL24"/>
     </row>
     <row r="25" spans="1:766" ht="24" customHeight="1">
-      <c r="A25" s="28">
+      <c r="A25" s="45">
         <v>1</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="165"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="165"/>
-      <c r="O25" s="76"/>
-      <c r="P25" s="76"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="107"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="165"/>
-      <c r="U25" s="165"/>
-      <c r="V25" s="76"/>
-      <c r="W25" s="76"/>
-      <c r="X25" s="110"/>
-      <c r="Y25" s="107"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="165"/>
-      <c r="AB25" s="181"/>
-      <c r="AC25" s="76"/>
-      <c r="AD25" s="76"/>
-      <c r="AE25" s="114"/>
-      <c r="AF25" s="107"/>
-      <c r="AG25" s="110"/>
-      <c r="AH25" s="91"/>
-      <c r="AI25" s="83"/>
-      <c r="AJ25" s="83"/>
-      <c r="AK25" s="84"/>
-      <c r="AL25" s="85"/>
-      <c r="AM25" s="86"/>
-      <c r="AN25" s="182"/>
-      <c r="AO25" s="182"/>
-      <c r="AP25" s="183"/>
-      <c r="AQ25" s="88"/>
-      <c r="AR25" s="88"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="15"/>
+      <c r="T25" s="83"/>
+      <c r="U25" s="83"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="83"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="65"/>
+      <c r="AF25" s="20"/>
+      <c r="AG25" s="15"/>
+      <c r="AH25" s="59"/>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="35"/>
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="118"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="145"/>
+      <c r="AQ25" s="119"/>
+      <c r="AR25" s="119"/>
       <c r="ACF25"/>
       <c r="ACG25"/>
       <c r="ACH25"/>
@@ -6663,728 +6690,728 @@
       <c r="ACL25"/>
     </row>
     <row r="26" spans="1:766" ht="24" customHeight="1">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="32"/>
-      <c r="AD26" s="32"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="43"/>
-      <c r="AN26" s="43"/>
-      <c r="AO26" s="43"/>
-      <c r="AP26" s="43"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
+      <c r="AB26" s="46"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="50"/>
+      <c r="AE26" s="46"/>
+      <c r="AF26" s="46"/>
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="68"/>
+      <c r="AI26" s="68"/>
+      <c r="AJ26" s="68"/>
+      <c r="AK26" s="68"/>
+      <c r="AL26" s="68"/>
+      <c r="AM26" s="68"/>
+      <c r="AN26" s="68"/>
+      <c r="AO26" s="68"/>
+      <c r="AP26" s="68"/>
     </row>
     <row r="27" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B27" s="26"/>
-      <c r="C27" s="26" t="s">
+      <c r="B27" s="43"/>
+      <c r="C27" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="43">
         <f>COUNTIF(D9:D19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="43">
         <f>COUNTIF(E9:E19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="43">
         <f>COUNTIF(F9:F19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="43">
         <f t="shared" ref="F27:AH27" si="0">COUNTIF(G9:G19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="43">
         <f>COUNTIF(I9:I19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27" s="26">
+      <c r="R27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S27" s="26">
+      <c r="S27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T27" s="26">
+      <c r="T27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U27" s="26">
+      <c r="U27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="26">
+      <c r="V27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="26">
+      <c r="W27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="26">
+      <c r="X27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="26">
+      <c r="Y27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="26">
+      <c r="Z27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="26">
+      <c r="AA27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="26">
+      <c r="AB27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="26">
+      <c r="AC27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="26">
+      <c r="AD27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="26">
+      <c r="AE27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="26">
+      <c r="AF27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="26">
+      <c r="AG27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="17">
+      <c r="AH27" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="17"/>
-      <c r="AJ27" s="17"/>
-      <c r="AK27" s="17"/>
-      <c r="AL27" s="17"/>
-      <c r="AM27" s="17"/>
-      <c r="AN27" s="17"/>
-      <c r="AO27" s="17"/>
-      <c r="AP27" s="43"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="27"/>
+      <c r="AK27" s="27"/>
+      <c r="AL27" s="27"/>
+      <c r="AM27" s="27"/>
+      <c r="AN27" s="27"/>
+      <c r="AO27" s="27"/>
+      <c r="AP27" s="68"/>
     </row>
     <row r="28" spans="1:766" ht="12.75" customHeight="1">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="27">
         <f t="shared" ref="D28:AH28" si="1">COUNTIF(D9:D19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="27">
         <f>COUNTIF(I9:I19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P28" s="17">
+      <c r="P28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="17">
+      <c r="R28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S28" s="17">
+      <c r="S28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T28" s="17">
+      <c r="T28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="17">
+      <c r="U28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V28" s="17">
+      <c r="V28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="17">
+      <c r="W28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X28" s="17">
+      <c r="X28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="17">
+      <c r="Y28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="17">
+      <c r="AA28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="17">
+      <c r="AB28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="17">
+      <c r="AC28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="17">
+      <c r="AD28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="17">
+      <c r="AE28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="17">
+      <c r="AF28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="17">
+      <c r="AG28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="17">
+      <c r="AH28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="17"/>
-      <c r="AJ28" s="17"/>
-      <c r="AK28" s="17"/>
-      <c r="AL28" s="17"/>
-      <c r="AM28" s="17"/>
-      <c r="AN28" s="17"/>
-      <c r="AO28" s="17"/>
-      <c r="AP28" s="43"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="27"/>
+      <c r="AL28" s="27"/>
+      <c r="AM28" s="27"/>
+      <c r="AN28" s="27"/>
+      <c r="AO28" s="27"/>
+      <c r="AP28" s="68"/>
     </row>
     <row r="29" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17" t="s">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="27">
         <f t="shared" ref="D29:AH29" si="2">COUNTIF(D9:D19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="27">
         <f>COUNTIF(I9:I19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M29" s="17">
+      <c r="M29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P29" s="17">
+      <c r="P29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="27">
         <v>2</v>
       </c>
-      <c r="R29" s="17">
+      <c r="R29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="17">
+      <c r="S29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T29" s="17">
+      <c r="T29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U29" s="17">
+      <c r="U29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V29" s="17">
+      <c r="V29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W29" s="17">
+      <c r="W29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X29" s="17">
+      <c r="X29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="17">
+      <c r="Y29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="17">
+      <c r="Z29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="17">
+      <c r="AA29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="17">
+      <c r="AB29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="17">
+      <c r="AC29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="17">
+      <c r="AD29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="17">
+      <c r="AE29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="17">
+      <c r="AF29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="17">
+      <c r="AG29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="17">
+      <c r="AH29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="17"/>
-      <c r="AJ29" s="17"/>
-      <c r="AK29" s="17"/>
-      <c r="AL29" s="17"/>
-      <c r="AM29" s="17"/>
-      <c r="AN29" s="17"/>
-      <c r="AO29" s="17"/>
-      <c r="AP29" s="43"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="27"/>
+      <c r="AK29" s="27"/>
+      <c r="AL29" s="27"/>
+      <c r="AM29" s="27"/>
+      <c r="AN29" s="27"/>
+      <c r="AO29" s="27"/>
+      <c r="AP29" s="68"/>
     </row>
     <row r="30" spans="1:766" ht="12" customHeight="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="27">
         <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="17">
+      <c r="M30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="27">
         <f>COUNTIF(N9:N25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="17">
+      <c r="P30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="17">
+      <c r="R30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S30" s="17">
+      <c r="S30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="17">
+      <c r="U30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V30" s="17">
+      <c r="V30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W30" s="17">
+      <c r="W30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X30" s="17">
+      <c r="X30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y30" s="17">
+      <c r="Y30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="17">
+      <c r="Z30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="17">
+      <c r="AA30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="17">
+      <c r="AB30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="17">
+      <c r="AC30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="17">
+      <c r="AD30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="17">
+      <c r="AE30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="17">
+      <c r="AF30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="17">
+      <c r="AG30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="17">
+      <c r="AH30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="17"/>
-      <c r="AJ30" s="17"/>
-      <c r="AK30" s="17"/>
-      <c r="AL30" s="17"/>
-      <c r="AM30" s="17"/>
-      <c r="AN30" s="17"/>
-      <c r="AO30" s="17"/>
-      <c r="AP30" s="43"/>
+      <c r="AI30" s="27"/>
+      <c r="AJ30" s="27"/>
+      <c r="AK30" s="27"/>
+      <c r="AL30" s="27"/>
+      <c r="AM30" s="27"/>
+      <c r="AN30" s="27"/>
+      <c r="AO30" s="27"/>
+      <c r="AP30" s="68"/>
     </row>
     <row r="31" spans="1:766">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
-      <c r="AE31" s="20"/>
-      <c r="AF31" s="20"/>
-      <c r="AG31" s="20"/>
-      <c r="AH31" s="20"/>
-      <c r="AI31" s="20"/>
-      <c r="AJ31" s="20"/>
-      <c r="AK31" s="20"/>
-      <c r="AL31" s="44"/>
-      <c r="AO31" s="42"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="69"/>
+      <c r="AO31" s="67"/>
     </row>
     <row r="32" spans="1:766">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="18"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="18"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="18"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="18"/>
-      <c r="AC32" s="18"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="18"/>
-      <c r="AF32" s="18"/>
-      <c r="AG32" s="18"/>
-      <c r="AH32" s="18"/>
-      <c r="AI32" s="18"/>
-      <c r="AJ32" s="18"/>
-      <c r="AK32" s="18"/>
-      <c r="AL32" s="44"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
+      <c r="AD32" s="28"/>
+      <c r="AE32" s="28"/>
+      <c r="AF32" s="28"/>
+      <c r="AG32" s="28"/>
+      <c r="AH32" s="28"/>
+      <c r="AI32" s="28"/>
+      <c r="AJ32" s="28"/>
+      <c r="AK32" s="28"/>
+      <c r="AL32" s="69"/>
     </row>
     <row r="33" spans="1:767" s="2" customFormat="1">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="18"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="18"/>
-      <c r="AC33" s="18"/>
-      <c r="AD33" s="18"/>
-      <c r="AE33" s="18"/>
-      <c r="AF33" s="18"/>
-      <c r="AG33" s="18"/>
-      <c r="AH33" s="18"/>
-      <c r="AI33" s="18"/>
-      <c r="AJ33" s="18"/>
-      <c r="AK33" s="18"/>
-      <c r="AL33" s="44"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
+      <c r="AD33" s="28"/>
+      <c r="AE33" s="28"/>
+      <c r="AF33" s="28"/>
+      <c r="AG33" s="28"/>
+      <c r="AH33" s="28"/>
+      <c r="AI33" s="28"/>
+      <c r="AJ33" s="28"/>
+      <c r="AK33" s="28"/>
+      <c r="AL33" s="69"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
-      <c r="AR33" s="21"/>
+      <c r="AR33" s="38"/>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -8110,50 +8137,50 @@
       <c r="ACM33"/>
     </row>
     <row r="34" spans="1:767" s="2" customFormat="1">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="18"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="18"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="18"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="18"/>
-      <c r="AC34" s="18"/>
-      <c r="AD34" s="18"/>
-      <c r="AE34" s="18"/>
-      <c r="AF34" s="18"/>
-      <c r="AG34" s="18"/>
-      <c r="AH34" s="18"/>
-      <c r="AI34" s="18"/>
-      <c r="AJ34" s="18"/>
-      <c r="AK34" s="18"/>
-      <c r="AL34" s="44"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+      <c r="AB34" s="28"/>
+      <c r="AC34" s="28"/>
+      <c r="AD34" s="28"/>
+      <c r="AE34" s="28"/>
+      <c r="AF34" s="28"/>
+      <c r="AG34" s="28"/>
+      <c r="AH34" s="28"/>
+      <c r="AI34" s="28"/>
+      <c r="AJ34" s="28"/>
+      <c r="AK34" s="28"/>
+      <c r="AL34" s="69"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="21"/>
+      <c r="AR34" s="38"/>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
@@ -8879,50 +8906,50 @@
       <c r="ACM34"/>
     </row>
     <row r="35" spans="1:767" s="2" customFormat="1">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="18"/>
-      <c r="Q35" s="18"/>
-      <c r="R35" s="18"/>
-      <c r="S35" s="18"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="18"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="18"/>
-      <c r="AC35" s="18"/>
-      <c r="AD35" s="18"/>
-      <c r="AE35" s="18"/>
-      <c r="AF35" s="18"/>
-      <c r="AG35" s="18"/>
-      <c r="AH35" s="18"/>
-      <c r="AI35" s="18"/>
-      <c r="AJ35" s="18"/>
-      <c r="AK35" s="18"/>
-      <c r="AL35" s="44"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
+      <c r="AD35" s="28"/>
+      <c r="AE35" s="28"/>
+      <c r="AF35" s="28"/>
+      <c r="AG35" s="28"/>
+      <c r="AH35" s="28"/>
+      <c r="AI35" s="28"/>
+      <c r="AJ35" s="28"/>
+      <c r="AK35" s="28"/>
+      <c r="AL35" s="69"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
-      <c r="AR35" s="21"/>
+      <c r="AR35" s="38"/>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
@@ -9648,50 +9675,50 @@
       <c r="ACM35"/>
     </row>
     <row r="36" spans="1:767" s="2" customFormat="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="18"/>
-      <c r="S36" s="18"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
-      <c r="W36" s="18"/>
-      <c r="X36" s="18"/>
-      <c r="Y36" s="18"/>
-      <c r="Z36" s="18"/>
-      <c r="AA36" s="18"/>
-      <c r="AB36" s="18"/>
-      <c r="AC36" s="18"/>
-      <c r="AD36" s="18"/>
-      <c r="AE36" s="18"/>
-      <c r="AF36" s="18"/>
-      <c r="AG36" s="18"/>
-      <c r="AH36" s="18"/>
-      <c r="AI36" s="18"/>
-      <c r="AJ36" s="18"/>
-      <c r="AK36" s="18"/>
-      <c r="AL36" s="44"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
+      <c r="AD36" s="28"/>
+      <c r="AE36" s="28"/>
+      <c r="AF36" s="28"/>
+      <c r="AG36" s="28"/>
+      <c r="AH36" s="28"/>
+      <c r="AI36" s="28"/>
+      <c r="AJ36" s="28"/>
+      <c r="AK36" s="28"/>
+      <c r="AL36" s="69"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
-      <c r="AR36" s="21"/>
+      <c r="AR36" s="38"/>
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
@@ -10417,50 +10444,50 @@
       <c r="ACM36"/>
     </row>
     <row r="37" spans="1:767" s="2" customFormat="1">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="18"/>
-      <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="18"/>
-      <c r="AG37" s="18"/>
-      <c r="AH37" s="18"/>
-      <c r="AI37" s="18"/>
-      <c r="AJ37" s="18"/>
-      <c r="AK37" s="18"/>
-      <c r="AL37" s="44"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="AH37" s="28"/>
+      <c r="AI37" s="28"/>
+      <c r="AJ37" s="28"/>
+      <c r="AK37" s="28"/>
+      <c r="AL37" s="69"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
-      <c r="AR37" s="21"/>
+      <c r="AR37" s="38"/>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
@@ -11186,50 +11213,50 @@
       <c r="ACM37"/>
     </row>
     <row r="38" spans="1:767" s="2" customFormat="1">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18"/>
-      <c r="AB38" s="18"/>
-      <c r="AC38" s="18"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="18"/>
-      <c r="AF38" s="18"/>
-      <c r="AG38" s="18"/>
-      <c r="AH38" s="18"/>
-      <c r="AI38" s="18"/>
-      <c r="AJ38" s="18"/>
-      <c r="AK38" s="18"/>
-      <c r="AL38" s="44"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
+      <c r="AD38" s="28"/>
+      <c r="AE38" s="28"/>
+      <c r="AF38" s="28"/>
+      <c r="AG38" s="28"/>
+      <c r="AH38" s="28"/>
+      <c r="AI38" s="28"/>
+      <c r="AJ38" s="28"/>
+      <c r="AK38" s="28"/>
+      <c r="AL38" s="69"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
-      <c r="AR38" s="21"/>
+      <c r="AR38" s="38"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
@@ -11955,50 +11982,50 @@
       <c r="ACM38"/>
     </row>
     <row r="39" spans="1:767" s="2" customFormat="1">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18"/>
-      <c r="AB39" s="18"/>
-      <c r="AC39" s="18"/>
-      <c r="AD39" s="18"/>
-      <c r="AE39" s="18"/>
-      <c r="AF39" s="18"/>
-      <c r="AG39" s="18"/>
-      <c r="AH39" s="18"/>
-      <c r="AI39" s="18"/>
-      <c r="AJ39" s="18"/>
-      <c r="AK39" s="18"/>
-      <c r="AL39" s="44"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
+      <c r="AD39" s="28"/>
+      <c r="AE39" s="28"/>
+      <c r="AF39" s="28"/>
+      <c r="AG39" s="28"/>
+      <c r="AH39" s="28"/>
+      <c r="AI39" s="28"/>
+      <c r="AJ39" s="28"/>
+      <c r="AK39" s="28"/>
+      <c r="AL39" s="69"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
-      <c r="AR39" s="21"/>
+      <c r="AR39" s="38"/>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
@@ -12724,50 +12751,50 @@
       <c r="ACM39"/>
     </row>
     <row r="40" spans="1:767" s="2" customFormat="1">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-      <c r="L40" s="18"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18"/>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="18"/>
-      <c r="AD40" s="18"/>
-      <c r="AE40" s="18"/>
-      <c r="AF40" s="18"/>
-      <c r="AG40" s="18"/>
-      <c r="AH40" s="18"/>
-      <c r="AI40" s="18"/>
-      <c r="AJ40" s="18"/>
-      <c r="AK40" s="18"/>
-      <c r="AL40" s="44"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
+      <c r="AD40" s="28"/>
+      <c r="AE40" s="28"/>
+      <c r="AF40" s="28"/>
+      <c r="AG40" s="28"/>
+      <c r="AH40" s="28"/>
+      <c r="AI40" s="28"/>
+      <c r="AJ40" s="28"/>
+      <c r="AK40" s="28"/>
+      <c r="AL40" s="69"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
-      <c r="AR40" s="21"/>
+      <c r="AR40" s="38"/>
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
@@ -13493,50 +13520,50 @@
       <c r="ACM40"/>
     </row>
     <row r="41" spans="1:767" s="2" customFormat="1">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="18"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18"/>
-      <c r="AB41" s="18"/>
-      <c r="AC41" s="18"/>
-      <c r="AD41" s="18"/>
-      <c r="AE41" s="18"/>
-      <c r="AF41" s="18"/>
-      <c r="AG41" s="18"/>
-      <c r="AH41" s="18"/>
-      <c r="AI41" s="18"/>
-      <c r="AJ41" s="18"/>
-      <c r="AK41" s="18"/>
-      <c r="AL41" s="44"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="28"/>
+      <c r="AA41" s="28"/>
+      <c r="AB41" s="28"/>
+      <c r="AC41" s="28"/>
+      <c r="AD41" s="28"/>
+      <c r="AE41" s="28"/>
+      <c r="AF41" s="28"/>
+      <c r="AG41" s="28"/>
+      <c r="AH41" s="28"/>
+      <c r="AI41" s="28"/>
+      <c r="AJ41" s="28"/>
+      <c r="AK41" s="28"/>
+      <c r="AL41" s="69"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
-      <c r="AR41" s="21"/>
+      <c r="AR41" s="38"/>
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
@@ -14262,50 +14289,50 @@
       <c r="ACM41"/>
     </row>
     <row r="42" spans="1:767" s="2" customFormat="1">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18"/>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="18"/>
-      <c r="Z42" s="18"/>
-      <c r="AA42" s="18"/>
-      <c r="AB42" s="18"/>
-      <c r="AC42" s="18"/>
-      <c r="AD42" s="18"/>
-      <c r="AE42" s="18"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="18"/>
-      <c r="AH42" s="18"/>
-      <c r="AI42" s="18"/>
-      <c r="AJ42" s="18"/>
-      <c r="AK42" s="18"/>
-      <c r="AL42" s="44"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+      <c r="AE42" s="28"/>
+      <c r="AF42" s="28"/>
+      <c r="AG42" s="28"/>
+      <c r="AH42" s="28"/>
+      <c r="AI42" s="28"/>
+      <c r="AJ42" s="28"/>
+      <c r="AK42" s="28"/>
+      <c r="AL42" s="69"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
-      <c r="AR42" s="21"/>
+      <c r="AR42" s="38"/>
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
@@ -15031,50 +15058,50 @@
       <c r="ACM42"/>
     </row>
     <row r="43" spans="1:767" s="2" customFormat="1">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="18"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="18"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="18"/>
-      <c r="AL43" s="44"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
+      <c r="AC43" s="28"/>
+      <c r="AD43" s="28"/>
+      <c r="AE43" s="28"/>
+      <c r="AF43" s="28"/>
+      <c r="AG43" s="28"/>
+      <c r="AH43" s="28"/>
+      <c r="AI43" s="28"/>
+      <c r="AJ43" s="28"/>
+      <c r="AK43" s="28"/>
+      <c r="AL43" s="69"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
-      <c r="AR43" s="21"/>
+      <c r="AR43" s="38"/>
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
@@ -15800,50 +15827,50 @@
       <c r="ACM43"/>
     </row>
     <row r="44" spans="1:767" s="2" customFormat="1">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18"/>
-      <c r="L44" s="18"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
-      <c r="R44" s="18"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="18"/>
-      <c r="V44" s="18"/>
-      <c r="W44" s="18"/>
-      <c r="X44" s="18"/>
-      <c r="Y44" s="18"/>
-      <c r="Z44" s="18"/>
-      <c r="AA44" s="18"/>
-      <c r="AB44" s="18"/>
-      <c r="AC44" s="18"/>
-      <c r="AD44" s="18"/>
-      <c r="AE44" s="18"/>
-      <c r="AF44" s="18"/>
-      <c r="AG44" s="18"/>
-      <c r="AH44" s="18"/>
-      <c r="AI44" s="18"/>
-      <c r="AJ44" s="18"/>
-      <c r="AK44" s="18"/>
-      <c r="AL44" s="44"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28"/>
+      <c r="V44" s="28"/>
+      <c r="W44" s="28"/>
+      <c r="X44" s="28"/>
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="28"/>
+      <c r="AA44" s="28"/>
+      <c r="AB44" s="28"/>
+      <c r="AC44" s="28"/>
+      <c r="AD44" s="28"/>
+      <c r="AE44" s="28"/>
+      <c r="AF44" s="28"/>
+      <c r="AG44" s="28"/>
+      <c r="AH44" s="28"/>
+      <c r="AI44" s="28"/>
+      <c r="AJ44" s="28"/>
+      <c r="AK44" s="28"/>
+      <c r="AL44" s="69"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
-      <c r="AR44" s="21"/>
+      <c r="AR44" s="38"/>
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
@@ -16569,50 +16596,50 @@
       <c r="ACM44"/>
     </row>
     <row r="45" spans="1:767" s="2" customFormat="1">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="18"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="18"/>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="18"/>
-      <c r="AH45" s="18"/>
-      <c r="AI45" s="18"/>
-      <c r="AJ45" s="18"/>
-      <c r="AK45" s="18"/>
-      <c r="AL45" s="44"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="28"/>
+      <c r="AA45" s="28"/>
+      <c r="AB45" s="28"/>
+      <c r="AC45" s="28"/>
+      <c r="AD45" s="28"/>
+      <c r="AE45" s="28"/>
+      <c r="AF45" s="28"/>
+      <c r="AG45" s="28"/>
+      <c r="AH45" s="28"/>
+      <c r="AI45" s="28"/>
+      <c r="AJ45" s="28"/>
+      <c r="AK45" s="28"/>
+      <c r="AL45" s="69"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
-      <c r="AR45" s="21"/>
+      <c r="AR45" s="38"/>
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
@@ -17338,50 +17365,50 @@
       <c r="ACM45"/>
     </row>
     <row r="46" spans="1:767" s="2" customFormat="1">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="18"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="18"/>
-      <c r="AD46" s="18"/>
-      <c r="AE46" s="18"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="18"/>
-      <c r="AH46" s="18"/>
-      <c r="AI46" s="18"/>
-      <c r="AJ46" s="18"/>
-      <c r="AK46" s="18"/>
-      <c r="AL46" s="44"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
+      <c r="AD46" s="28"/>
+      <c r="AE46" s="28"/>
+      <c r="AF46" s="28"/>
+      <c r="AG46" s="28"/>
+      <c r="AH46" s="28"/>
+      <c r="AI46" s="28"/>
+      <c r="AJ46" s="28"/>
+      <c r="AK46" s="28"/>
+      <c r="AL46" s="69"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
-      <c r="AR46" s="21"/>
+      <c r="AR46" s="38"/>
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
@@ -18107,50 +18134,50 @@
       <c r="ACM46"/>
     </row>
     <row r="47" spans="1:767" s="2" customFormat="1">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
-      <c r="H47" s="18"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-      <c r="K47" s="18"/>
-      <c r="L47" s="18"/>
-      <c r="M47" s="18"/>
-      <c r="N47" s="18"/>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="18"/>
-      <c r="AH47" s="18"/>
-      <c r="AI47" s="18"/>
-      <c r="AJ47" s="18"/>
-      <c r="AK47" s="18"/>
-      <c r="AL47" s="44"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="28"/>
+      <c r="U47" s="28"/>
+      <c r="V47" s="28"/>
+      <c r="W47" s="28"/>
+      <c r="X47" s="28"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="28"/>
+      <c r="AA47" s="28"/>
+      <c r="AB47" s="28"/>
+      <c r="AC47" s="28"/>
+      <c r="AD47" s="28"/>
+      <c r="AE47" s="28"/>
+      <c r="AF47" s="28"/>
+      <c r="AG47" s="28"/>
+      <c r="AH47" s="28"/>
+      <c r="AI47" s="28"/>
+      <c r="AJ47" s="28"/>
+      <c r="AK47" s="28"/>
+      <c r="AL47" s="69"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
-      <c r="AR47" s="21"/>
+      <c r="AR47" s="38"/>
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
@@ -18876,50 +18903,50 @@
       <c r="ACM47"/>
     </row>
     <row r="48" spans="1:767" s="2" customFormat="1">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-      <c r="N48" s="18"/>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="18"/>
-      <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="18"/>
-      <c r="Z48" s="18"/>
-      <c r="AA48" s="18"/>
-      <c r="AB48" s="18"/>
-      <c r="AC48" s="18"/>
-      <c r="AD48" s="18"/>
-      <c r="AE48" s="18"/>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="18"/>
-      <c r="AH48" s="18"/>
-      <c r="AI48" s="18"/>
-      <c r="AJ48" s="18"/>
-      <c r="AK48" s="18"/>
-      <c r="AL48" s="44"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="28"/>
+      <c r="W48" s="28"/>
+      <c r="X48" s="28"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="28"/>
+      <c r="AA48" s="28"/>
+      <c r="AB48" s="28"/>
+      <c r="AC48" s="28"/>
+      <c r="AD48" s="28"/>
+      <c r="AE48" s="28"/>
+      <c r="AF48" s="28"/>
+      <c r="AG48" s="28"/>
+      <c r="AH48" s="28"/>
+      <c r="AI48" s="28"/>
+      <c r="AJ48" s="28"/>
+      <c r="AK48" s="28"/>
+      <c r="AL48" s="69"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
-      <c r="AR48" s="21"/>
+      <c r="AR48" s="38"/>
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
@@ -19645,50 +19672,50 @@
       <c r="ACM48"/>
     </row>
     <row r="49" spans="1:767" s="2" customFormat="1">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
-      <c r="N49" s="18"/>
-      <c r="O49" s="18"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="18"/>
-      <c r="R49" s="18"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="18"/>
-      <c r="V49" s="18"/>
-      <c r="W49" s="18"/>
-      <c r="X49" s="18"/>
-      <c r="Y49" s="18"/>
-      <c r="Z49" s="18"/>
-      <c r="AA49" s="18"/>
-      <c r="AB49" s="18"/>
-      <c r="AC49" s="18"/>
-      <c r="AD49" s="18"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="18"/>
-      <c r="AH49" s="18"/>
-      <c r="AI49" s="18"/>
-      <c r="AJ49" s="18"/>
-      <c r="AK49" s="18"/>
-      <c r="AL49" s="44"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="28"/>
+      <c r="AH49" s="28"/>
+      <c r="AI49" s="28"/>
+      <c r="AJ49" s="28"/>
+      <c r="AK49" s="28"/>
+      <c r="AL49" s="69"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
-      <c r="AR49" s="21"/>
+      <c r="AR49" s="38"/>
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
@@ -20414,50 +20441,50 @@
       <c r="ACM49"/>
     </row>
     <row r="50" spans="1:767" s="2" customFormat="1">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="18"/>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="18"/>
-      <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
-      <c r="Z50" s="18"/>
-      <c r="AA50" s="18"/>
-      <c r="AB50" s="18"/>
-      <c r="AC50" s="18"/>
-      <c r="AD50" s="18"/>
-      <c r="AE50" s="18"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="18"/>
-      <c r="AH50" s="18"/>
-      <c r="AI50" s="18"/>
-      <c r="AJ50" s="18"/>
-      <c r="AK50" s="18"/>
-      <c r="AL50" s="44"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="28"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+      <c r="AC50" s="28"/>
+      <c r="AD50" s="28"/>
+      <c r="AE50" s="28"/>
+      <c r="AF50" s="28"/>
+      <c r="AG50" s="28"/>
+      <c r="AH50" s="28"/>
+      <c r="AI50" s="28"/>
+      <c r="AJ50" s="28"/>
+      <c r="AK50" s="28"/>
+      <c r="AL50" s="69"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
       <c r="AO50" s="3"/>
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
-      <c r="AR50" s="21"/>
+      <c r="AR50" s="38"/>
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>

--- a/nurse_scheduler_template.xlsx
+++ b/nurse_scheduler_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A966DE56-6147-4528-B1E5-52A89A86012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2050D00-9B3C-40B6-8044-E56CBF5530D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B332721F-AB2B-4BF1-A12F-4722F279DAC4}"/>
   </bookViews>
@@ -176,7 +176,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-412]General"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -272,6 +272,14 @@
       <charset val="129"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
@@ -297,6 +305,28 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -384,26 +414,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C5700"/>
-      <name val="Dotum"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -726,6 +736,21 @@
       </diagonal>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -790,41 +815,26 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -851,42 +861,55 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -902,47 +925,88 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="13" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -953,66 +1017,116 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="26" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1024,238 +1138,13 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1309,64 +1198,252 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="10" xfId="5" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="31" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="3" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="28" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="6" xfId="2" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1690,13 +1767,13 @@
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.44140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="3.6640625" style="24" customWidth="1"/>
+    <col min="4" max="5" width="3.6640625" style="29" customWidth="1"/>
     <col min="6" max="13" width="3.6640625" style="3" customWidth="1"/>
-    <col min="14" max="17" width="3.6640625" style="24" customWidth="1"/>
+    <col min="14" max="17" width="3.6640625" style="29" customWidth="1"/>
     <col min="18" max="18" width="3.6640625" style="3" customWidth="1"/>
-    <col min="19" max="32" width="3.6640625" style="24" customWidth="1"/>
-    <col min="33" max="33" width="3.44140625" style="24" customWidth="1"/>
-    <col min="34" max="34" width="3.5546875" style="24" customWidth="1"/>
+    <col min="19" max="32" width="3.6640625" style="29" customWidth="1"/>
+    <col min="33" max="33" width="3.44140625" style="29" customWidth="1"/>
+    <col min="34" max="34" width="3.5546875" style="29" customWidth="1"/>
     <col min="35" max="35" width="3" style="3" customWidth="1"/>
     <col min="36" max="36" width="3" style="2" customWidth="1"/>
     <col min="37" max="37" width="4.5546875" style="2" customWidth="1"/>
@@ -1706,7 +1783,7 @@
     <col min="41" max="41" width="7.5546875" style="3" customWidth="1"/>
     <col min="42" max="42" width="6.88671875" style="3" customWidth="1"/>
     <col min="43" max="43" width="7.5546875" style="3" customWidth="1"/>
-    <col min="44" max="44" width="5.44140625" style="38" customWidth="1"/>
+    <col min="44" max="44" width="5.44140625" style="45" customWidth="1"/>
     <col min="45" max="765" width="7.5546875" style="3" customWidth="1"/>
     <col min="766" max="766" width="8.88671875" style="3" customWidth="1"/>
     <col min="767" max="767" width="8.88671875" customWidth="1"/>
@@ -1746,93 +1823,93 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
-      <c r="AI1" s="69"/>
-      <c r="AJ1" s="69"/>
-      <c r="AK1" s="69"/>
-      <c r="AL1" s="69"/>
-      <c r="AV1" s="48"/>
-      <c r="AW1" s="48"/>
+      <c r="AI1" s="107"/>
+      <c r="AJ1" s="107"/>
+      <c r="AK1" s="107"/>
+      <c r="AL1" s="107"/>
+      <c r="AV1" s="70"/>
+      <c r="AW1" s="70"/>
     </row>
     <row r="2" spans="1:766" ht="49.5" customHeight="1">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="151"/>
-      <c r="R2" s="151"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="151"/>
-      <c r="X2" s="151"/>
-      <c r="Y2" s="151"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="151"/>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="151"/>
-      <c r="AF2" s="151"/>
-      <c r="AG2" s="151"/>
-      <c r="AH2" s="151"/>
-      <c r="AI2" s="151"/>
-      <c r="AJ2" s="151"/>
-      <c r="AK2" s="151"/>
-      <c r="AL2" s="151"/>
-      <c r="AM2" s="151"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
+      <c r="AE2" s="114"/>
+      <c r="AF2" s="114"/>
+      <c r="AG2" s="114"/>
+      <c r="AH2" s="114"/>
+      <c r="AI2" s="114"/>
+      <c r="AJ2" s="114"/>
+      <c r="AK2" s="114"/>
+      <c r="AL2" s="114"/>
+      <c r="AM2" s="114"/>
     </row>
     <row r="3" spans="1:766" ht="6" customHeight="1" thickBot="1">
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="115"/>
-      <c r="T3" s="115"/>
-      <c r="U3" s="115"/>
-      <c r="V3" s="115"/>
-      <c r="W3" s="115"/>
-      <c r="X3" s="115"/>
-      <c r="Y3" s="115"/>
-      <c r="Z3" s="115"/>
-      <c r="AA3" s="115"/>
-      <c r="AB3" s="115"/>
-      <c r="AC3" s="115"/>
-      <c r="AD3" s="115"/>
-      <c r="AE3" s="115"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="115"/>
-      <c r="AH3" s="115"/>
-      <c r="AI3" s="115"/>
-      <c r="AJ3" s="115"/>
-      <c r="AK3" s="115"/>
-      <c r="AL3" s="115"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
+      <c r="R3" s="103"/>
+      <c r="S3" s="103"/>
+      <c r="T3" s="103"/>
+      <c r="U3" s="103"/>
+      <c r="V3" s="103"/>
+      <c r="W3" s="103"/>
+      <c r="X3" s="103"/>
+      <c r="Y3" s="103"/>
+      <c r="Z3" s="103"/>
+      <c r="AA3" s="103"/>
+      <c r="AB3" s="103"/>
+      <c r="AC3" s="103"/>
+      <c r="AD3" s="103"/>
+      <c r="AE3" s="103"/>
+      <c r="AF3" s="103"/>
+      <c r="AG3" s="103"/>
+      <c r="AH3" s="103"/>
+      <c r="AI3" s="103"/>
+      <c r="AJ3" s="103"/>
+      <c r="AK3" s="103"/>
+      <c r="AL3" s="103"/>
     </row>
     <row r="4" spans="1:766" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="4"/>
@@ -1858,42 +1935,42 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
-      <c r="Z4" s="152"/>
-      <c r="AA4" s="152"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="70"/>
-      <c r="AE4" s="153" t="s">
+      <c r="AD4" s="108"/>
+      <c r="AE4" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="AF4" s="154"/>
-      <c r="AG4" s="155" t="s">
+      <c r="AF4" s="117"/>
+      <c r="AG4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="AH4" s="156"/>
-      <c r="AR4" s="38"/>
+      <c r="AH4" s="119"/>
+      <c r="AR4" s="45"/>
     </row>
     <row r="5" spans="1:766" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="B5" s="157" t="s">
+      <c r="B5" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="159"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="122"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="160" t="s">
+      <c r="H5" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="161"/>
-      <c r="N5" s="161"/>
-      <c r="O5" s="161"/>
-      <c r="P5" s="161"/>
-      <c r="Q5" s="162"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="124"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="125"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1901,16 +1978,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Z5" s="152"/>
-      <c r="AA5" s="152"/>
-      <c r="AB5" s="152"/>
-      <c r="AC5" s="152"/>
-      <c r="AD5" s="116"/>
-      <c r="AE5" s="163"/>
-      <c r="AF5" s="164"/>
-      <c r="AG5" s="164"/>
-      <c r="AH5" s="165"/>
-      <c r="AR5" s="38" t="s">
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="104"/>
+      <c r="AE5" s="126"/>
+      <c r="AF5" s="127"/>
+      <c r="AG5" s="127"/>
+      <c r="AH5" s="128"/>
+      <c r="AR5" s="45" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1952,129 +2029,129 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="69"/>
+      <c r="AK6" s="107"/>
+      <c r="AL6" s="107"/>
     </row>
     <row r="7" spans="1:766" s="9" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B7" s="146" t="s">
+      <c r="B7" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="53">
+      <c r="C7" s="109"/>
+      <c r="D7" s="85">
         <v>1</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="85">
         <v>2</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="88">
         <v>3</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="88">
         <v>4</v>
       </c>
-      <c r="H7" s="54">
+      <c r="H7" s="86">
         <v>5</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="87">
         <v>6</v>
       </c>
-      <c r="J7" s="53">
+      <c r="J7" s="85">
         <v>7</v>
       </c>
-      <c r="K7" s="53">
+      <c r="K7" s="85">
         <v>8</v>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="88">
         <v>9</v>
       </c>
-      <c r="M7" s="56">
+      <c r="M7" s="88">
         <v>10</v>
       </c>
-      <c r="N7" s="56">
+      <c r="N7" s="88">
         <v>11</v>
       </c>
-      <c r="O7" s="55">
+      <c r="O7" s="87">
         <v>12</v>
       </c>
-      <c r="P7" s="55">
+      <c r="P7" s="87">
         <v>13</v>
       </c>
-      <c r="Q7" s="53">
+      <c r="Q7" s="85">
         <v>14</v>
       </c>
-      <c r="R7" s="53">
+      <c r="R7" s="85">
         <v>15</v>
       </c>
-      <c r="S7" s="53">
+      <c r="S7" s="85">
         <v>16</v>
       </c>
-      <c r="T7" s="56">
+      <c r="T7" s="88">
         <v>17</v>
       </c>
-      <c r="U7" s="56">
+      <c r="U7" s="88">
         <v>18</v>
       </c>
-      <c r="V7" s="55">
+      <c r="V7" s="87">
         <v>19</v>
       </c>
-      <c r="W7" s="55">
+      <c r="W7" s="87">
         <v>20</v>
       </c>
-      <c r="X7" s="53">
+      <c r="X7" s="85">
         <v>21</v>
       </c>
-      <c r="Y7" s="53">
+      <c r="Y7" s="85">
         <v>22</v>
       </c>
-      <c r="Z7" s="53">
+      <c r="Z7" s="85">
         <v>23</v>
       </c>
-      <c r="AA7" s="52">
+      <c r="AA7" s="84">
         <v>24</v>
       </c>
-      <c r="AB7" s="52">
+      <c r="AB7" s="84">
         <v>25</v>
       </c>
-      <c r="AC7" s="55">
+      <c r="AC7" s="87">
         <v>26</v>
       </c>
-      <c r="AD7" s="55">
+      <c r="AD7" s="87">
         <v>27</v>
       </c>
-      <c r="AE7" s="53">
+      <c r="AE7" s="85">
         <v>28</v>
       </c>
-      <c r="AF7" s="53">
+      <c r="AF7" s="85">
         <v>29</v>
       </c>
-      <c r="AG7" s="53">
+      <c r="AG7" s="85">
         <v>30</v>
       </c>
-      <c r="AH7" s="56">
+      <c r="AH7" s="88">
         <v>31</v>
       </c>
-      <c r="AI7" s="113" t="s">
+      <c r="AI7" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="AJ7" s="40" t="s">
+      <c r="AJ7" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="AK7" s="113" t="s">
+      <c r="AK7" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="AL7" s="41" t="s">
+      <c r="AL7" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="AM7" s="147" t="s">
+      <c r="AM7" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="AN7" s="148" t="s">
+      <c r="AN7" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="AO7" s="114"/>
-      <c r="AP7" s="39"/>
+      <c r="AO7" s="102"/>
+      <c r="AP7" s="46"/>
       <c r="AQ7" s="10"/>
-      <c r="AR7" s="39"/>
+      <c r="AR7" s="46"/>
       <c r="AS7" s="11"/>
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
@@ -2793,117 +2870,117 @@
       <c r="ACF7" s="11"/>
     </row>
     <row r="8" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="149" t="s">
+      <c r="B8" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="149"/>
-      <c r="D8" s="53" t="s">
+      <c r="C8" s="112"/>
+      <c r="D8" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="183" t="s">
+      <c r="F8" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="183" t="s">
+      <c r="G8" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="183" t="s">
+      <c r="H8" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="184" t="s">
+      <c r="I8" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="53" t="s">
+      <c r="K8" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="56" t="s">
+      <c r="L8" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="56" t="s">
+      <c r="M8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="56" t="s">
+      <c r="N8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="184" t="s">
+      <c r="O8" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="184" t="s">
+      <c r="P8" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="53" t="s">
+      <c r="Q8" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="53" t="s">
+      <c r="R8" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="53" t="s">
+      <c r="S8" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="56" t="s">
+      <c r="T8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="56" t="s">
+      <c r="U8" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="184" t="s">
+      <c r="V8" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="184" t="s">
+      <c r="W8" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="53" t="s">
+      <c r="X8" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="185" t="s">
+      <c r="Y8" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="185" t="s">
+      <c r="Z8" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="52" t="s">
+      <c r="AA8" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" s="58" t="s">
+      <c r="AB8" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="184" t="s">
+      <c r="AC8" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AD8" s="184" t="s">
+      <c r="AD8" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="AE8" s="57" t="s">
+      <c r="AE8" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="53" t="s">
+      <c r="AF8" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="AG8" s="53" t="s">
+      <c r="AG8" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="52" t="s">
+      <c r="AH8" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="AI8" s="113"/>
-      <c r="AJ8" s="113"/>
-      <c r="AK8" s="113"/>
-      <c r="AL8" s="42"/>
-      <c r="AM8" s="147"/>
-      <c r="AN8" s="148"/>
-      <c r="AO8" s="114"/>
-      <c r="AP8" s="47" t="s">
+      <c r="AI8" s="101"/>
+      <c r="AJ8" s="101"/>
+      <c r="AK8" s="101"/>
+      <c r="AL8" s="50"/>
+      <c r="AM8" s="110"/>
+      <c r="AN8" s="111"/>
+      <c r="AO8" s="102"/>
+      <c r="AP8" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="AQ8" s="39" t="s">
+      <c r="AQ8" s="46" t="s">
         <v>29</v>
       </c>
       <c r="AR8" s="10" t="s">
@@ -3626,52 +3703,52 @@
       <c r="ACF8" s="11"/>
     </row>
     <row r="9" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="45">
+      <c r="A9" s="65">
         <v>1</v>
       </c>
-      <c r="B9" s="117"/>
-      <c r="C9" s="66"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="13"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="166"/>
-      <c r="G9" s="166"/>
-      <c r="H9" s="166"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="156"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="166"/>
-      <c r="M9" s="166"/>
-      <c r="N9" s="166"/>
-      <c r="O9" s="16"/>
+      <c r="L9" s="156"/>
+      <c r="M9" s="156"/>
+      <c r="N9" s="156"/>
+      <c r="O9" s="129"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
-      <c r="R9" s="71"/>
+      <c r="R9" s="130"/>
       <c r="S9" s="16"/>
-      <c r="T9" s="78"/>
-      <c r="U9" s="78"/>
+      <c r="T9" s="143"/>
+      <c r="U9" s="143"/>
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="36"/>
+      <c r="Y9" s="43"/>
       <c r="Z9" s="16"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="36"/>
+      <c r="AA9" s="150"/>
+      <c r="AB9" s="150"/>
+      <c r="AC9" s="129"/>
+      <c r="AD9" s="129"/>
+      <c r="AE9" s="82"/>
+      <c r="AF9" s="43"/>
       <c r="AG9" s="16"/>
-      <c r="AH9" s="60"/>
+      <c r="AH9" s="93"/>
       <c r="AI9" s="18"/>
       <c r="AJ9" s="18"/>
-      <c r="AK9" s="35"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="118"/>
-      <c r="AN9" s="167"/>
-      <c r="AO9" s="167"/>
-      <c r="AP9" s="119"/>
-      <c r="AQ9" s="119"/>
-      <c r="AR9" s="119"/>
+      <c r="AK9" s="41"/>
+      <c r="AL9" s="50"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="53"/>
+      <c r="AO9" s="53"/>
+      <c r="AP9" s="46"/>
+      <c r="AQ9" s="10"/>
+      <c r="AR9" s="46"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
@@ -4388,52 +4465,52 @@
       <c r="ACD9" s="11"/>
     </row>
     <row r="10" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="45">
+      <c r="A10" s="65">
         <v>2</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="66"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="13"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="168"/>
-      <c r="I10" s="16"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="160"/>
+      <c r="I10" s="129"/>
       <c r="J10" s="13"/>
       <c r="K10" s="16"/>
-      <c r="L10" s="78"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
+      <c r="L10" s="143"/>
+      <c r="M10" s="143"/>
+      <c r="N10" s="143"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="129"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
+      <c r="T10" s="143"/>
+      <c r="U10" s="143"/>
+      <c r="V10" s="129"/>
+      <c r="W10" s="129"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="36"/>
+      <c r="Y10" s="43"/>
       <c r="Z10" s="16"/>
-      <c r="AA10" s="78"/>
-      <c r="AB10" s="84"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="51"/>
-      <c r="AF10" s="36"/>
+      <c r="AA10" s="143"/>
+      <c r="AB10" s="150"/>
+      <c r="AC10" s="129"/>
+      <c r="AD10" s="129"/>
+      <c r="AE10" s="82"/>
+      <c r="AF10" s="43"/>
       <c r="AG10" s="16"/>
-      <c r="AH10" s="59"/>
+      <c r="AH10" s="92"/>
       <c r="AI10" s="18"/>
       <c r="AJ10" s="18"/>
-      <c r="AK10" s="35"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="118"/>
-      <c r="AN10" s="167"/>
-      <c r="AO10" s="167"/>
-      <c r="AP10" s="119"/>
-      <c r="AQ10" s="119"/>
-      <c r="AR10" s="119"/>
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="50"/>
+      <c r="AM10" s="52"/>
+      <c r="AN10" s="53"/>
+      <c r="AO10" s="53"/>
+      <c r="AP10" s="46"/>
+      <c r="AQ10" s="10"/>
+      <c r="AR10" s="46"/>
       <c r="AS10" s="11"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
@@ -5150,52 +5227,52 @@
       <c r="ACD10" s="11"/>
     </row>
     <row r="11" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="45">
+      <c r="A11" s="65">
         <v>3</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="66"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="13"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="166"/>
-      <c r="I11" s="16"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="129"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="169"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="129"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="16"/>
       <c r="S11" s="13"/>
-      <c r="T11" s="78"/>
-      <c r="U11" s="78"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
+      <c r="T11" s="143"/>
+      <c r="U11" s="143"/>
+      <c r="V11" s="129"/>
+      <c r="W11" s="129"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
-      <c r="AA11" s="79"/>
-      <c r="AB11" s="84"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="51"/>
+      <c r="AA11" s="144"/>
+      <c r="AB11" s="150"/>
+      <c r="AC11" s="129"/>
+      <c r="AD11" s="129"/>
+      <c r="AE11" s="82"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
-      <c r="AH11" s="59"/>
+      <c r="AH11" s="92"/>
       <c r="AI11" s="18"/>
       <c r="AJ11" s="18"/>
-      <c r="AK11" s="35"/>
-      <c r="AL11" s="118"/>
-      <c r="AM11" s="118"/>
-      <c r="AN11" s="167"/>
-      <c r="AO11" s="167"/>
-      <c r="AP11" s="119"/>
-      <c r="AQ11" s="119"/>
-      <c r="AR11" s="119"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="56"/>
+      <c r="AM11" s="52"/>
+      <c r="AN11" s="55"/>
+      <c r="AO11" s="55"/>
+      <c r="AP11" s="47"/>
+      <c r="AQ11" s="20"/>
+      <c r="AR11" s="47"/>
       <c r="AS11" s="11"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
@@ -5912,52 +5989,52 @@
       <c r="ACD11" s="11"/>
     </row>
     <row r="12" spans="1:766" ht="24" customHeight="1">
-      <c r="A12" s="45">
+      <c r="A12" s="65">
         <v>4</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="66"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="13"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="16"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="129"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="78"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="144"/>
+      <c r="N12" s="143"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="129"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="79"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
+      <c r="T12" s="144"/>
+      <c r="U12" s="144"/>
+      <c r="V12" s="129"/>
+      <c r="W12" s="129"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="79"/>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="32"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="144"/>
+      <c r="AB12" s="141"/>
+      <c r="AC12" s="129"/>
+      <c r="AD12" s="129"/>
+      <c r="AE12" s="37"/>
       <c r="AF12" s="16"/>
-      <c r="AG12" s="22"/>
-      <c r="AH12" s="61"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="94"/>
       <c r="AI12" s="18"/>
       <c r="AJ12" s="18"/>
-      <c r="AK12" s="120"/>
-      <c r="AL12" s="167"/>
-      <c r="AM12" s="120"/>
-      <c r="AN12" s="167"/>
-      <c r="AO12" s="167"/>
-      <c r="AP12" s="119"/>
-      <c r="AQ12" s="119"/>
-      <c r="AR12" s="119"/>
+      <c r="AK12" s="58"/>
+      <c r="AL12" s="55"/>
+      <c r="AM12" s="58"/>
+      <c r="AN12" s="55"/>
+      <c r="AO12" s="55"/>
+      <c r="AP12" s="47"/>
+      <c r="AQ12" s="20"/>
+      <c r="AR12" s="47"/>
       <c r="ACE12"/>
       <c r="ACF12"/>
       <c r="ACG12"/>
@@ -5967,53 +6044,53 @@
       <c r="ACK12"/>
       <c r="ACL12"/>
     </row>
-    <row r="13" spans="1:766" ht="24" customHeight="1">
-      <c r="A13" s="45">
+    <row r="13" spans="1:766" ht="24" customHeight="1" thickBot="1">
+      <c r="A13" s="65">
         <v>5</v>
       </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="66"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="16"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="156"/>
+      <c r="I13" s="129"/>
       <c r="J13" s="16"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="79"/>
-      <c r="U13" s="170"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="129"/>
+      <c r="Q13" s="130"/>
+      <c r="R13" s="130"/>
+      <c r="S13" s="130"/>
+      <c r="T13" s="144"/>
+      <c r="U13" s="145"/>
+      <c r="V13" s="129"/>
+      <c r="W13" s="129"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-      <c r="AA13" s="79"/>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="32"/>
+      <c r="AA13" s="144"/>
+      <c r="AB13" s="141"/>
+      <c r="AC13" s="129"/>
+      <c r="AD13" s="129"/>
+      <c r="AE13" s="37"/>
       <c r="AF13" s="16"/>
       <c r="AG13" s="16"/>
-      <c r="AH13" s="61"/>
+      <c r="AH13" s="94"/>
       <c r="AI13" s="18"/>
       <c r="AJ13" s="18"/>
-      <c r="AK13" s="35"/>
-      <c r="AL13" s="118"/>
-      <c r="AM13" s="118"/>
-      <c r="AN13" s="167"/>
-      <c r="AO13" s="167"/>
-      <c r="AP13" s="119"/>
-      <c r="AQ13" s="119"/>
-      <c r="AR13" s="119"/>
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="56"/>
+      <c r="AM13" s="52"/>
+      <c r="AN13" s="55"/>
+      <c r="AO13" s="55"/>
+      <c r="AP13" s="47"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="47"/>
       <c r="ACE13"/>
       <c r="ACF13"/>
       <c r="ACG13"/>
@@ -6023,53 +6100,53 @@
       <c r="ACK13"/>
       <c r="ACL13"/>
     </row>
-    <row r="14" spans="1:766" ht="24" customHeight="1">
-      <c r="A14" s="45">
+    <row r="14" spans="1:766" ht="24" customHeight="1" thickTop="1">
+      <c r="A14" s="65">
         <v>6</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="66"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="166"/>
-      <c r="I14" s="16"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="129"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
-      <c r="T14" s="79"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
+      <c r="T14" s="144"/>
+      <c r="U14" s="144"/>
+      <c r="V14" s="129"/>
+      <c r="W14" s="129"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
-      <c r="AA14" s="79"/>
-      <c r="AB14" s="121"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="16"/>
-      <c r="AE14" s="32"/>
+      <c r="AA14" s="144"/>
+      <c r="AB14" s="142"/>
+      <c r="AC14" s="138"/>
+      <c r="AD14" s="129"/>
+      <c r="AE14" s="37"/>
       <c r="AF14" s="16"/>
       <c r="AG14" s="16"/>
-      <c r="AH14" s="61"/>
+      <c r="AH14" s="94"/>
       <c r="AI14" s="18"/>
       <c r="AJ14" s="18"/>
       <c r="AK14" s="18"/>
-      <c r="AL14" s="118"/>
-      <c r="AM14" s="120"/>
-      <c r="AN14" s="167"/>
-      <c r="AO14" s="167"/>
-      <c r="AP14" s="119"/>
-      <c r="AQ14" s="119"/>
-      <c r="AR14" s="119"/>
+      <c r="AL14" s="56"/>
+      <c r="AM14" s="58"/>
+      <c r="AN14" s="55"/>
+      <c r="AO14" s="55"/>
+      <c r="AP14" s="47"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="47"/>
       <c r="ACE14"/>
       <c r="ACF14"/>
       <c r="ACG14"/>
@@ -6080,52 +6157,52 @@
       <c r="ACL14"/>
     </row>
     <row r="15" spans="1:766" ht="24" customHeight="1">
-      <c r="A15" s="45">
+      <c r="A15" s="65">
         <v>7</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="166"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="122"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="132"/>
       <c r="K15" s="16"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="171"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="22"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="131"/>
+      <c r="Q15" s="25"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
-      <c r="T15" s="79"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="146"/>
+      <c r="V15" s="129"/>
+      <c r="W15" s="129"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
-      <c r="AA15" s="79"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="22"/>
+      <c r="AA15" s="144"/>
+      <c r="AB15" s="141"/>
+      <c r="AC15" s="129"/>
+      <c r="AD15" s="129"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="25"/>
       <c r="AG15" s="16"/>
-      <c r="AH15" s="62"/>
+      <c r="AH15" s="95"/>
       <c r="AI15" s="18"/>
       <c r="AJ15" s="18"/>
-      <c r="AK15" s="35"/>
-      <c r="AL15" s="118"/>
-      <c r="AM15" s="118"/>
-      <c r="AN15" s="167"/>
-      <c r="AO15" s="167"/>
-      <c r="AP15" s="119"/>
-      <c r="AQ15" s="119"/>
-      <c r="AR15" s="119"/>
+      <c r="AK15" s="59"/>
+      <c r="AL15" s="56"/>
+      <c r="AM15" s="52"/>
+      <c r="AN15" s="55"/>
+      <c r="AO15" s="55"/>
+      <c r="AP15" s="47"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="47"/>
       <c r="ACE15"/>
       <c r="ACF15"/>
       <c r="ACG15"/>
@@ -6136,52 +6213,52 @@
       <c r="ACL15"/>
     </row>
     <row r="16" spans="1:766" ht="24" customHeight="1">
-      <c r="A16" s="45">
+      <c r="A16" s="65">
         <v>8</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="166"/>
-      <c r="I16" s="16"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="161"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="129"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="129"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="80"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="78"/>
-      <c r="AB16" s="77"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
-      <c r="AE16" s="33"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="22"/>
-      <c r="AH16" s="62"/>
+      <c r="T16" s="143"/>
+      <c r="U16" s="146"/>
+      <c r="V16" s="129"/>
+      <c r="W16" s="129"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="143"/>
+      <c r="AB16" s="141"/>
+      <c r="AC16" s="129"/>
+      <c r="AD16" s="129"/>
+      <c r="AE16" s="83"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="95"/>
       <c r="AI16" s="18"/>
       <c r="AJ16" s="18"/>
-      <c r="AK16" s="123"/>
-      <c r="AL16" s="118"/>
-      <c r="AM16" s="118"/>
-      <c r="AN16" s="167"/>
-      <c r="AO16" s="167"/>
-      <c r="AP16" s="119"/>
-      <c r="AQ16" s="119"/>
-      <c r="AR16" s="119"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="56"/>
+      <c r="AM16" s="52"/>
+      <c r="AN16" s="55"/>
+      <c r="AO16" s="55"/>
+      <c r="AP16" s="47"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="47"/>
       <c r="ACE16"/>
       <c r="ACF16"/>
       <c r="ACG16"/>
@@ -6192,52 +6269,52 @@
       <c r="ACL16"/>
     </row>
     <row r="17" spans="1:766" ht="24" customHeight="1">
-      <c r="A17" s="45">
+      <c r="A17" s="65">
         <v>1</v>
       </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="124"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="16"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="156"/>
+      <c r="I17" s="129"/>
       <c r="J17" s="13"/>
       <c r="K17" s="16"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="22"/>
+      <c r="L17" s="143"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="129"/>
+      <c r="Q17" s="25"/>
       <c r="R17" s="16"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="79"/>
-      <c r="U17" s="79"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="79"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="33"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="144"/>
+      <c r="U17" s="144"/>
+      <c r="V17" s="129"/>
+      <c r="W17" s="129"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="130"/>
+      <c r="Z17" s="133"/>
+      <c r="AA17" s="144"/>
+      <c r="AB17" s="141"/>
+      <c r="AC17" s="129"/>
+      <c r="AD17" s="129"/>
+      <c r="AE17" s="38"/>
       <c r="AF17" s="16"/>
-      <c r="AG17" s="22"/>
-      <c r="AH17" s="62"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="95"/>
       <c r="AI17" s="18"/>
       <c r="AJ17" s="18"/>
-      <c r="AK17" s="35"/>
-      <c r="AL17" s="118"/>
-      <c r="AM17" s="118"/>
-      <c r="AN17" s="167"/>
-      <c r="AO17" s="167"/>
-      <c r="AP17" s="119"/>
-      <c r="AQ17" s="119"/>
-      <c r="AR17" s="119"/>
+      <c r="AK17" s="41"/>
+      <c r="AL17" s="56"/>
+      <c r="AM17" s="52"/>
+      <c r="AN17" s="55"/>
+      <c r="AO17" s="55"/>
+      <c r="AP17" s="47"/>
+      <c r="AQ17" s="20"/>
+      <c r="AR17" s="47"/>
       <c r="ACE17"/>
       <c r="ACF17"/>
       <c r="ACG17"/>
@@ -6248,52 +6325,52 @@
       <c r="ACL17"/>
     </row>
     <row r="18" spans="1:766" ht="24" customHeight="1">
-      <c r="A18" s="45">
+      <c r="A18" s="65">
         <v>1</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="126"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="172"/>
-      <c r="I18" s="20"/>
+      <c r="B18" s="169"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="192"/>
+      <c r="I18" s="193"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="158"/>
+      <c r="M18" s="158"/>
+      <c r="N18" s="158"/>
+      <c r="O18" s="193"/>
+      <c r="P18" s="193"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="104"/>
-      <c r="U18" s="104"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="90"/>
-      <c r="AB18" s="105"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="65"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="63"/>
-      <c r="AI18" s="23"/>
-      <c r="AJ18" s="23"/>
-      <c r="AK18" s="23"/>
-      <c r="AL18" s="127"/>
-      <c r="AM18" s="127"/>
-      <c r="AN18" s="128"/>
-      <c r="AO18" s="128"/>
-      <c r="AP18" s="129"/>
-      <c r="AQ18" s="129"/>
-      <c r="AR18" s="129"/>
+      <c r="S18" s="194"/>
+      <c r="T18" s="195"/>
+      <c r="U18" s="195"/>
+      <c r="V18" s="196"/>
+      <c r="W18" s="193"/>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="158"/>
+      <c r="AB18" s="197"/>
+      <c r="AC18" s="193"/>
+      <c r="AD18" s="193"/>
+      <c r="AE18" s="99"/>
+      <c r="AF18" s="21"/>
+      <c r="AG18" s="21"/>
+      <c r="AH18" s="96"/>
+      <c r="AI18" s="27"/>
+      <c r="AJ18" s="27"/>
+      <c r="AK18" s="27"/>
+      <c r="AL18" s="71"/>
+      <c r="AM18" s="72"/>
+      <c r="AN18" s="198"/>
+      <c r="AO18" s="198"/>
+      <c r="AP18" s="62"/>
+      <c r="AQ18" s="74"/>
+      <c r="AR18" s="62"/>
       <c r="ACE18"/>
       <c r="ACF18"/>
       <c r="ACG18"/>
@@ -6304,52 +6381,52 @@
       <c r="ACL18"/>
     </row>
     <row r="19" spans="1:766" ht="24" customHeight="1">
-      <c r="A19" s="45">
+      <c r="A19" s="65">
         <v>2</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="131"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="173"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="96"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="173"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="93"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="93"/>
-      <c r="W19" s="93"/>
-      <c r="X19" s="93"/>
-      <c r="Y19" s="93"/>
-      <c r="Z19" s="97"/>
-      <c r="AA19" s="98"/>
-      <c r="AB19" s="99"/>
-      <c r="AC19" s="97"/>
-      <c r="AD19" s="93"/>
-      <c r="AE19" s="100"/>
-      <c r="AF19" s="93"/>
-      <c r="AG19" s="93"/>
-      <c r="AH19" s="101"/>
-      <c r="AI19" s="102"/>
-      <c r="AJ19" s="102"/>
-      <c r="AK19" s="102"/>
-      <c r="AL19" s="132"/>
-      <c r="AM19" s="132"/>
-      <c r="AN19" s="174"/>
-      <c r="AO19" s="174"/>
-      <c r="AP19" s="133"/>
-      <c r="AQ19" s="133"/>
-      <c r="AR19" s="133"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="175"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="177"/>
+      <c r="K19" s="173"/>
+      <c r="L19" s="174"/>
+      <c r="M19" s="178"/>
+      <c r="N19" s="174"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="176"/>
+      <c r="R19" s="177"/>
+      <c r="S19" s="173"/>
+      <c r="T19" s="174"/>
+      <c r="U19" s="174"/>
+      <c r="V19" s="179"/>
+      <c r="W19" s="179"/>
+      <c r="X19" s="173"/>
+      <c r="Y19" s="173"/>
+      <c r="Z19" s="180"/>
+      <c r="AA19" s="181"/>
+      <c r="AB19" s="182"/>
+      <c r="AC19" s="183"/>
+      <c r="AD19" s="179"/>
+      <c r="AE19" s="184"/>
+      <c r="AF19" s="173"/>
+      <c r="AG19" s="173"/>
+      <c r="AH19" s="185"/>
+      <c r="AI19" s="186"/>
+      <c r="AJ19" s="186"/>
+      <c r="AK19" s="186"/>
+      <c r="AL19" s="187"/>
+      <c r="AM19" s="188"/>
+      <c r="AN19" s="189"/>
+      <c r="AO19" s="189"/>
+      <c r="AP19" s="190"/>
+      <c r="AQ19" s="191"/>
+      <c r="AR19" s="190"/>
       <c r="ACE19"/>
       <c r="ACF19"/>
       <c r="ACG19"/>
@@ -6360,52 +6437,52 @@
       <c r="ACL19"/>
     </row>
     <row r="20" spans="1:766" ht="24" customHeight="1">
-      <c r="A20" s="45">
+      <c r="A20" s="65">
         <v>1</v>
       </c>
-      <c r="B20" s="134"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="175"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="21"/>
+      <c r="B20" s="170"/>
+      <c r="C20" s="199"/>
+      <c r="D20" s="200"/>
+      <c r="E20" s="201"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="202"/>
+      <c r="I20" s="203"/>
+      <c r="J20" s="24"/>
       <c r="K20" s="14"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="108"/>
-      <c r="O20" s="12"/>
-      <c r="P20" s="12"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="162"/>
+      <c r="N20" s="204"/>
+      <c r="O20" s="203"/>
+      <c r="P20" s="203"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="17"/>
       <c r="S20" s="12"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="85"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="12"/>
+      <c r="T20" s="205"/>
+      <c r="U20" s="151"/>
+      <c r="V20" s="203"/>
+      <c r="W20" s="203"/>
       <c r="X20" s="12"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="85"/>
-      <c r="AB20" s="86"/>
-      <c r="AC20" s="12"/>
-      <c r="AD20" s="12"/>
-      <c r="AE20" s="31"/>
-      <c r="AF20" s="76"/>
-      <c r="AG20" s="76"/>
-      <c r="AH20" s="110"/>
+      <c r="AA20" s="151"/>
+      <c r="AB20" s="152"/>
+      <c r="AC20" s="203"/>
+      <c r="AD20" s="203"/>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="140"/>
+      <c r="AG20" s="140"/>
+      <c r="AH20" s="206"/>
       <c r="AI20" s="19"/>
       <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="136"/>
-      <c r="AM20" s="137"/>
-      <c r="AN20" s="176"/>
-      <c r="AO20" s="176"/>
-      <c r="AP20" s="138"/>
-      <c r="AQ20" s="138"/>
-      <c r="AR20" s="139"/>
+      <c r="AK20" s="207"/>
+      <c r="AL20" s="208"/>
+      <c r="AM20" s="209"/>
+      <c r="AN20" s="78"/>
+      <c r="AO20" s="78"/>
+      <c r="AP20" s="79"/>
+      <c r="AQ20" s="210"/>
+      <c r="AR20" s="211"/>
       <c r="ACF20"/>
       <c r="ACG20"/>
       <c r="ACH20"/>
@@ -6415,52 +6492,52 @@
       <c r="ACL20"/>
     </row>
     <row r="21" spans="1:766" ht="24" customHeight="1">
-      <c r="A21" s="45">
+      <c r="A21" s="65">
         <v>2</v>
       </c>
-      <c r="B21" s="125"/>
-      <c r="C21" s="66"/>
+      <c r="B21" s="169"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="166"/>
-      <c r="I21" s="16"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="156"/>
+      <c r="I21" s="129"/>
       <c r="J21" s="16"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="143"/>
+      <c r="N21" s="144"/>
+      <c r="O21" s="129"/>
+      <c r="P21" s="129"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="13"/>
       <c r="S21" s="16"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="79"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
+      <c r="T21" s="143"/>
+      <c r="U21" s="144"/>
+      <c r="V21" s="129"/>
+      <c r="W21" s="129"/>
       <c r="X21" s="16"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="16"/>
-      <c r="AA21" s="85"/>
-      <c r="AB21" s="86"/>
-      <c r="AC21" s="16"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="31"/>
+      <c r="AA21" s="151"/>
+      <c r="AB21" s="152"/>
+      <c r="AC21" s="129"/>
+      <c r="AD21" s="129"/>
+      <c r="AE21" s="36"/>
       <c r="AF21" s="12"/>
-      <c r="AG21" s="177"/>
-      <c r="AH21" s="64"/>
+      <c r="AG21" s="98"/>
+      <c r="AH21" s="97"/>
       <c r="AI21" s="18"/>
       <c r="AJ21" s="18"/>
-      <c r="AK21" s="23"/>
-      <c r="AL21" s="118"/>
-      <c r="AM21" s="127"/>
-      <c r="AN21" s="178"/>
-      <c r="AO21" s="178"/>
-      <c r="AP21" s="129"/>
-      <c r="AQ21" s="119"/>
-      <c r="AR21" s="129"/>
+      <c r="AK21" s="214"/>
+      <c r="AL21" s="56"/>
+      <c r="AM21" s="72"/>
+      <c r="AN21" s="73"/>
+      <c r="AO21" s="73"/>
+      <c r="AP21" s="62"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="62"/>
       <c r="ACF21"/>
       <c r="ACG21"/>
       <c r="ACH21"/>
@@ -6470,52 +6547,52 @@
       <c r="ACL21"/>
     </row>
     <row r="22" spans="1:766" ht="24" customHeight="1">
-      <c r="A22" s="45">
+      <c r="A22" s="65">
         <v>3</v>
       </c>
-      <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="16"/>
+      <c r="B22" s="167"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="163"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="156"/>
+      <c r="I22" s="129"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="20"/>
+      <c r="L22" s="144"/>
+      <c r="M22" s="158"/>
+      <c r="N22" s="158"/>
+      <c r="O22" s="129"/>
+      <c r="P22" s="129"/>
+      <c r="Q22" s="21"/>
       <c r="R22" s="15"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="82"/>
-      <c r="U22" s="82"/>
-      <c r="V22" s="73"/>
-      <c r="W22" s="73"/>
-      <c r="X22" s="73"/>
-      <c r="Y22" s="74"/>
-      <c r="Z22" s="73"/>
-      <c r="AA22" s="87"/>
-      <c r="AB22" s="88"/>
-      <c r="AC22" s="73"/>
-      <c r="AD22" s="71"/>
-      <c r="AE22" s="75"/>
-      <c r="AF22" s="76"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="148"/>
+      <c r="U22" s="148"/>
+      <c r="V22" s="135"/>
+      <c r="W22" s="135"/>
+      <c r="X22" s="136"/>
+      <c r="Y22" s="137"/>
+      <c r="Z22" s="136"/>
+      <c r="AA22" s="153"/>
+      <c r="AB22" s="154"/>
+      <c r="AC22" s="135"/>
+      <c r="AD22" s="134"/>
+      <c r="AE22" s="139"/>
+      <c r="AF22" s="140"/>
       <c r="AG22" s="13"/>
-      <c r="AH22" s="60"/>
+      <c r="AH22" s="93"/>
       <c r="AI22" s="19"/>
-      <c r="AJ22" s="112"/>
-      <c r="AK22" s="111"/>
-      <c r="AL22" s="142"/>
-      <c r="AM22" s="143"/>
-      <c r="AN22" s="179"/>
-      <c r="AO22" s="179"/>
-      <c r="AP22" s="180"/>
-      <c r="AQ22" s="181"/>
-      <c r="AR22" s="119"/>
+      <c r="AJ22" s="213"/>
+      <c r="AK22" s="212"/>
+      <c r="AL22" s="22"/>
+      <c r="AM22" s="164"/>
+      <c r="AN22" s="165"/>
+      <c r="AO22" s="165"/>
+      <c r="AP22" s="166"/>
+      <c r="AQ22" s="39"/>
+      <c r="AR22" s="47"/>
       <c r="ACF22"/>
       <c r="ACG22"/>
       <c r="ACH22"/>
@@ -6525,52 +6602,52 @@
       <c r="ACL22"/>
     </row>
     <row r="23" spans="1:766" ht="24" customHeight="1">
-      <c r="A23" s="45">
+      <c r="A23" s="65">
         <v>4</v>
       </c>
-      <c r="B23" s="134"/>
-      <c r="C23" s="66"/>
+      <c r="B23" s="170"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="71"/>
+      <c r="F23" s="143"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="156"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="130"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="79"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="144"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="129"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="13"/>
       <c r="S23" s="16"/>
-      <c r="T23" s="81"/>
-      <c r="U23" s="81"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
+      <c r="T23" s="147"/>
+      <c r="U23" s="147"/>
+      <c r="V23" s="129"/>
+      <c r="W23" s="129"/>
       <c r="X23" s="16"/>
       <c r="Y23" s="13"/>
       <c r="Z23" s="16"/>
-      <c r="AA23" s="79"/>
-      <c r="AB23" s="77"/>
-      <c r="AC23" s="16"/>
-      <c r="AD23" s="16"/>
-      <c r="AE23" s="32"/>
+      <c r="AA23" s="144"/>
+      <c r="AB23" s="141"/>
+      <c r="AC23" s="129"/>
+      <c r="AD23" s="129"/>
+      <c r="AE23" s="37"/>
       <c r="AF23" s="16"/>
       <c r="AG23" s="16"/>
-      <c r="AH23" s="59"/>
+      <c r="AH23" s="92"/>
       <c r="AI23" s="19"/>
       <c r="AJ23" s="19"/>
-      <c r="AK23" s="49"/>
-      <c r="AL23" s="144"/>
-      <c r="AM23" s="144"/>
-      <c r="AN23" s="176"/>
-      <c r="AO23" s="176"/>
-      <c r="AP23" s="138"/>
-      <c r="AQ23" s="138"/>
-      <c r="AR23" s="119"/>
+      <c r="AK23" s="75"/>
+      <c r="AL23" s="76"/>
+      <c r="AM23" s="77"/>
+      <c r="AN23" s="78"/>
+      <c r="AO23" s="78"/>
+      <c r="AP23" s="79"/>
+      <c r="AQ23" s="80"/>
+      <c r="AR23" s="47"/>
       <c r="ACF23"/>
       <c r="ACG23"/>
       <c r="ACH23"/>
@@ -6580,52 +6657,52 @@
       <c r="ACL23"/>
     </row>
     <row r="24" spans="1:766" ht="24" customHeight="1">
-      <c r="A24" s="45">
+      <c r="A24" s="65">
         <v>5</v>
       </c>
-      <c r="B24" s="117"/>
-      <c r="C24" s="66"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="51"/>
       <c r="D24" s="16"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="16"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="143"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="129"/>
       <c r="J24" s="16"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="143"/>
+      <c r="N24" s="144"/>
+      <c r="O24" s="129"/>
+      <c r="P24" s="129"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="79"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
+      <c r="T24" s="143"/>
+      <c r="U24" s="144"/>
+      <c r="V24" s="129"/>
+      <c r="W24" s="129"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="13"/>
-      <c r="AA24" s="85"/>
-      <c r="AB24" s="86"/>
-      <c r="AC24" s="16"/>
-      <c r="AD24" s="16"/>
-      <c r="AE24" s="32"/>
+      <c r="AA24" s="151"/>
+      <c r="AB24" s="152"/>
+      <c r="AC24" s="129"/>
+      <c r="AD24" s="129"/>
+      <c r="AE24" s="37"/>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
-      <c r="AH24" s="61"/>
+      <c r="AH24" s="94"/>
       <c r="AI24" s="18"/>
       <c r="AJ24" s="18"/>
-      <c r="AK24" s="35"/>
-      <c r="AL24" s="118"/>
-      <c r="AM24" s="118"/>
-      <c r="AN24" s="167"/>
-      <c r="AO24" s="167"/>
-      <c r="AP24" s="119"/>
-      <c r="AQ24" s="119"/>
-      <c r="AR24" s="119"/>
+      <c r="AK24" s="41"/>
+      <c r="AL24" s="56"/>
+      <c r="AM24" s="52"/>
+      <c r="AN24" s="55"/>
+      <c r="AO24" s="55"/>
+      <c r="AP24" s="47"/>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="47"/>
       <c r="ACF24"/>
       <c r="ACG24"/>
       <c r="ACH24"/>
@@ -6635,52 +6712,52 @@
       <c r="ACL24"/>
     </row>
     <row r="25" spans="1:766" ht="24" customHeight="1">
-      <c r="A25" s="45">
+      <c r="A25" s="65">
         <v>1</v>
       </c>
-      <c r="B25" s="125"/>
-      <c r="C25" s="126"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="42"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="166"/>
-      <c r="G25" s="166"/>
-      <c r="H25" s="166"/>
-      <c r="I25" s="16"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="156"/>
+      <c r="H25" s="156"/>
+      <c r="I25" s="129"/>
       <c r="J25" s="15"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="149"/>
+      <c r="M25" s="159"/>
+      <c r="N25" s="149"/>
+      <c r="O25" s="129"/>
+      <c r="P25" s="129"/>
       <c r="Q25" s="15"/>
-      <c r="R25" s="20"/>
+      <c r="R25" s="21"/>
       <c r="S25" s="15"/>
-      <c r="T25" s="83"/>
-      <c r="U25" s="83"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
+      <c r="T25" s="149"/>
+      <c r="U25" s="149"/>
+      <c r="V25" s="129"/>
+      <c r="W25" s="129"/>
       <c r="X25" s="15"/>
-      <c r="Y25" s="20"/>
+      <c r="Y25" s="21"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="83"/>
-      <c r="AB25" s="89"/>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="65"/>
-      <c r="AF25" s="20"/>
+      <c r="AA25" s="149"/>
+      <c r="AB25" s="155"/>
+      <c r="AC25" s="129"/>
+      <c r="AD25" s="129"/>
+      <c r="AE25" s="99"/>
+      <c r="AF25" s="21"/>
       <c r="AG25" s="15"/>
-      <c r="AH25" s="59"/>
+      <c r="AH25" s="92"/>
       <c r="AI25" s="18"/>
       <c r="AJ25" s="18"/>
-      <c r="AK25" s="35"/>
-      <c r="AL25" s="41"/>
-      <c r="AM25" s="118"/>
-      <c r="AN25" s="37"/>
-      <c r="AO25" s="37"/>
-      <c r="AP25" s="145"/>
-      <c r="AQ25" s="119"/>
-      <c r="AR25" s="119"/>
+      <c r="AK25" s="41"/>
+      <c r="AL25" s="54"/>
+      <c r="AM25" s="52"/>
+      <c r="AN25" s="44"/>
+      <c r="AO25" s="44"/>
+      <c r="AP25" s="68"/>
+      <c r="AQ25" s="20"/>
+      <c r="AR25" s="47"/>
       <c r="ACF25"/>
       <c r="ACG25"/>
       <c r="ACH25"/>
@@ -6690,728 +6767,728 @@
       <c r="ACL25"/>
     </row>
     <row r="26" spans="1:766" ht="24" customHeight="1">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="46"/>
-      <c r="AB26" s="46"/>
-      <c r="AC26" s="50"/>
-      <c r="AD26" s="50"/>
-      <c r="AE26" s="46"/>
-      <c r="AF26" s="46"/>
-      <c r="AG26" s="46"/>
-      <c r="AH26" s="68"/>
-      <c r="AI26" s="68"/>
-      <c r="AJ26" s="68"/>
-      <c r="AK26" s="68"/>
-      <c r="AL26" s="68"/>
-      <c r="AM26" s="68"/>
-      <c r="AN26" s="68"/>
-      <c r="AO26" s="68"/>
-      <c r="AP26" s="68"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="67"/>
+      <c r="Q26" s="67"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="67"/>
+      <c r="X26" s="67"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="67"/>
+      <c r="AA26" s="67"/>
+      <c r="AB26" s="67"/>
+      <c r="AC26" s="81"/>
+      <c r="AD26" s="81"/>
+      <c r="AE26" s="67"/>
+      <c r="AF26" s="67"/>
+      <c r="AG26" s="67"/>
+      <c r="AH26" s="106"/>
+      <c r="AI26" s="106"/>
+      <c r="AJ26" s="106"/>
+      <c r="AK26" s="106"/>
+      <c r="AL26" s="106"/>
+      <c r="AM26" s="106"/>
+      <c r="AN26" s="106"/>
+      <c r="AO26" s="106"/>
+      <c r="AP26" s="106"/>
     </row>
     <row r="27" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B27" s="43"/>
-      <c r="C27" s="43" t="s">
+      <c r="B27" s="63"/>
+      <c r="C27" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="63">
         <f>COUNTIF(D9:D19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="63">
         <f>COUNTIF(E9:E19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="43">
+      <c r="F27" s="63">
         <f>COUNTIF(F9:F19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="G27" s="43">
+      <c r="G27" s="63">
         <f t="shared" ref="F27:AH27" si="0">COUNTIF(G9:G19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="63">
         <f>COUNTIF(I9:I19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="43">
+      <c r="J27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="43">
+      <c r="K27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M27" s="43">
+      <c r="M27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="43">
+      <c r="N27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="43">
+      <c r="P27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="43">
+      <c r="Q27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27" s="43">
+      <c r="R27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S27" s="43">
+      <c r="S27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T27" s="43">
+      <c r="T27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U27" s="43">
+      <c r="U27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="43">
+      <c r="V27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="43">
+      <c r="W27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="43">
+      <c r="X27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="43">
+      <c r="Y27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="43">
+      <c r="Z27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="43">
+      <c r="AA27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="43">
+      <c r="AB27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="43">
+      <c r="AC27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="43">
+      <c r="AD27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="43">
+      <c r="AE27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="43">
+      <c r="AF27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="43">
+      <c r="AG27" s="63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="27">
+      <c r="AH27" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="27"/>
-      <c r="AJ27" s="27"/>
-      <c r="AK27" s="27"/>
-      <c r="AL27" s="27"/>
-      <c r="AM27" s="27"/>
-      <c r="AN27" s="27"/>
-      <c r="AO27" s="27"/>
-      <c r="AP27" s="68"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="106"/>
     </row>
     <row r="28" spans="1:766" ht="12.75" customHeight="1">
-      <c r="B28" s="27"/>
-      <c r="C28" s="27" t="s">
+      <c r="B28" s="32"/>
+      <c r="C28" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="32">
         <f t="shared" ref="D28:AH28" si="1">COUNTIF(D9:D19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="32">
         <f>COUNTIF(I9:I19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="27">
+      <c r="K28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="27">
+      <c r="L28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M28" s="27">
+      <c r="M28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="27">
+      <c r="N28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P28" s="27">
+      <c r="P28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="27">
+      <c r="R28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S28" s="27">
+      <c r="S28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T28" s="27">
+      <c r="T28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="27">
+      <c r="U28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V28" s="27">
+      <c r="V28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="27">
+      <c r="W28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X28" s="27">
+      <c r="X28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="27">
+      <c r="Y28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="27">
+      <c r="Z28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="27">
+      <c r="AA28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="27">
+      <c r="AB28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="27">
+      <c r="AC28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="27">
+      <c r="AD28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="27">
+      <c r="AE28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="27">
+      <c r="AF28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="27">
+      <c r="AG28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="27">
+      <c r="AH28" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="27"/>
-      <c r="AL28" s="27"/>
-      <c r="AM28" s="27"/>
-      <c r="AN28" s="27"/>
-      <c r="AO28" s="27"/>
-      <c r="AP28" s="68"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="32"/>
+      <c r="AP28" s="106"/>
     </row>
     <row r="29" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27" t="s">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="32">
         <f t="shared" ref="D29:AH29" si="2">COUNTIF(D9:D19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="32">
         <f>COUNTIF(I9:I19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="J29" s="27">
+      <c r="J29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="27">
+      <c r="K29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M29" s="27">
+      <c r="M29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="27">
+      <c r="N29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P29" s="27">
+      <c r="P29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="32">
         <v>2</v>
       </c>
-      <c r="R29" s="27">
+      <c r="R29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="27">
+      <c r="S29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T29" s="27">
+      <c r="T29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U29" s="27">
+      <c r="U29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V29" s="27">
+      <c r="V29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W29" s="27">
+      <c r="W29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X29" s="27">
+      <c r="X29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="27">
+      <c r="Y29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="27">
+      <c r="Z29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="27">
+      <c r="AA29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="27">
+      <c r="AB29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="27">
+      <c r="AC29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="27">
+      <c r="AD29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="27">
+      <c r="AE29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="27">
+      <c r="AF29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="27">
+      <c r="AG29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="27">
+      <c r="AH29" s="32">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="27"/>
-      <c r="AJ29" s="27"/>
-      <c r="AK29" s="27"/>
-      <c r="AL29" s="27"/>
-      <c r="AM29" s="27"/>
-      <c r="AN29" s="27"/>
-      <c r="AO29" s="27"/>
-      <c r="AP29" s="68"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="32"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="32"/>
+      <c r="AP29" s="106"/>
     </row>
     <row r="30" spans="1:766" ht="12" customHeight="1">
-      <c r="A30" s="28"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="32">
         <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="27">
+      <c r="K30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="27">
+      <c r="M30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="27">
+      <c r="N30" s="32">
         <f>COUNTIF(N9:N25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="27">
+      <c r="P30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="27">
+      <c r="R30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S30" s="27">
+      <c r="S30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T30" s="27">
+      <c r="T30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="27">
+      <c r="U30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V30" s="27">
+      <c r="V30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W30" s="27">
+      <c r="W30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X30" s="27">
+      <c r="X30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y30" s="27">
+      <c r="Y30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="27">
+      <c r="Z30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="27">
+      <c r="AA30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="27">
+      <c r="AB30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="27">
+      <c r="AC30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="27">
+      <c r="AD30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="27">
+      <c r="AE30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="27">
+      <c r="AF30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="27">
+      <c r="AG30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="27">
+      <c r="AH30" s="32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="27"/>
-      <c r="AJ30" s="27"/>
-      <c r="AK30" s="27"/>
-      <c r="AL30" s="27"/>
-      <c r="AM30" s="27"/>
-      <c r="AN30" s="27"/>
-      <c r="AO30" s="27"/>
-      <c r="AP30" s="68"/>
+      <c r="AI30" s="32"/>
+      <c r="AJ30" s="32"/>
+      <c r="AK30" s="32"/>
+      <c r="AL30" s="32"/>
+      <c r="AM30" s="32"/>
+      <c r="AN30" s="32"/>
+      <c r="AO30" s="32"/>
+      <c r="AP30" s="106"/>
     </row>
     <row r="31" spans="1:766">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
-      <c r="V31" s="30"/>
-      <c r="W31" s="30"/>
-      <c r="X31" s="30"/>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="30"/>
-      <c r="AD31" s="30"/>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
-      <c r="AG31" s="30"/>
-      <c r="AH31" s="30"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="30"/>
-      <c r="AK31" s="30"/>
-      <c r="AL31" s="69"/>
-      <c r="AO31" s="67"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="35"/>
+      <c r="AF31" s="35"/>
+      <c r="AG31" s="35"/>
+      <c r="AH31" s="35"/>
+      <c r="AI31" s="35"/>
+      <c r="AJ31" s="35"/>
+      <c r="AK31" s="35"/>
+      <c r="AL31" s="107"/>
+      <c r="AO31" s="105"/>
     </row>
     <row r="32" spans="1:766">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
-      <c r="AE32" s="28"/>
-      <c r="AF32" s="28"/>
-      <c r="AG32" s="28"/>
-      <c r="AH32" s="28"/>
-      <c r="AI32" s="28"/>
-      <c r="AJ32" s="28"/>
-      <c r="AK32" s="28"/>
-      <c r="AL32" s="69"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="33"/>
+      <c r="AD32" s="33"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="33"/>
+      <c r="AH32" s="33"/>
+      <c r="AI32" s="33"/>
+      <c r="AJ32" s="33"/>
+      <c r="AK32" s="33"/>
+      <c r="AL32" s="107"/>
     </row>
     <row r="33" spans="1:767" s="2" customFormat="1">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
-      <c r="AD33" s="28"/>
-      <c r="AE33" s="28"/>
-      <c r="AF33" s="28"/>
-      <c r="AG33" s="28"/>
-      <c r="AH33" s="28"/>
-      <c r="AI33" s="28"/>
-      <c r="AJ33" s="28"/>
-      <c r="AK33" s="28"/>
-      <c r="AL33" s="69"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33"/>
+      <c r="U33" s="33"/>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="33"/>
+      <c r="Y33" s="33"/>
+      <c r="Z33" s="33"/>
+      <c r="AA33" s="33"/>
+      <c r="AB33" s="33"/>
+      <c r="AC33" s="33"/>
+      <c r="AD33" s="33"/>
+      <c r="AE33" s="33"/>
+      <c r="AF33" s="33"/>
+      <c r="AG33" s="33"/>
+      <c r="AH33" s="33"/>
+      <c r="AI33" s="33"/>
+      <c r="AJ33" s="33"/>
+      <c r="AK33" s="33"/>
+      <c r="AL33" s="107"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
-      <c r="AR33" s="38"/>
+      <c r="AR33" s="45"/>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -8137,50 +8214,50 @@
       <c r="ACM33"/>
     </row>
     <row r="34" spans="1:767" s="2" customFormat="1">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
-      <c r="AD34" s="28"/>
-      <c r="AE34" s="28"/>
-      <c r="AF34" s="28"/>
-      <c r="AG34" s="28"/>
-      <c r="AH34" s="28"/>
-      <c r="AI34" s="28"/>
-      <c r="AJ34" s="28"/>
-      <c r="AK34" s="28"/>
-      <c r="AL34" s="69"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="33"/>
+      <c r="AJ34" s="33"/>
+      <c r="AK34" s="33"/>
+      <c r="AL34" s="107"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="38"/>
+      <c r="AR34" s="45"/>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
@@ -8906,50 +8983,50 @@
       <c r="ACM34"/>
     </row>
     <row r="35" spans="1:767" s="2" customFormat="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="28"/>
-      <c r="AE35" s="28"/>
-      <c r="AF35" s="28"/>
-      <c r="AG35" s="28"/>
-      <c r="AH35" s="28"/>
-      <c r="AI35" s="28"/>
-      <c r="AJ35" s="28"/>
-      <c r="AK35" s="28"/>
-      <c r="AL35" s="69"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="33"/>
+      <c r="AD35" s="33"/>
+      <c r="AE35" s="33"/>
+      <c r="AF35" s="33"/>
+      <c r="AG35" s="33"/>
+      <c r="AH35" s="33"/>
+      <c r="AI35" s="33"/>
+      <c r="AJ35" s="33"/>
+      <c r="AK35" s="33"/>
+      <c r="AL35" s="107"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
-      <c r="AR35" s="38"/>
+      <c r="AR35" s="45"/>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
@@ -9675,50 +9752,50 @@
       <c r="ACM35"/>
     </row>
     <row r="36" spans="1:767" s="2" customFormat="1">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
-      <c r="AD36" s="28"/>
-      <c r="AE36" s="28"/>
-      <c r="AF36" s="28"/>
-      <c r="AG36" s="28"/>
-      <c r="AH36" s="28"/>
-      <c r="AI36" s="28"/>
-      <c r="AJ36" s="28"/>
-      <c r="AK36" s="28"/>
-      <c r="AL36" s="69"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
+      <c r="AD36" s="33"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="33"/>
+      <c r="AH36" s="33"/>
+      <c r="AI36" s="33"/>
+      <c r="AJ36" s="33"/>
+      <c r="AK36" s="33"/>
+      <c r="AL36" s="107"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
-      <c r="AR36" s="38"/>
+      <c r="AR36" s="45"/>
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
@@ -10444,50 +10521,50 @@
       <c r="ACM36"/>
     </row>
     <row r="37" spans="1:767" s="2" customFormat="1">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
-      <c r="AE37" s="28"/>
-      <c r="AF37" s="28"/>
-      <c r="AG37" s="28"/>
-      <c r="AH37" s="28"/>
-      <c r="AI37" s="28"/>
-      <c r="AJ37" s="28"/>
-      <c r="AK37" s="28"/>
-      <c r="AL37" s="69"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="33"/>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="33"/>
+      <c r="Y37" s="33"/>
+      <c r="Z37" s="33"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="33"/>
+      <c r="AC37" s="33"/>
+      <c r="AD37" s="33"/>
+      <c r="AE37" s="33"/>
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="33"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33"/>
+      <c r="AL37" s="107"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
-      <c r="AR37" s="38"/>
+      <c r="AR37" s="45"/>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
@@ -11213,50 +11290,50 @@
       <c r="ACM37"/>
     </row>
     <row r="38" spans="1:767" s="2" customFormat="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
-      <c r="AD38" s="28"/>
-      <c r="AE38" s="28"/>
-      <c r="AF38" s="28"/>
-      <c r="AG38" s="28"/>
-      <c r="AH38" s="28"/>
-      <c r="AI38" s="28"/>
-      <c r="AJ38" s="28"/>
-      <c r="AK38" s="28"/>
-      <c r="AL38" s="69"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="33"/>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="33"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
+      <c r="AC38" s="33"/>
+      <c r="AD38" s="33"/>
+      <c r="AE38" s="33"/>
+      <c r="AF38" s="33"/>
+      <c r="AG38" s="33"/>
+      <c r="AH38" s="33"/>
+      <c r="AI38" s="33"/>
+      <c r="AJ38" s="33"/>
+      <c r="AK38" s="33"/>
+      <c r="AL38" s="107"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
-      <c r="AR38" s="38"/>
+      <c r="AR38" s="45"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
@@ -11982,50 +12059,50 @@
       <c r="ACM38"/>
     </row>
     <row r="39" spans="1:767" s="2" customFormat="1">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-      <c r="N39" s="28"/>
-      <c r="O39" s="28"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
-      <c r="AD39" s="28"/>
-      <c r="AE39" s="28"/>
-      <c r="AF39" s="28"/>
-      <c r="AG39" s="28"/>
-      <c r="AH39" s="28"/>
-      <c r="AI39" s="28"/>
-      <c r="AJ39" s="28"/>
-      <c r="AK39" s="28"/>
-      <c r="AL39" s="69"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="33"/>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="33"/>
+      <c r="AF39" s="33"/>
+      <c r="AG39" s="33"/>
+      <c r="AH39" s="33"/>
+      <c r="AI39" s="33"/>
+      <c r="AJ39" s="33"/>
+      <c r="AK39" s="33"/>
+      <c r="AL39" s="107"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
-      <c r="AR39" s="38"/>
+      <c r="AR39" s="45"/>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
@@ -12751,50 +12828,50 @@
       <c r="ACM39"/>
     </row>
     <row r="40" spans="1:767" s="2" customFormat="1">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
-      <c r="AD40" s="28"/>
-      <c r="AE40" s="28"/>
-      <c r="AF40" s="28"/>
-      <c r="AG40" s="28"/>
-      <c r="AH40" s="28"/>
-      <c r="AI40" s="28"/>
-      <c r="AJ40" s="28"/>
-      <c r="AK40" s="28"/>
-      <c r="AL40" s="69"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="33"/>
+      <c r="M40" s="33"/>
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="33"/>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="33"/>
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="33"/>
+      <c r="AA40" s="33"/>
+      <c r="AB40" s="33"/>
+      <c r="AC40" s="33"/>
+      <c r="AD40" s="33"/>
+      <c r="AE40" s="33"/>
+      <c r="AF40" s="33"/>
+      <c r="AG40" s="33"/>
+      <c r="AH40" s="33"/>
+      <c r="AI40" s="33"/>
+      <c r="AJ40" s="33"/>
+      <c r="AK40" s="33"/>
+      <c r="AL40" s="107"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
-      <c r="AR40" s="38"/>
+      <c r="AR40" s="45"/>
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
@@ -13520,50 +13597,50 @@
       <c r="ACM40"/>
     </row>
     <row r="41" spans="1:767" s="2" customFormat="1">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="28"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="28"/>
-      <c r="X41" s="28"/>
-      <c r="Y41" s="28"/>
-      <c r="Z41" s="28"/>
-      <c r="AA41" s="28"/>
-      <c r="AB41" s="28"/>
-      <c r="AC41" s="28"/>
-      <c r="AD41" s="28"/>
-      <c r="AE41" s="28"/>
-      <c r="AF41" s="28"/>
-      <c r="AG41" s="28"/>
-      <c r="AH41" s="28"/>
-      <c r="AI41" s="28"/>
-      <c r="AJ41" s="28"/>
-      <c r="AK41" s="28"/>
-      <c r="AL41" s="69"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33"/>
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="33"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="33"/>
+      <c r="Y41" s="33"/>
+      <c r="Z41" s="33"/>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33"/>
+      <c r="AC41" s="33"/>
+      <c r="AD41" s="33"/>
+      <c r="AE41" s="33"/>
+      <c r="AF41" s="33"/>
+      <c r="AG41" s="33"/>
+      <c r="AH41" s="33"/>
+      <c r="AI41" s="33"/>
+      <c r="AJ41" s="33"/>
+      <c r="AK41" s="33"/>
+      <c r="AL41" s="107"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
-      <c r="AR41" s="38"/>
+      <c r="AR41" s="45"/>
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
@@ -14289,50 +14366,50 @@
       <c r="ACM41"/>
     </row>
     <row r="42" spans="1:767" s="2" customFormat="1">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="28"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
-      <c r="AC42" s="28"/>
-      <c r="AD42" s="28"/>
-      <c r="AE42" s="28"/>
-      <c r="AF42" s="28"/>
-      <c r="AG42" s="28"/>
-      <c r="AH42" s="28"/>
-      <c r="AI42" s="28"/>
-      <c r="AJ42" s="28"/>
-      <c r="AK42" s="28"/>
-      <c r="AL42" s="69"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33"/>
+      <c r="U42" s="33"/>
+      <c r="V42" s="33"/>
+      <c r="W42" s="33"/>
+      <c r="X42" s="33"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="33"/>
+      <c r="AF42" s="33"/>
+      <c r="AG42" s="33"/>
+      <c r="AH42" s="33"/>
+      <c r="AI42" s="33"/>
+      <c r="AJ42" s="33"/>
+      <c r="AK42" s="33"/>
+      <c r="AL42" s="107"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
-      <c r="AR42" s="38"/>
+      <c r="AR42" s="45"/>
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
@@ -15058,50 +15135,50 @@
       <c r="ACM42"/>
     </row>
     <row r="43" spans="1:767" s="2" customFormat="1">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="28"/>
-      <c r="AB43" s="28"/>
-      <c r="AC43" s="28"/>
-      <c r="AD43" s="28"/>
-      <c r="AE43" s="28"/>
-      <c r="AF43" s="28"/>
-      <c r="AG43" s="28"/>
-      <c r="AH43" s="28"/>
-      <c r="AI43" s="28"/>
-      <c r="AJ43" s="28"/>
-      <c r="AK43" s="28"/>
-      <c r="AL43" s="69"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+      <c r="M43" s="33"/>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="33"/>
+      <c r="U43" s="33"/>
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="33"/>
+      <c r="Y43" s="33"/>
+      <c r="Z43" s="33"/>
+      <c r="AA43" s="33"/>
+      <c r="AB43" s="33"/>
+      <c r="AC43" s="33"/>
+      <c r="AD43" s="33"/>
+      <c r="AE43" s="33"/>
+      <c r="AF43" s="33"/>
+      <c r="AG43" s="33"/>
+      <c r="AH43" s="33"/>
+      <c r="AI43" s="33"/>
+      <c r="AJ43" s="33"/>
+      <c r="AK43" s="33"/>
+      <c r="AL43" s="107"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
-      <c r="AR43" s="38"/>
+      <c r="AR43" s="45"/>
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
@@ -15827,50 +15904,50 @@
       <c r="ACM43"/>
     </row>
     <row r="44" spans="1:767" s="2" customFormat="1">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
-      <c r="T44" s="28"/>
-      <c r="U44" s="28"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="28"/>
-      <c r="X44" s="28"/>
-      <c r="Y44" s="28"/>
-      <c r="Z44" s="28"/>
-      <c r="AA44" s="28"/>
-      <c r="AB44" s="28"/>
-      <c r="AC44" s="28"/>
-      <c r="AD44" s="28"/>
-      <c r="AE44" s="28"/>
-      <c r="AF44" s="28"/>
-      <c r="AG44" s="28"/>
-      <c r="AH44" s="28"/>
-      <c r="AI44" s="28"/>
-      <c r="AJ44" s="28"/>
-      <c r="AK44" s="28"/>
-      <c r="AL44" s="69"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="33"/>
+      <c r="M44" s="33"/>
+      <c r="N44" s="33"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="33"/>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
+      <c r="Y44" s="33"/>
+      <c r="Z44" s="33"/>
+      <c r="AA44" s="33"/>
+      <c r="AB44" s="33"/>
+      <c r="AC44" s="33"/>
+      <c r="AD44" s="33"/>
+      <c r="AE44" s="33"/>
+      <c r="AF44" s="33"/>
+      <c r="AG44" s="33"/>
+      <c r="AH44" s="33"/>
+      <c r="AI44" s="33"/>
+      <c r="AJ44" s="33"/>
+      <c r="AK44" s="33"/>
+      <c r="AL44" s="107"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
-      <c r="AR44" s="38"/>
+      <c r="AR44" s="45"/>
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
@@ -16596,50 +16673,50 @@
       <c r="ACM44"/>
     </row>
     <row r="45" spans="1:767" s="2" customFormat="1">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28"/>
-      <c r="S45" s="28"/>
-      <c r="T45" s="28"/>
-      <c r="U45" s="28"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="28"/>
-      <c r="X45" s="28"/>
-      <c r="Y45" s="28"/>
-      <c r="Z45" s="28"/>
-      <c r="AA45" s="28"/>
-      <c r="AB45" s="28"/>
-      <c r="AC45" s="28"/>
-      <c r="AD45" s="28"/>
-      <c r="AE45" s="28"/>
-      <c r="AF45" s="28"/>
-      <c r="AG45" s="28"/>
-      <c r="AH45" s="28"/>
-      <c r="AI45" s="28"/>
-      <c r="AJ45" s="28"/>
-      <c r="AK45" s="28"/>
-      <c r="AL45" s="69"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+      <c r="AA45" s="33"/>
+      <c r="AB45" s="33"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
+      <c r="AE45" s="33"/>
+      <c r="AF45" s="33"/>
+      <c r="AG45" s="33"/>
+      <c r="AH45" s="33"/>
+      <c r="AI45" s="33"/>
+      <c r="AJ45" s="33"/>
+      <c r="AK45" s="33"/>
+      <c r="AL45" s="107"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
-      <c r="AR45" s="38"/>
+      <c r="AR45" s="45"/>
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
@@ -17365,50 +17442,50 @@
       <c r="ACM45"/>
     </row>
     <row r="46" spans="1:767" s="2" customFormat="1">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
-      <c r="AD46" s="28"/>
-      <c r="AE46" s="28"/>
-      <c r="AF46" s="28"/>
-      <c r="AG46" s="28"/>
-      <c r="AH46" s="28"/>
-      <c r="AI46" s="28"/>
-      <c r="AJ46" s="28"/>
-      <c r="AK46" s="28"/>
-      <c r="AL46" s="69"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="33"/>
+      <c r="AC46" s="33"/>
+      <c r="AD46" s="33"/>
+      <c r="AE46" s="33"/>
+      <c r="AF46" s="33"/>
+      <c r="AG46" s="33"/>
+      <c r="AH46" s="33"/>
+      <c r="AI46" s="33"/>
+      <c r="AJ46" s="33"/>
+      <c r="AK46" s="33"/>
+      <c r="AL46" s="107"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
-      <c r="AR46" s="38"/>
+      <c r="AR46" s="45"/>
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
@@ -18134,50 +18211,50 @@
       <c r="ACM46"/>
     </row>
     <row r="47" spans="1:767" s="2" customFormat="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
-      <c r="Q47" s="28"/>
-      <c r="R47" s="28"/>
-      <c r="S47" s="28"/>
-      <c r="T47" s="28"/>
-      <c r="U47" s="28"/>
-      <c r="V47" s="28"/>
-      <c r="W47" s="28"/>
-      <c r="X47" s="28"/>
-      <c r="Y47" s="28"/>
-      <c r="Z47" s="28"/>
-      <c r="AA47" s="28"/>
-      <c r="AB47" s="28"/>
-      <c r="AC47" s="28"/>
-      <c r="AD47" s="28"/>
-      <c r="AE47" s="28"/>
-      <c r="AF47" s="28"/>
-      <c r="AG47" s="28"/>
-      <c r="AH47" s="28"/>
-      <c r="AI47" s="28"/>
-      <c r="AJ47" s="28"/>
-      <c r="AK47" s="28"/>
-      <c r="AL47" s="69"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="33"/>
+      <c r="Y47" s="33"/>
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="33"/>
+      <c r="AB47" s="33"/>
+      <c r="AC47" s="33"/>
+      <c r="AD47" s="33"/>
+      <c r="AE47" s="33"/>
+      <c r="AF47" s="33"/>
+      <c r="AG47" s="33"/>
+      <c r="AH47" s="33"/>
+      <c r="AI47" s="33"/>
+      <c r="AJ47" s="33"/>
+      <c r="AK47" s="33"/>
+      <c r="AL47" s="107"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
-      <c r="AR47" s="38"/>
+      <c r="AR47" s="45"/>
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
@@ -18903,50 +18980,50 @@
       <c r="ACM47"/>
     </row>
     <row r="48" spans="1:767" s="2" customFormat="1">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="28"/>
-      <c r="S48" s="28"/>
-      <c r="T48" s="28"/>
-      <c r="U48" s="28"/>
-      <c r="V48" s="28"/>
-      <c r="W48" s="28"/>
-      <c r="X48" s="28"/>
-      <c r="Y48" s="28"/>
-      <c r="Z48" s="28"/>
-      <c r="AA48" s="28"/>
-      <c r="AB48" s="28"/>
-      <c r="AC48" s="28"/>
-      <c r="AD48" s="28"/>
-      <c r="AE48" s="28"/>
-      <c r="AF48" s="28"/>
-      <c r="AG48" s="28"/>
-      <c r="AH48" s="28"/>
-      <c r="AI48" s="28"/>
-      <c r="AJ48" s="28"/>
-      <c r="AK48" s="28"/>
-      <c r="AL48" s="69"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="33"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="33"/>
+      <c r="AA48" s="33"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
+      <c r="AF48" s="33"/>
+      <c r="AG48" s="33"/>
+      <c r="AH48" s="33"/>
+      <c r="AI48" s="33"/>
+      <c r="AJ48" s="33"/>
+      <c r="AK48" s="33"/>
+      <c r="AL48" s="107"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
-      <c r="AR48" s="38"/>
+      <c r="AR48" s="45"/>
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
@@ -19672,50 +19749,50 @@
       <c r="ACM48"/>
     </row>
     <row r="49" spans="1:767" s="2" customFormat="1">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
-      <c r="AD49" s="28"/>
-      <c r="AE49" s="28"/>
-      <c r="AF49" s="28"/>
-      <c r="AG49" s="28"/>
-      <c r="AH49" s="28"/>
-      <c r="AI49" s="28"/>
-      <c r="AJ49" s="28"/>
-      <c r="AK49" s="28"/>
-      <c r="AL49" s="69"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33"/>
+      <c r="AE49" s="33"/>
+      <c r="AF49" s="33"/>
+      <c r="AG49" s="33"/>
+      <c r="AH49" s="33"/>
+      <c r="AI49" s="33"/>
+      <c r="AJ49" s="33"/>
+      <c r="AK49" s="33"/>
+      <c r="AL49" s="107"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
-      <c r="AR49" s="38"/>
+      <c r="AR49" s="45"/>
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
@@ -20441,50 +20518,50 @@
       <c r="ACM49"/>
     </row>
     <row r="50" spans="1:767" s="2" customFormat="1">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
-      <c r="N50" s="28"/>
-      <c r="O50" s="28"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="28"/>
-      <c r="R50" s="28"/>
-      <c r="S50" s="28"/>
-      <c r="T50" s="28"/>
-      <c r="U50" s="28"/>
-      <c r="V50" s="28"/>
-      <c r="W50" s="28"/>
-      <c r="X50" s="28"/>
-      <c r="Y50" s="28"/>
-      <c r="Z50" s="28"/>
-      <c r="AA50" s="28"/>
-      <c r="AB50" s="28"/>
-      <c r="AC50" s="28"/>
-      <c r="AD50" s="28"/>
-      <c r="AE50" s="28"/>
-      <c r="AF50" s="28"/>
-      <c r="AG50" s="28"/>
-      <c r="AH50" s="28"/>
-      <c r="AI50" s="28"/>
-      <c r="AJ50" s="28"/>
-      <c r="AK50" s="28"/>
-      <c r="AL50" s="69"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="33"/>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33"/>
+      <c r="Q50" s="33"/>
+      <c r="R50" s="33"/>
+      <c r="S50" s="33"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="33"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="33"/>
+      <c r="Y50" s="33"/>
+      <c r="Z50" s="33"/>
+      <c r="AA50" s="33"/>
+      <c r="AB50" s="33"/>
+      <c r="AC50" s="33"/>
+      <c r="AD50" s="33"/>
+      <c r="AE50" s="33"/>
+      <c r="AF50" s="33"/>
+      <c r="AG50" s="33"/>
+      <c r="AH50" s="33"/>
+      <c r="AI50" s="33"/>
+      <c r="AJ50" s="33"/>
+      <c r="AK50" s="33"/>
+      <c r="AL50" s="107"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
       <c r="AO50" s="3"/>
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
-      <c r="AR50" s="38"/>
+      <c r="AR50" s="45"/>
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>

--- a/nurse_scheduler_template.xlsx
+++ b/nurse_scheduler_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2050D00-9B3C-40B6-8044-E56CBF5530D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A966DE56-6147-4528-B1E5-52A89A86012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{B332721F-AB2B-4BF1-A12F-4722F279DAC4}"/>
   </bookViews>
@@ -176,7 +176,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-412]General"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -272,14 +272,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
@@ -305,28 +297,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -414,6 +384,26 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9C5700"/>
+      <name val="Dotum"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -736,21 +726,6 @@
       </diagonal>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -815,26 +790,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,55 +851,42 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -925,88 +902,47 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="13" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1017,116 +953,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="26" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="22" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="25" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1138,13 +1024,238 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="25" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="29" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="23" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1198,252 +1309,64 @@
     <xf numFmtId="176" fontId="5" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="10" xfId="5" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="3" borderId="10" xfId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="3" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="3" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="28" fillId="9" borderId="4" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="9" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="6" xfId="2" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="9" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1767,13 +1690,13 @@
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="3" style="4" customWidth="1"/>
     <col min="3" max="3" width="5.44140625" style="2" customWidth="1"/>
-    <col min="4" max="5" width="3.6640625" style="29" customWidth="1"/>
+    <col min="4" max="5" width="3.6640625" style="24" customWidth="1"/>
     <col min="6" max="13" width="3.6640625" style="3" customWidth="1"/>
-    <col min="14" max="17" width="3.6640625" style="29" customWidth="1"/>
+    <col min="14" max="17" width="3.6640625" style="24" customWidth="1"/>
     <col min="18" max="18" width="3.6640625" style="3" customWidth="1"/>
-    <col min="19" max="32" width="3.6640625" style="29" customWidth="1"/>
-    <col min="33" max="33" width="3.44140625" style="29" customWidth="1"/>
-    <col min="34" max="34" width="3.5546875" style="29" customWidth="1"/>
+    <col min="19" max="32" width="3.6640625" style="24" customWidth="1"/>
+    <col min="33" max="33" width="3.44140625" style="24" customWidth="1"/>
+    <col min="34" max="34" width="3.5546875" style="24" customWidth="1"/>
     <col min="35" max="35" width="3" style="3" customWidth="1"/>
     <col min="36" max="36" width="3" style="2" customWidth="1"/>
     <col min="37" max="37" width="4.5546875" style="2" customWidth="1"/>
@@ -1783,7 +1706,7 @@
     <col min="41" max="41" width="7.5546875" style="3" customWidth="1"/>
     <col min="42" max="42" width="6.88671875" style="3" customWidth="1"/>
     <col min="43" max="43" width="7.5546875" style="3" customWidth="1"/>
-    <col min="44" max="44" width="5.44140625" style="45" customWidth="1"/>
+    <col min="44" max="44" width="5.44140625" style="38" customWidth="1"/>
     <col min="45" max="765" width="7.5546875" style="3" customWidth="1"/>
     <col min="766" max="766" width="8.88671875" style="3" customWidth="1"/>
     <col min="767" max="767" width="8.88671875" customWidth="1"/>
@@ -1823,93 +1746,93 @@
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
-      <c r="AI1" s="107"/>
-      <c r="AJ1" s="107"/>
-      <c r="AK1" s="107"/>
-      <c r="AL1" s="107"/>
-      <c r="AV1" s="70"/>
-      <c r="AW1" s="70"/>
+      <c r="AI1" s="69"/>
+      <c r="AJ1" s="69"/>
+      <c r="AK1" s="69"/>
+      <c r="AL1" s="69"/>
+      <c r="AV1" s="48"/>
+      <c r="AW1" s="48"/>
     </row>
     <row r="2" spans="1:766" ht="49.5" customHeight="1">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="114"/>
-      <c r="AG2" s="114"/>
-      <c r="AH2" s="114"/>
-      <c r="AI2" s="114"/>
-      <c r="AJ2" s="114"/>
-      <c r="AK2" s="114"/>
-      <c r="AL2" s="114"/>
-      <c r="AM2" s="114"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="151"/>
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="151"/>
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="151"/>
+      <c r="X2" s="151"/>
+      <c r="Y2" s="151"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="151"/>
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="151"/>
+      <c r="AF2" s="151"/>
+      <c r="AG2" s="151"/>
+      <c r="AH2" s="151"/>
+      <c r="AI2" s="151"/>
+      <c r="AJ2" s="151"/>
+      <c r="AK2" s="151"/>
+      <c r="AL2" s="151"/>
+      <c r="AM2" s="151"/>
     </row>
     <row r="3" spans="1:766" ht="6" customHeight="1" thickBot="1">
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="103"/>
-      <c r="T3" s="103"/>
-      <c r="U3" s="103"/>
-      <c r="V3" s="103"/>
-      <c r="W3" s="103"/>
-      <c r="X3" s="103"/>
-      <c r="Y3" s="103"/>
-      <c r="Z3" s="103"/>
-      <c r="AA3" s="103"/>
-      <c r="AB3" s="103"/>
-      <c r="AC3" s="103"/>
-      <c r="AD3" s="103"/>
-      <c r="AE3" s="103"/>
-      <c r="AF3" s="103"/>
-      <c r="AG3" s="103"/>
-      <c r="AH3" s="103"/>
-      <c r="AI3" s="103"/>
-      <c r="AJ3" s="103"/>
-      <c r="AK3" s="103"/>
-      <c r="AL3" s="103"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="115"/>
+      <c r="T3" s="115"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
+      <c r="AE3" s="115"/>
+      <c r="AF3" s="115"/>
+      <c r="AG3" s="115"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="115"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
     </row>
     <row r="4" spans="1:766" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="B4" s="4"/>
@@ -1935,42 +1858,42 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
+      <c r="Z4" s="152"/>
+      <c r="AA4" s="152"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
-      <c r="AD4" s="108"/>
-      <c r="AE4" s="116" t="s">
+      <c r="AD4" s="70"/>
+      <c r="AE4" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="AF4" s="117"/>
-      <c r="AG4" s="118" t="s">
+      <c r="AF4" s="154"/>
+      <c r="AG4" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="AH4" s="119"/>
-      <c r="AR4" s="45"/>
+      <c r="AH4" s="156"/>
+      <c r="AR4" s="38"/>
     </row>
     <row r="5" spans="1:766" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="122"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="159"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="123" t="s">
+      <c r="H5" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="124"/>
-      <c r="N5" s="124"/>
-      <c r="O5" s="124"/>
-      <c r="P5" s="124"/>
-      <c r="Q5" s="125"/>
+      <c r="I5" s="161"/>
+      <c r="J5" s="161"/>
+      <c r="K5" s="161"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="161"/>
+      <c r="N5" s="161"/>
+      <c r="O5" s="161"/>
+      <c r="P5" s="161"/>
+      <c r="Q5" s="162"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -1978,16 +1901,16 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Z5" s="115"/>
-      <c r="AA5" s="115"/>
-      <c r="AB5" s="115"/>
-      <c r="AC5" s="115"/>
-      <c r="AD5" s="104"/>
-      <c r="AE5" s="126"/>
-      <c r="AF5" s="127"/>
-      <c r="AG5" s="127"/>
-      <c r="AH5" s="128"/>
-      <c r="AR5" s="45" t="s">
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="116"/>
+      <c r="AE5" s="163"/>
+      <c r="AF5" s="164"/>
+      <c r="AG5" s="164"/>
+      <c r="AH5" s="165"/>
+      <c r="AR5" s="38" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2029,129 +1952,129 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7"/>
-      <c r="AK6" s="107"/>
-      <c r="AL6" s="107"/>
+      <c r="AK6" s="69"/>
+      <c r="AL6" s="69"/>
     </row>
     <row r="7" spans="1:766" s="9" customFormat="1" ht="30.75" customHeight="1">
-      <c r="B7" s="109" t="s">
+      <c r="B7" s="146" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="85">
+      <c r="C7" s="146"/>
+      <c r="D7" s="53">
         <v>1</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="53">
         <v>2</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="56">
         <v>3</v>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="56">
         <v>4</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="54">
         <v>5</v>
       </c>
-      <c r="I7" s="87">
+      <c r="I7" s="55">
         <v>6</v>
       </c>
-      <c r="J7" s="85">
+      <c r="J7" s="53">
         <v>7</v>
       </c>
-      <c r="K7" s="85">
+      <c r="K7" s="53">
         <v>8</v>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="56">
         <v>9</v>
       </c>
-      <c r="M7" s="88">
+      <c r="M7" s="56">
         <v>10</v>
       </c>
-      <c r="N7" s="88">
+      <c r="N7" s="56">
         <v>11</v>
       </c>
-      <c r="O7" s="87">
+      <c r="O7" s="55">
         <v>12</v>
       </c>
-      <c r="P7" s="87">
+      <c r="P7" s="55">
         <v>13</v>
       </c>
-      <c r="Q7" s="85">
+      <c r="Q7" s="53">
         <v>14</v>
       </c>
-      <c r="R7" s="85">
+      <c r="R7" s="53">
         <v>15</v>
       </c>
-      <c r="S7" s="85">
+      <c r="S7" s="53">
         <v>16</v>
       </c>
-      <c r="T7" s="88">
+      <c r="T7" s="56">
         <v>17</v>
       </c>
-      <c r="U7" s="88">
+      <c r="U7" s="56">
         <v>18</v>
       </c>
-      <c r="V7" s="87">
+      <c r="V7" s="55">
         <v>19</v>
       </c>
-      <c r="W7" s="87">
+      <c r="W7" s="55">
         <v>20</v>
       </c>
-      <c r="X7" s="85">
+      <c r="X7" s="53">
         <v>21</v>
       </c>
-      <c r="Y7" s="85">
+      <c r="Y7" s="53">
         <v>22</v>
       </c>
-      <c r="Z7" s="85">
+      <c r="Z7" s="53">
         <v>23</v>
       </c>
-      <c r="AA7" s="84">
+      <c r="AA7" s="52">
         <v>24</v>
       </c>
-      <c r="AB7" s="84">
+      <c r="AB7" s="52">
         <v>25</v>
       </c>
-      <c r="AC7" s="87">
+      <c r="AC7" s="55">
         <v>26</v>
       </c>
-      <c r="AD7" s="87">
+      <c r="AD7" s="55">
         <v>27</v>
       </c>
-      <c r="AE7" s="85">
+      <c r="AE7" s="53">
         <v>28</v>
       </c>
-      <c r="AF7" s="85">
+      <c r="AF7" s="53">
         <v>29</v>
       </c>
-      <c r="AG7" s="85">
+      <c r="AG7" s="53">
         <v>30</v>
       </c>
-      <c r="AH7" s="88">
+      <c r="AH7" s="56">
         <v>31</v>
       </c>
-      <c r="AI7" s="101" t="s">
+      <c r="AI7" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="AJ7" s="48" t="s">
+      <c r="AJ7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AK7" s="101" t="s">
+      <c r="AK7" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="AL7" s="49" t="s">
+      <c r="AL7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="AM7" s="110" t="s">
+      <c r="AM7" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="AN7" s="111" t="s">
+      <c r="AN7" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="AO7" s="102"/>
-      <c r="AP7" s="46"/>
+      <c r="AO7" s="114"/>
+      <c r="AP7" s="39"/>
       <c r="AQ7" s="10"/>
-      <c r="AR7" s="46"/>
+      <c r="AR7" s="39"/>
       <c r="AS7" s="11"/>
       <c r="AT7" s="11"/>
       <c r="AU7" s="11"/>
@@ -2870,117 +2793,117 @@
       <c r="ACF7" s="11"/>
     </row>
     <row r="8" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="149" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="85" t="s">
+      <c r="C8" s="149"/>
+      <c r="D8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="F8" s="183" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="86" t="s">
+      <c r="G8" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="183" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="I8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="J8" s="85" t="s">
+      <c r="J8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="85" t="s">
+      <c r="K8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="88" t="s">
+      <c r="L8" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="88" t="s">
+      <c r="M8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="88" t="s">
+      <c r="N8" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="87" t="s">
+      <c r="O8" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="87" t="s">
+      <c r="P8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="85" t="s">
+      <c r="Q8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="85" t="s">
+      <c r="R8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="85" t="s">
+      <c r="S8" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="T8" s="88" t="s">
+      <c r="T8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="88" t="s">
+      <c r="U8" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="V8" s="87" t="s">
+      <c r="V8" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="W8" s="87" t="s">
+      <c r="W8" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="85" t="s">
+      <c r="X8" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="Y8" s="89" t="s">
+      <c r="Y8" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="89" t="s">
+      <c r="Z8" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="84" t="s">
+      <c r="AA8" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="AB8" s="91" t="s">
+      <c r="AB8" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="AC8" s="87" t="s">
+      <c r="AC8" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="AD8" s="87" t="s">
+      <c r="AD8" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="AE8" s="90" t="s">
+      <c r="AE8" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="AF8" s="85" t="s">
+      <c r="AF8" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="AG8" s="85" t="s">
+      <c r="AG8" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="AH8" s="84" t="s">
+      <c r="AH8" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="AI8" s="101"/>
-      <c r="AJ8" s="101"/>
-      <c r="AK8" s="101"/>
-      <c r="AL8" s="50"/>
-      <c r="AM8" s="110"/>
-      <c r="AN8" s="111"/>
-      <c r="AO8" s="102"/>
-      <c r="AP8" s="69" t="s">
+      <c r="AI8" s="113"/>
+      <c r="AJ8" s="113"/>
+      <c r="AK8" s="113"/>
+      <c r="AL8" s="42"/>
+      <c r="AM8" s="147"/>
+      <c r="AN8" s="148"/>
+      <c r="AO8" s="114"/>
+      <c r="AP8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AQ8" s="46" t="s">
+      <c r="AQ8" s="39" t="s">
         <v>29</v>
       </c>
       <c r="AR8" s="10" t="s">
@@ -3703,52 +3626,52 @@
       <c r="ACF8" s="11"/>
     </row>
     <row r="9" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A9" s="65">
+      <c r="A9" s="45">
         <v>1</v>
       </c>
-      <c r="B9" s="101"/>
-      <c r="C9" s="51"/>
+      <c r="B9" s="117"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="13"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
+      <c r="F9" s="166"/>
+      <c r="G9" s="166"/>
+      <c r="H9" s="166"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="156"/>
-      <c r="M9" s="156"/>
-      <c r="N9" s="156"/>
-      <c r="O9" s="129"/>
+      <c r="L9" s="166"/>
+      <c r="M9" s="166"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="16"/>
       <c r="P9" s="13"/>
       <c r="Q9" s="13"/>
-      <c r="R9" s="130"/>
+      <c r="R9" s="71"/>
       <c r="S9" s="16"/>
-      <c r="T9" s="143"/>
-      <c r="U9" s="143"/>
+      <c r="T9" s="78"/>
+      <c r="U9" s="78"/>
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="43"/>
+      <c r="Y9" s="36"/>
       <c r="Z9" s="16"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="129"/>
-      <c r="AD9" s="129"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="43"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="36"/>
       <c r="AG9" s="16"/>
-      <c r="AH9" s="93"/>
+      <c r="AH9" s="60"/>
       <c r="AI9" s="18"/>
       <c r="AJ9" s="18"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="50"/>
-      <c r="AM9" s="52"/>
-      <c r="AN9" s="53"/>
-      <c r="AO9" s="53"/>
-      <c r="AP9" s="46"/>
-      <c r="AQ9" s="10"/>
-      <c r="AR9" s="46"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="41"/>
+      <c r="AM9" s="118"/>
+      <c r="AN9" s="167"/>
+      <c r="AO9" s="167"/>
+      <c r="AP9" s="119"/>
+      <c r="AQ9" s="119"/>
+      <c r="AR9" s="119"/>
       <c r="AS9" s="11"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
@@ -4465,52 +4388,52 @@
       <c r="ACD9" s="11"/>
     </row>
     <row r="10" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="65">
+      <c r="A10" s="45">
         <v>2</v>
       </c>
-      <c r="B10" s="101"/>
-      <c r="C10" s="51"/>
+      <c r="B10" s="117"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="13"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="160"/>
-      <c r="I10" s="129"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="168"/>
+      <c r="I10" s="16"/>
       <c r="J10" s="13"/>
       <c r="K10" s="16"/>
-      <c r="L10" s="143"/>
-      <c r="M10" s="143"/>
-      <c r="N10" s="143"/>
-      <c r="O10" s="129"/>
-      <c r="P10" s="129"/>
+      <c r="L10" s="78"/>
+      <c r="M10" s="78"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
-      <c r="T10" s="143"/>
-      <c r="U10" s="143"/>
-      <c r="V10" s="129"/>
-      <c r="W10" s="129"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="78"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="43"/>
+      <c r="Y10" s="36"/>
       <c r="Z10" s="16"/>
-      <c r="AA10" s="143"/>
-      <c r="AB10" s="150"/>
-      <c r="AC10" s="129"/>
-      <c r="AD10" s="129"/>
-      <c r="AE10" s="82"/>
-      <c r="AF10" s="43"/>
+      <c r="AA10" s="78"/>
+      <c r="AB10" s="84"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="51"/>
+      <c r="AF10" s="36"/>
       <c r="AG10" s="16"/>
-      <c r="AH10" s="92"/>
+      <c r="AH10" s="59"/>
       <c r="AI10" s="18"/>
       <c r="AJ10" s="18"/>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="50"/>
-      <c r="AM10" s="52"/>
-      <c r="AN10" s="53"/>
-      <c r="AO10" s="53"/>
-      <c r="AP10" s="46"/>
-      <c r="AQ10" s="10"/>
-      <c r="AR10" s="46"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="118"/>
+      <c r="AN10" s="167"/>
+      <c r="AO10" s="167"/>
+      <c r="AP10" s="119"/>
+      <c r="AQ10" s="119"/>
+      <c r="AR10" s="119"/>
       <c r="AS10" s="11"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
@@ -5227,52 +5150,52 @@
       <c r="ACD10" s="11"/>
     </row>
     <row r="11" spans="1:766" s="9" customFormat="1" ht="24" customHeight="1">
-      <c r="A11" s="65">
+      <c r="A11" s="45">
         <v>3</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="51"/>
+      <c r="B11" s="117"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="13"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="129"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="16"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
-      <c r="N11" s="143"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="16"/>
       <c r="S11" s="13"/>
-      <c r="T11" s="143"/>
-      <c r="U11" s="143"/>
-      <c r="V11" s="129"/>
-      <c r="W11" s="129"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="78"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="150"/>
-      <c r="AC11" s="129"/>
-      <c r="AD11" s="129"/>
-      <c r="AE11" s="82"/>
+      <c r="AA11" s="79"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="51"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
-      <c r="AH11" s="92"/>
+      <c r="AH11" s="59"/>
       <c r="AI11" s="18"/>
       <c r="AJ11" s="18"/>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="56"/>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="55"/>
-      <c r="AO11" s="55"/>
-      <c r="AP11" s="47"/>
-      <c r="AQ11" s="20"/>
-      <c r="AR11" s="47"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="118"/>
+      <c r="AM11" s="118"/>
+      <c r="AN11" s="167"/>
+      <c r="AO11" s="167"/>
+      <c r="AP11" s="119"/>
+      <c r="AQ11" s="119"/>
+      <c r="AR11" s="119"/>
       <c r="AS11" s="11"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
@@ -5989,52 +5912,52 @@
       <c r="ACD11" s="11"/>
     </row>
     <row r="12" spans="1:766" ht="24" customHeight="1">
-      <c r="A12" s="65">
+      <c r="A12" s="45">
         <v>4</v>
       </c>
-      <c r="B12" s="101"/>
-      <c r="C12" s="57"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="13"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="129"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="16"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="130"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="144"/>
-      <c r="N12" s="143"/>
-      <c r="O12" s="129"/>
-      <c r="P12" s="129"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
-      <c r="T12" s="144"/>
-      <c r="U12" s="144"/>
-      <c r="V12" s="129"/>
-      <c r="W12" s="129"/>
+      <c r="T12" s="79"/>
+      <c r="U12" s="79"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="144"/>
-      <c r="AB12" s="141"/>
-      <c r="AC12" s="129"/>
-      <c r="AD12" s="129"/>
-      <c r="AE12" s="37"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="79"/>
+      <c r="AB12" s="77"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="32"/>
       <c r="AF12" s="16"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="94"/>
+      <c r="AG12" s="22"/>
+      <c r="AH12" s="61"/>
       <c r="AI12" s="18"/>
       <c r="AJ12" s="18"/>
-      <c r="AK12" s="58"/>
-      <c r="AL12" s="55"/>
-      <c r="AM12" s="58"/>
-      <c r="AN12" s="55"/>
-      <c r="AO12" s="55"/>
-      <c r="AP12" s="47"/>
-      <c r="AQ12" s="20"/>
-      <c r="AR12" s="47"/>
+      <c r="AK12" s="120"/>
+      <c r="AL12" s="167"/>
+      <c r="AM12" s="120"/>
+      <c r="AN12" s="167"/>
+      <c r="AO12" s="167"/>
+      <c r="AP12" s="119"/>
+      <c r="AQ12" s="119"/>
+      <c r="AR12" s="119"/>
       <c r="ACE12"/>
       <c r="ACF12"/>
       <c r="ACG12"/>
@@ -6044,53 +5967,53 @@
       <c r="ACK12"/>
       <c r="ACL12"/>
     </row>
-    <row r="13" spans="1:766" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="65">
+    <row r="13" spans="1:766" ht="24" customHeight="1">
+      <c r="A13" s="45">
         <v>5</v>
       </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="51"/>
+      <c r="B13" s="117"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="129"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="13"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="129"/>
-      <c r="P13" s="129"/>
-      <c r="Q13" s="130"/>
-      <c r="R13" s="130"/>
-      <c r="S13" s="130"/>
-      <c r="T13" s="144"/>
-      <c r="U13" s="145"/>
-      <c r="V13" s="129"/>
-      <c r="W13" s="129"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="79"/>
+      <c r="U13" s="170"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-      <c r="AA13" s="144"/>
-      <c r="AB13" s="141"/>
-      <c r="AC13" s="129"/>
-      <c r="AD13" s="129"/>
-      <c r="AE13" s="37"/>
+      <c r="AA13" s="79"/>
+      <c r="AB13" s="77"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="32"/>
       <c r="AF13" s="16"/>
       <c r="AG13" s="16"/>
-      <c r="AH13" s="94"/>
+      <c r="AH13" s="61"/>
       <c r="AI13" s="18"/>
       <c r="AJ13" s="18"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="56"/>
-      <c r="AM13" s="52"/>
-      <c r="AN13" s="55"/>
-      <c r="AO13" s="55"/>
-      <c r="AP13" s="47"/>
-      <c r="AQ13" s="60"/>
-      <c r="AR13" s="47"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="118"/>
+      <c r="AM13" s="118"/>
+      <c r="AN13" s="167"/>
+      <c r="AO13" s="167"/>
+      <c r="AP13" s="119"/>
+      <c r="AQ13" s="119"/>
+      <c r="AR13" s="119"/>
       <c r="ACE13"/>
       <c r="ACF13"/>
       <c r="ACG13"/>
@@ -6100,53 +6023,53 @@
       <c r="ACK13"/>
       <c r="ACL13"/>
     </row>
-    <row r="14" spans="1:766" ht="24" customHeight="1" thickTop="1">
-      <c r="A14" s="65">
+    <row r="14" spans="1:766" ht="24" customHeight="1">
+      <c r="A14" s="45">
         <v>6</v>
       </c>
-      <c r="B14" s="101"/>
-      <c r="C14" s="100"/>
+      <c r="B14" s="117"/>
+      <c r="C14" s="66"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="129"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="166"/>
+      <c r="I14" s="16"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="129"/>
-      <c r="W14" s="129"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="85"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="142"/>
-      <c r="AC14" s="138"/>
-      <c r="AD14" s="129"/>
-      <c r="AE14" s="37"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="121"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="32"/>
       <c r="AF14" s="16"/>
       <c r="AG14" s="16"/>
-      <c r="AH14" s="94"/>
+      <c r="AH14" s="61"/>
       <c r="AI14" s="18"/>
       <c r="AJ14" s="18"/>
       <c r="AK14" s="18"/>
-      <c r="AL14" s="56"/>
-      <c r="AM14" s="58"/>
-      <c r="AN14" s="55"/>
-      <c r="AO14" s="55"/>
-      <c r="AP14" s="47"/>
-      <c r="AQ14" s="20"/>
-      <c r="AR14" s="47"/>
+      <c r="AL14" s="118"/>
+      <c r="AM14" s="120"/>
+      <c r="AN14" s="167"/>
+      <c r="AO14" s="167"/>
+      <c r="AP14" s="119"/>
+      <c r="AQ14" s="119"/>
+      <c r="AR14" s="119"/>
       <c r="ACE14"/>
       <c r="ACF14"/>
       <c r="ACG14"/>
@@ -6157,52 +6080,52 @@
       <c r="ACL14"/>
     </row>
     <row r="15" spans="1:766" ht="24" customHeight="1">
-      <c r="A15" s="65">
+      <c r="A15" s="45">
         <v>7</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="156"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="132"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="122"/>
       <c r="K15" s="16"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="25"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="171"/>
+      <c r="P15" s="171"/>
+      <c r="Q15" s="22"/>
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
-      <c r="T15" s="144"/>
-      <c r="U15" s="146"/>
-      <c r="V15" s="129"/>
-      <c r="W15" s="129"/>
+      <c r="T15" s="79"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
-      <c r="AA15" s="144"/>
-      <c r="AB15" s="141"/>
-      <c r="AC15" s="129"/>
-      <c r="AD15" s="129"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="25"/>
+      <c r="AA15" s="79"/>
+      <c r="AB15" s="77"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="33"/>
+      <c r="AF15" s="22"/>
       <c r="AG15" s="16"/>
-      <c r="AH15" s="95"/>
+      <c r="AH15" s="62"/>
       <c r="AI15" s="18"/>
       <c r="AJ15" s="18"/>
-      <c r="AK15" s="59"/>
-      <c r="AL15" s="56"/>
-      <c r="AM15" s="52"/>
-      <c r="AN15" s="55"/>
-      <c r="AO15" s="55"/>
-      <c r="AP15" s="47"/>
-      <c r="AQ15" s="60"/>
-      <c r="AR15" s="47"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="118"/>
+      <c r="AM15" s="118"/>
+      <c r="AN15" s="167"/>
+      <c r="AO15" s="167"/>
+      <c r="AP15" s="119"/>
+      <c r="AQ15" s="119"/>
+      <c r="AR15" s="119"/>
       <c r="ACE15"/>
       <c r="ACF15"/>
       <c r="ACG15"/>
@@ -6213,52 +6136,52 @@
       <c r="ACL15"/>
     </row>
     <row r="16" spans="1:766" ht="24" customHeight="1">
-      <c r="A16" s="65">
+      <c r="A16" s="45">
         <v>8</v>
       </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="129"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="166"/>
+      <c r="I16" s="16"/>
       <c r="J16" s="13"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
-      <c r="T16" s="143"/>
-      <c r="U16" s="146"/>
-      <c r="V16" s="129"/>
-      <c r="W16" s="129"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="143"/>
-      <c r="AB16" s="141"/>
-      <c r="AC16" s="129"/>
-      <c r="AD16" s="129"/>
-      <c r="AE16" s="83"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="95"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="78"/>
+      <c r="AB16" s="77"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="33"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="62"/>
       <c r="AI16" s="18"/>
       <c r="AJ16" s="18"/>
-      <c r="AK16" s="28"/>
-      <c r="AL16" s="56"/>
-      <c r="AM16" s="52"/>
-      <c r="AN16" s="55"/>
-      <c r="AO16" s="55"/>
-      <c r="AP16" s="47"/>
-      <c r="AQ16" s="20"/>
-      <c r="AR16" s="47"/>
+      <c r="AK16" s="123"/>
+      <c r="AL16" s="118"/>
+      <c r="AM16" s="118"/>
+      <c r="AN16" s="167"/>
+      <c r="AO16" s="167"/>
+      <c r="AP16" s="119"/>
+      <c r="AQ16" s="119"/>
+      <c r="AR16" s="119"/>
       <c r="ACE16"/>
       <c r="ACF16"/>
       <c r="ACG16"/>
@@ -6269,52 +6192,52 @@
       <c r="ACL16"/>
     </row>
     <row r="17" spans="1:766" ht="24" customHeight="1">
-      <c r="A17" s="65">
+      <c r="A17" s="45">
         <v>1</v>
       </c>
-      <c r="B17" s="101"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="117"/>
+      <c r="C17" s="124"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="143"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="129"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="16"/>
       <c r="J17" s="13"/>
       <c r="K17" s="16"/>
-      <c r="L17" s="143"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="25"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="22"/>
       <c r="R17" s="16"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="144"/>
-      <c r="U17" s="144"/>
-      <c r="V17" s="129"/>
-      <c r="W17" s="129"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="130"/>
-      <c r="Z17" s="133"/>
-      <c r="AA17" s="144"/>
-      <c r="AB17" s="141"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="129"/>
-      <c r="AE17" s="38"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="79"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="79"/>
+      <c r="AB17" s="77"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="33"/>
       <c r="AF17" s="16"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="95"/>
+      <c r="AG17" s="22"/>
+      <c r="AH17" s="62"/>
       <c r="AI17" s="18"/>
       <c r="AJ17" s="18"/>
-      <c r="AK17" s="41"/>
-      <c r="AL17" s="56"/>
-      <c r="AM17" s="52"/>
-      <c r="AN17" s="55"/>
-      <c r="AO17" s="55"/>
-      <c r="AP17" s="47"/>
-      <c r="AQ17" s="20"/>
-      <c r="AR17" s="47"/>
+      <c r="AK17" s="35"/>
+      <c r="AL17" s="118"/>
+      <c r="AM17" s="118"/>
+      <c r="AN17" s="167"/>
+      <c r="AO17" s="167"/>
+      <c r="AP17" s="119"/>
+      <c r="AQ17" s="119"/>
+      <c r="AR17" s="119"/>
       <c r="ACE17"/>
       <c r="ACF17"/>
       <c r="ACG17"/>
@@ -6325,52 +6248,52 @@
       <c r="ACL17"/>
     </row>
     <row r="18" spans="1:766" ht="24" customHeight="1">
-      <c r="A18" s="65">
+      <c r="A18" s="45">
         <v>1</v>
       </c>
-      <c r="B18" s="169"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="158"/>
-      <c r="G18" s="158"/>
-      <c r="H18" s="192"/>
-      <c r="I18" s="193"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="172"/>
+      <c r="I18" s="20"/>
       <c r="J18" s="15"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="158"/>
-      <c r="M18" s="158"/>
-      <c r="N18" s="158"/>
-      <c r="O18" s="193"/>
-      <c r="P18" s="193"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
-      <c r="S18" s="194"/>
-      <c r="T18" s="195"/>
-      <c r="U18" s="195"/>
-      <c r="V18" s="196"/>
-      <c r="W18" s="193"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="158"/>
-      <c r="AB18" s="197"/>
-      <c r="AC18" s="193"/>
-      <c r="AD18" s="193"/>
-      <c r="AE18" s="99"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="96"/>
-      <c r="AI18" s="27"/>
-      <c r="AJ18" s="27"/>
-      <c r="AK18" s="27"/>
-      <c r="AL18" s="71"/>
-      <c r="AM18" s="72"/>
-      <c r="AN18" s="198"/>
-      <c r="AO18" s="198"/>
-      <c r="AP18" s="62"/>
-      <c r="AQ18" s="74"/>
-      <c r="AR18" s="62"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="104"/>
+      <c r="U18" s="104"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="105"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="65"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="63"/>
+      <c r="AI18" s="23"/>
+      <c r="AJ18" s="23"/>
+      <c r="AK18" s="23"/>
+      <c r="AL18" s="127"/>
+      <c r="AM18" s="127"/>
+      <c r="AN18" s="128"/>
+      <c r="AO18" s="128"/>
+      <c r="AP18" s="129"/>
+      <c r="AQ18" s="129"/>
+      <c r="AR18" s="129"/>
       <c r="ACE18"/>
       <c r="ACF18"/>
       <c r="ACG18"/>
@@ -6381,52 +6304,52 @@
       <c r="ACL18"/>
     </row>
     <row r="19" spans="1:766" ht="24" customHeight="1">
-      <c r="A19" s="65">
+      <c r="A19" s="45">
         <v>2</v>
       </c>
-      <c r="B19" s="171"/>
-      <c r="C19" s="172"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="175"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="173"/>
-      <c r="L19" s="174"/>
-      <c r="M19" s="178"/>
-      <c r="N19" s="174"/>
-      <c r="O19" s="179"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="176"/>
-      <c r="R19" s="177"/>
-      <c r="S19" s="173"/>
-      <c r="T19" s="174"/>
-      <c r="U19" s="174"/>
-      <c r="V19" s="179"/>
-      <c r="W19" s="179"/>
-      <c r="X19" s="173"/>
-      <c r="Y19" s="173"/>
-      <c r="Z19" s="180"/>
-      <c r="AA19" s="181"/>
-      <c r="AB19" s="182"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="179"/>
-      <c r="AE19" s="184"/>
-      <c r="AF19" s="173"/>
-      <c r="AG19" s="173"/>
-      <c r="AH19" s="185"/>
-      <c r="AI19" s="186"/>
-      <c r="AJ19" s="186"/>
-      <c r="AK19" s="186"/>
-      <c r="AL19" s="187"/>
-      <c r="AM19" s="188"/>
-      <c r="AN19" s="189"/>
-      <c r="AO19" s="189"/>
-      <c r="AP19" s="190"/>
-      <c r="AQ19" s="191"/>
-      <c r="AR19" s="190"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="93"/>
+      <c r="P19" s="93"/>
+      <c r="Q19" s="173"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="93"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="93"/>
+      <c r="W19" s="93"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="93"/>
+      <c r="Z19" s="97"/>
+      <c r="AA19" s="98"/>
+      <c r="AB19" s="99"/>
+      <c r="AC19" s="97"/>
+      <c r="AD19" s="93"/>
+      <c r="AE19" s="100"/>
+      <c r="AF19" s="93"/>
+      <c r="AG19" s="93"/>
+      <c r="AH19" s="101"/>
+      <c r="AI19" s="102"/>
+      <c r="AJ19" s="102"/>
+      <c r="AK19" s="102"/>
+      <c r="AL19" s="132"/>
+      <c r="AM19" s="132"/>
+      <c r="AN19" s="174"/>
+      <c r="AO19" s="174"/>
+      <c r="AP19" s="133"/>
+      <c r="AQ19" s="133"/>
+      <c r="AR19" s="133"/>
       <c r="ACE19"/>
       <c r="ACF19"/>
       <c r="ACG19"/>
@@ -6437,52 +6360,52 @@
       <c r="ACL19"/>
     </row>
     <row r="20" spans="1:766" ht="24" customHeight="1">
-      <c r="A20" s="65">
+      <c r="A20" s="45">
         <v>1</v>
       </c>
-      <c r="B20" s="170"/>
-      <c r="C20" s="199"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="201"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="203"/>
-      <c r="J20" s="24"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="175"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="21"/>
       <c r="K20" s="14"/>
-      <c r="L20" s="162"/>
-      <c r="M20" s="162"/>
-      <c r="N20" s="204"/>
-      <c r="O20" s="203"/>
-      <c r="P20" s="203"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="108"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
       <c r="R20" s="17"/>
       <c r="S20" s="12"/>
-      <c r="T20" s="205"/>
-      <c r="U20" s="151"/>
-      <c r="V20" s="203"/>
-      <c r="W20" s="203"/>
+      <c r="T20" s="109"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
       <c r="X20" s="12"/>
       <c r="Y20" s="17"/>
       <c r="Z20" s="12"/>
-      <c r="AA20" s="151"/>
-      <c r="AB20" s="152"/>
-      <c r="AC20" s="203"/>
-      <c r="AD20" s="203"/>
-      <c r="AE20" s="36"/>
-      <c r="AF20" s="140"/>
-      <c r="AG20" s="140"/>
-      <c r="AH20" s="206"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="86"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="76"/>
+      <c r="AG20" s="76"/>
+      <c r="AH20" s="110"/>
       <c r="AI20" s="19"/>
       <c r="AJ20" s="19"/>
-      <c r="AK20" s="207"/>
-      <c r="AL20" s="208"/>
-      <c r="AM20" s="209"/>
-      <c r="AN20" s="78"/>
-      <c r="AO20" s="78"/>
-      <c r="AP20" s="79"/>
-      <c r="AQ20" s="210"/>
-      <c r="AR20" s="211"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="136"/>
+      <c r="AM20" s="137"/>
+      <c r="AN20" s="176"/>
+      <c r="AO20" s="176"/>
+      <c r="AP20" s="138"/>
+      <c r="AQ20" s="138"/>
+      <c r="AR20" s="139"/>
       <c r="ACF20"/>
       <c r="ACG20"/>
       <c r="ACH20"/>
@@ -6492,52 +6415,52 @@
       <c r="ACL20"/>
     </row>
     <row r="21" spans="1:766" ht="24" customHeight="1">
-      <c r="A21" s="65">
+      <c r="A21" s="45">
         <v>2</v>
       </c>
-      <c r="B21" s="169"/>
-      <c r="C21" s="51"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="156"/>
-      <c r="I21" s="129"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="16"/>
       <c r="J21" s="16"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="129"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="13"/>
       <c r="S21" s="16"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="144"/>
-      <c r="V21" s="129"/>
-      <c r="W21" s="129"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
       <c r="X21" s="16"/>
       <c r="Y21" s="12"/>
       <c r="Z21" s="16"/>
-      <c r="AA21" s="151"/>
-      <c r="AB21" s="152"/>
-      <c r="AC21" s="129"/>
-      <c r="AD21" s="129"/>
-      <c r="AE21" s="36"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="86"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="31"/>
       <c r="AF21" s="12"/>
-      <c r="AG21" s="98"/>
-      <c r="AH21" s="97"/>
+      <c r="AG21" s="177"/>
+      <c r="AH21" s="64"/>
       <c r="AI21" s="18"/>
       <c r="AJ21" s="18"/>
-      <c r="AK21" s="214"/>
-      <c r="AL21" s="56"/>
-      <c r="AM21" s="72"/>
-      <c r="AN21" s="73"/>
-      <c r="AO21" s="73"/>
-      <c r="AP21" s="62"/>
-      <c r="AQ21" s="20"/>
-      <c r="AR21" s="62"/>
+      <c r="AK21" s="23"/>
+      <c r="AL21" s="118"/>
+      <c r="AM21" s="127"/>
+      <c r="AN21" s="178"/>
+      <c r="AO21" s="178"/>
+      <c r="AP21" s="129"/>
+      <c r="AQ21" s="119"/>
+      <c r="AR21" s="129"/>
       <c r="ACF21"/>
       <c r="ACG21"/>
       <c r="ACH21"/>
@@ -6547,52 +6470,52 @@
       <c r="ACL21"/>
     </row>
     <row r="22" spans="1:766" ht="24" customHeight="1">
-      <c r="A22" s="65">
+      <c r="A22" s="45">
         <v>3</v>
       </c>
-      <c r="B22" s="167"/>
-      <c r="C22" s="168"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="163"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="156"/>
-      <c r="I22" s="129"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="16"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="144"/>
-      <c r="M22" s="158"/>
-      <c r="N22" s="158"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="129"/>
-      <c r="Q22" s="21"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="20"/>
       <c r="R22" s="15"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="148"/>
-      <c r="U22" s="148"/>
-      <c r="V22" s="135"/>
-      <c r="W22" s="135"/>
-      <c r="X22" s="136"/>
-      <c r="Y22" s="137"/>
-      <c r="Z22" s="136"/>
-      <c r="AA22" s="153"/>
-      <c r="AB22" s="154"/>
-      <c r="AC22" s="135"/>
-      <c r="AD22" s="134"/>
-      <c r="AE22" s="139"/>
-      <c r="AF22" s="140"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="87"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="73"/>
+      <c r="AD22" s="71"/>
+      <c r="AE22" s="75"/>
+      <c r="AF22" s="76"/>
       <c r="AG22" s="13"/>
-      <c r="AH22" s="93"/>
+      <c r="AH22" s="60"/>
       <c r="AI22" s="19"/>
-      <c r="AJ22" s="213"/>
-      <c r="AK22" s="212"/>
-      <c r="AL22" s="22"/>
-      <c r="AM22" s="164"/>
-      <c r="AN22" s="165"/>
-      <c r="AO22" s="165"/>
-      <c r="AP22" s="166"/>
-      <c r="AQ22" s="39"/>
-      <c r="AR22" s="47"/>
+      <c r="AJ22" s="112"/>
+      <c r="AK22" s="111"/>
+      <c r="AL22" s="142"/>
+      <c r="AM22" s="143"/>
+      <c r="AN22" s="179"/>
+      <c r="AO22" s="179"/>
+      <c r="AP22" s="180"/>
+      <c r="AQ22" s="181"/>
+      <c r="AR22" s="119"/>
       <c r="ACF22"/>
       <c r="ACG22"/>
       <c r="ACH22"/>
@@ -6602,52 +6525,52 @@
       <c r="ACL22"/>
     </row>
     <row r="23" spans="1:766" ht="24" customHeight="1">
-      <c r="A23" s="65">
+      <c r="A23" s="45">
         <v>4</v>
       </c>
-      <c r="B23" s="170"/>
-      <c r="C23" s="51"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="66"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="130"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="166"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="71"/>
       <c r="K23" s="13"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="143"/>
-      <c r="N23" s="144"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="13"/>
       <c r="S23" s="16"/>
-      <c r="T23" s="147"/>
-      <c r="U23" s="147"/>
-      <c r="V23" s="129"/>
-      <c r="W23" s="129"/>
+      <c r="T23" s="81"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
       <c r="X23" s="16"/>
       <c r="Y23" s="13"/>
       <c r="Z23" s="16"/>
-      <c r="AA23" s="144"/>
-      <c r="AB23" s="141"/>
-      <c r="AC23" s="129"/>
-      <c r="AD23" s="129"/>
-      <c r="AE23" s="37"/>
+      <c r="AA23" s="79"/>
+      <c r="AB23" s="77"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="32"/>
       <c r="AF23" s="16"/>
       <c r="AG23" s="16"/>
-      <c r="AH23" s="92"/>
+      <c r="AH23" s="59"/>
       <c r="AI23" s="19"/>
       <c r="AJ23" s="19"/>
-      <c r="AK23" s="75"/>
-      <c r="AL23" s="76"/>
-      <c r="AM23" s="77"/>
-      <c r="AN23" s="78"/>
-      <c r="AO23" s="78"/>
-      <c r="AP23" s="79"/>
-      <c r="AQ23" s="80"/>
-      <c r="AR23" s="47"/>
+      <c r="AK23" s="49"/>
+      <c r="AL23" s="144"/>
+      <c r="AM23" s="144"/>
+      <c r="AN23" s="176"/>
+      <c r="AO23" s="176"/>
+      <c r="AP23" s="138"/>
+      <c r="AQ23" s="138"/>
+      <c r="AR23" s="119"/>
       <c r="ACF23"/>
       <c r="ACG23"/>
       <c r="ACH23"/>
@@ -6657,52 +6580,52 @@
       <c r="ACL23"/>
     </row>
     <row r="24" spans="1:766" ht="24" customHeight="1">
-      <c r="A24" s="65">
+      <c r="A24" s="45">
         <v>5</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="51"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="66"/>
       <c r="D24" s="16"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="143"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="156"/>
-      <c r="I24" s="129"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="16"/>
       <c r="J24" s="16"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="143"/>
-      <c r="M24" s="143"/>
-      <c r="N24" s="144"/>
-      <c r="O24" s="129"/>
-      <c r="P24" s="129"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
-      <c r="T24" s="143"/>
-      <c r="U24" s="144"/>
-      <c r="V24" s="129"/>
-      <c r="W24" s="129"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="79"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="12"/>
       <c r="Z24" s="13"/>
-      <c r="AA24" s="151"/>
-      <c r="AB24" s="152"/>
-      <c r="AC24" s="129"/>
-      <c r="AD24" s="129"/>
-      <c r="AE24" s="37"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="86"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="32"/>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
-      <c r="AH24" s="94"/>
+      <c r="AH24" s="61"/>
       <c r="AI24" s="18"/>
       <c r="AJ24" s="18"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="56"/>
-      <c r="AM24" s="52"/>
-      <c r="AN24" s="55"/>
-      <c r="AO24" s="55"/>
-      <c r="AP24" s="47"/>
-      <c r="AQ24" s="20"/>
-      <c r="AR24" s="47"/>
+      <c r="AK24" s="35"/>
+      <c r="AL24" s="118"/>
+      <c r="AM24" s="118"/>
+      <c r="AN24" s="167"/>
+      <c r="AO24" s="167"/>
+      <c r="AP24" s="119"/>
+      <c r="AQ24" s="119"/>
+      <c r="AR24" s="119"/>
       <c r="ACF24"/>
       <c r="ACG24"/>
       <c r="ACH24"/>
@@ -6712,52 +6635,52 @@
       <c r="ACL24"/>
     </row>
     <row r="25" spans="1:766" ht="24" customHeight="1">
-      <c r="A25" s="65">
+      <c r="A25" s="45">
         <v>1</v>
       </c>
-      <c r="B25" s="66"/>
-      <c r="C25" s="42"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="126"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="156"/>
-      <c r="G25" s="156"/>
-      <c r="H25" s="156"/>
-      <c r="I25" s="129"/>
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="16"/>
       <c r="J25" s="15"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="149"/>
-      <c r="M25" s="159"/>
-      <c r="N25" s="149"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="83"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
       <c r="Q25" s="15"/>
-      <c r="R25" s="21"/>
+      <c r="R25" s="20"/>
       <c r="S25" s="15"/>
-      <c r="T25" s="149"/>
-      <c r="U25" s="149"/>
-      <c r="V25" s="129"/>
-      <c r="W25" s="129"/>
+      <c r="T25" s="83"/>
+      <c r="U25" s="83"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
       <c r="X25" s="15"/>
-      <c r="Y25" s="21"/>
+      <c r="Y25" s="20"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="149"/>
-      <c r="AB25" s="155"/>
-      <c r="AC25" s="129"/>
-      <c r="AD25" s="129"/>
-      <c r="AE25" s="99"/>
-      <c r="AF25" s="21"/>
+      <c r="AA25" s="83"/>
+      <c r="AB25" s="89"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="65"/>
+      <c r="AF25" s="20"/>
       <c r="AG25" s="15"/>
-      <c r="AH25" s="92"/>
+      <c r="AH25" s="59"/>
       <c r="AI25" s="18"/>
       <c r="AJ25" s="18"/>
-      <c r="AK25" s="41"/>
-      <c r="AL25" s="54"/>
-      <c r="AM25" s="52"/>
-      <c r="AN25" s="44"/>
-      <c r="AO25" s="44"/>
-      <c r="AP25" s="68"/>
-      <c r="AQ25" s="20"/>
-      <c r="AR25" s="47"/>
+      <c r="AK25" s="35"/>
+      <c r="AL25" s="41"/>
+      <c r="AM25" s="118"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="145"/>
+      <c r="AQ25" s="119"/>
+      <c r="AR25" s="119"/>
       <c r="ACF25"/>
       <c r="ACG25"/>
       <c r="ACH25"/>
@@ -6767,728 +6690,728 @@
       <c r="ACL25"/>
     </row>
     <row r="26" spans="1:766" ht="24" customHeight="1">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="67"/>
-      <c r="X26" s="67"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-      <c r="AA26" s="67"/>
-      <c r="AB26" s="67"/>
-      <c r="AC26" s="81"/>
-      <c r="AD26" s="81"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="67"/>
-      <c r="AH26" s="106"/>
-      <c r="AI26" s="106"/>
-      <c r="AJ26" s="106"/>
-      <c r="AK26" s="106"/>
-      <c r="AL26" s="106"/>
-      <c r="AM26" s="106"/>
-      <c r="AN26" s="106"/>
-      <c r="AO26" s="106"/>
-      <c r="AP26" s="106"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
+      <c r="AB26" s="46"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="50"/>
+      <c r="AE26" s="46"/>
+      <c r="AF26" s="46"/>
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="68"/>
+      <c r="AI26" s="68"/>
+      <c r="AJ26" s="68"/>
+      <c r="AK26" s="68"/>
+      <c r="AL26" s="68"/>
+      <c r="AM26" s="68"/>
+      <c r="AN26" s="68"/>
+      <c r="AO26" s="68"/>
+      <c r="AP26" s="68"/>
     </row>
     <row r="27" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B27" s="63"/>
-      <c r="C27" s="63" t="s">
+      <c r="B27" s="43"/>
+      <c r="C27" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="43">
         <f>COUNTIF(D9:D19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="63">
+      <c r="E27" s="43">
         <f>COUNTIF(E9:E19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="63">
+      <c r="F27" s="43">
         <f>COUNTIF(F9:F19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="G27" s="63">
+      <c r="G27" s="43">
         <f t="shared" ref="F27:AH27" si="0">COUNTIF(G9:G19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="63">
+      <c r="H27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="63">
+      <c r="I27" s="43">
         <f>COUNTIF(I9:I19,"*D*")</f>
         <v>0</v>
       </c>
-      <c r="J27" s="63">
+      <c r="J27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K27" s="63">
+      <c r="K27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="63">
+      <c r="L27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M27" s="63">
+      <c r="M27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="63">
+      <c r="N27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O27" s="63">
+      <c r="O27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="63">
+      <c r="P27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="63">
+      <c r="Q27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R27" s="63">
+      <c r="R27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S27" s="63">
+      <c r="S27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T27" s="63">
+      <c r="T27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U27" s="63">
+      <c r="U27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V27" s="63">
+      <c r="V27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W27" s="63">
+      <c r="W27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X27" s="63">
+      <c r="X27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="63">
+      <c r="Y27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="63">
+      <c r="Z27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA27" s="63">
+      <c r="AA27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="63">
+      <c r="AB27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="63">
+      <c r="AC27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD27" s="63">
+      <c r="AD27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AE27" s="63">
+      <c r="AE27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF27" s="63">
+      <c r="AF27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="63">
+      <c r="AG27" s="43">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="32">
+      <c r="AH27" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="106"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="27"/>
+      <c r="AK27" s="27"/>
+      <c r="AL27" s="27"/>
+      <c r="AM27" s="27"/>
+      <c r="AN27" s="27"/>
+      <c r="AO27" s="27"/>
+      <c r="AP27" s="68"/>
     </row>
     <row r="28" spans="1:766" ht="12.75" customHeight="1">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32" t="s">
+      <c r="B28" s="27"/>
+      <c r="C28" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="27">
         <f t="shared" ref="D28:AH28" si="1">COUNTIF(D9:D19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="27">
         <f>COUNTIF(I9:I19,"*E*")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X28" s="32">
+      <c r="X28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="32">
+      <c r="Y28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA28" s="32">
+      <c r="AA28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="32">
+      <c r="AB28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="32">
+      <c r="AC28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD28" s="32">
+      <c r="AD28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE28" s="32">
+      <c r="AE28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF28" s="32">
+      <c r="AF28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="32">
+      <c r="AG28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="32">
+      <c r="AH28" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="32"/>
-      <c r="AP28" s="106"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="27"/>
+      <c r="AL28" s="27"/>
+      <c r="AM28" s="27"/>
+      <c r="AN28" s="27"/>
+      <c r="AO28" s="27"/>
+      <c r="AP28" s="68"/>
     </row>
     <row r="29" spans="1:766" ht="14.25" customHeight="1">
-      <c r="B29" s="32"/>
-      <c r="C29" s="32" t="s">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="27">
         <f t="shared" ref="D29:AH29" si="2">COUNTIF(D9:D19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="27">
         <f>COUNTIF(I9:I19,"*N*")</f>
         <v>0</v>
       </c>
-      <c r="J29" s="32">
+      <c r="J29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="27">
         <v>2</v>
       </c>
-      <c r="R29" s="32">
+      <c r="R29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S29" s="32">
+      <c r="S29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T29" s="32">
+      <c r="T29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U29" s="32">
+      <c r="U29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V29" s="32">
+      <c r="V29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W29" s="32">
+      <c r="W29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X29" s="32">
+      <c r="X29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="32">
+      <c r="Y29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="32">
+      <c r="Z29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA29" s="32">
+      <c r="AA29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="32">
+      <c r="AB29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="32">
+      <c r="AC29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD29" s="32">
+      <c r="AD29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE29" s="32">
+      <c r="AE29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="32">
+      <c r="AF29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="32">
+      <c r="AG29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="32">
+      <c r="AH29" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="32"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="32"/>
-      <c r="AP29" s="106"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="27"/>
+      <c r="AK29" s="27"/>
+      <c r="AL29" s="27"/>
+      <c r="AM29" s="27"/>
+      <c r="AN29" s="27"/>
+      <c r="AO29" s="27"/>
+      <c r="AP29" s="68"/>
     </row>
     <row r="30" spans="1:766" ht="12" customHeight="1">
-      <c r="A30" s="33"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32" t="s">
+      <c r="A30" s="28"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="27">
         <f t="shared" ref="D30:AH30" si="3">COUNTIF(D9:D25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="27">
         <f>COUNTIF(N9:N25,"*M*")</f>
         <v>0</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="32">
+      <c r="R30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T30" s="32">
+      <c r="T30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X30" s="32">
+      <c r="X30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y30" s="32">
+      <c r="Y30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z30" s="32">
+      <c r="Z30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA30" s="32">
+      <c r="AA30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD30" s="32">
+      <c r="AD30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE30" s="32">
+      <c r="AE30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="32">
+      <c r="AF30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="32">
+      <c r="AG30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="32">
+      <c r="AH30" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI30" s="32"/>
-      <c r="AJ30" s="32"/>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="32"/>
-      <c r="AP30" s="106"/>
+      <c r="AI30" s="27"/>
+      <c r="AJ30" s="27"/>
+      <c r="AK30" s="27"/>
+      <c r="AL30" s="27"/>
+      <c r="AM30" s="27"/>
+      <c r="AN30" s="27"/>
+      <c r="AO30" s="27"/>
+      <c r="AP30" s="68"/>
     </row>
     <row r="31" spans="1:766">
-      <c r="A31" s="33"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="35"/>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
-      <c r="AF31" s="35"/>
-      <c r="AG31" s="35"/>
-      <c r="AH31" s="35"/>
-      <c r="AI31" s="35"/>
-      <c r="AJ31" s="35"/>
-      <c r="AK31" s="35"/>
-      <c r="AL31" s="107"/>
-      <c r="AO31" s="105"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
+      <c r="AA31" s="30"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="30"/>
+      <c r="AD31" s="30"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="30"/>
+      <c r="AG31" s="30"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="30"/>
+      <c r="AJ31" s="30"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="69"/>
+      <c r="AO31" s="67"/>
     </row>
     <row r="32" spans="1:766">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33"/>
-      <c r="U32" s="33"/>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="33"/>
-      <c r="Y32" s="33"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33"/>
-      <c r="AC32" s="33"/>
-      <c r="AD32" s="33"/>
-      <c r="AE32" s="33"/>
-      <c r="AF32" s="33"/>
-      <c r="AG32" s="33"/>
-      <c r="AH32" s="33"/>
-      <c r="AI32" s="33"/>
-      <c r="AJ32" s="33"/>
-      <c r="AK32" s="33"/>
-      <c r="AL32" s="107"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
+      <c r="AD32" s="28"/>
+      <c r="AE32" s="28"/>
+      <c r="AF32" s="28"/>
+      <c r="AG32" s="28"/>
+      <c r="AH32" s="28"/>
+      <c r="AI32" s="28"/>
+      <c r="AJ32" s="28"/>
+      <c r="AK32" s="28"/>
+      <c r="AL32" s="69"/>
     </row>
     <row r="33" spans="1:767" s="2" customFormat="1">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="33"/>
-      <c r="AA33" s="33"/>
-      <c r="AB33" s="33"/>
-      <c r="AC33" s="33"/>
-      <c r="AD33" s="33"/>
-      <c r="AE33" s="33"/>
-      <c r="AF33" s="33"/>
-      <c r="AG33" s="33"/>
-      <c r="AH33" s="33"/>
-      <c r="AI33" s="33"/>
-      <c r="AJ33" s="33"/>
-      <c r="AK33" s="33"/>
-      <c r="AL33" s="107"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
+      <c r="AD33" s="28"/>
+      <c r="AE33" s="28"/>
+      <c r="AF33" s="28"/>
+      <c r="AG33" s="28"/>
+      <c r="AH33" s="28"/>
+      <c r="AI33" s="28"/>
+      <c r="AJ33" s="28"/>
+      <c r="AK33" s="28"/>
+      <c r="AL33" s="69"/>
       <c r="AM33" s="3"/>
       <c r="AN33" s="3"/>
       <c r="AO33" s="3"/>
       <c r="AP33" s="3"/>
       <c r="AQ33" s="3"/>
-      <c r="AR33" s="45"/>
+      <c r="AR33" s="38"/>
       <c r="AS33" s="3"/>
       <c r="AT33" s="3"/>
       <c r="AU33" s="3"/>
@@ -8214,50 +8137,50 @@
       <c r="ACM33"/>
     </row>
     <row r="34" spans="1:767" s="2" customFormat="1">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
-      <c r="AK34" s="33"/>
-      <c r="AL34" s="107"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+      <c r="AB34" s="28"/>
+      <c r="AC34" s="28"/>
+      <c r="AD34" s="28"/>
+      <c r="AE34" s="28"/>
+      <c r="AF34" s="28"/>
+      <c r="AG34" s="28"/>
+      <c r="AH34" s="28"/>
+      <c r="AI34" s="28"/>
+      <c r="AJ34" s="28"/>
+      <c r="AK34" s="28"/>
+      <c r="AL34" s="69"/>
       <c r="AM34" s="3"/>
       <c r="AN34" s="3"/>
       <c r="AO34" s="3"/>
       <c r="AP34" s="3"/>
       <c r="AQ34" s="3"/>
-      <c r="AR34" s="45"/>
+      <c r="AR34" s="38"/>
       <c r="AS34" s="3"/>
       <c r="AT34" s="3"/>
       <c r="AU34" s="3"/>
@@ -8983,50 +8906,50 @@
       <c r="ACM34"/>
     </row>
     <row r="35" spans="1:767" s="2" customFormat="1">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="33"/>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="33"/>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="33"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="33"/>
-      <c r="AC35" s="33"/>
-      <c r="AD35" s="33"/>
-      <c r="AE35" s="33"/>
-      <c r="AF35" s="33"/>
-      <c r="AG35" s="33"/>
-      <c r="AH35" s="33"/>
-      <c r="AI35" s="33"/>
-      <c r="AJ35" s="33"/>
-      <c r="AK35" s="33"/>
-      <c r="AL35" s="107"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
+      <c r="AD35" s="28"/>
+      <c r="AE35" s="28"/>
+      <c r="AF35" s="28"/>
+      <c r="AG35" s="28"/>
+      <c r="AH35" s="28"/>
+      <c r="AI35" s="28"/>
+      <c r="AJ35" s="28"/>
+      <c r="AK35" s="28"/>
+      <c r="AL35" s="69"/>
       <c r="AM35" s="3"/>
       <c r="AN35" s="3"/>
       <c r="AO35" s="3"/>
       <c r="AP35" s="3"/>
       <c r="AQ35" s="3"/>
-      <c r="AR35" s="45"/>
+      <c r="AR35" s="38"/>
       <c r="AS35" s="3"/>
       <c r="AT35" s="3"/>
       <c r="AU35" s="3"/>
@@ -9752,50 +9675,50 @@
       <c r="ACM35"/>
     </row>
     <row r="36" spans="1:767" s="2" customFormat="1">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33"/>
-      <c r="U36" s="33"/>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="33"/>
-      <c r="Y36" s="33"/>
-      <c r="Z36" s="33"/>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
-      <c r="AD36" s="33"/>
-      <c r="AE36" s="33"/>
-      <c r="AF36" s="33"/>
-      <c r="AG36" s="33"/>
-      <c r="AH36" s="33"/>
-      <c r="AI36" s="33"/>
-      <c r="AJ36" s="33"/>
-      <c r="AK36" s="33"/>
-      <c r="AL36" s="107"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
+      <c r="AD36" s="28"/>
+      <c r="AE36" s="28"/>
+      <c r="AF36" s="28"/>
+      <c r="AG36" s="28"/>
+      <c r="AH36" s="28"/>
+      <c r="AI36" s="28"/>
+      <c r="AJ36" s="28"/>
+      <c r="AK36" s="28"/>
+      <c r="AL36" s="69"/>
       <c r="AM36" s="3"/>
       <c r="AN36" s="3"/>
       <c r="AO36" s="3"/>
       <c r="AP36" s="3"/>
       <c r="AQ36" s="3"/>
-      <c r="AR36" s="45"/>
+      <c r="AR36" s="38"/>
       <c r="AS36" s="3"/>
       <c r="AT36" s="3"/>
       <c r="AU36" s="3"/>
@@ -10521,50 +10444,50 @@
       <c r="ACM36"/>
     </row>
     <row r="37" spans="1:767" s="2" customFormat="1">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33"/>
-      <c r="T37" s="33"/>
-      <c r="U37" s="33"/>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="33"/>
-      <c r="Y37" s="33"/>
-      <c r="Z37" s="33"/>
-      <c r="AA37" s="33"/>
-      <c r="AB37" s="33"/>
-      <c r="AC37" s="33"/>
-      <c r="AD37" s="33"/>
-      <c r="AE37" s="33"/>
-      <c r="AF37" s="33"/>
-      <c r="AG37" s="33"/>
-      <c r="AH37" s="33"/>
-      <c r="AI37" s="33"/>
-      <c r="AJ37" s="33"/>
-      <c r="AK37" s="33"/>
-      <c r="AL37" s="107"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="AH37" s="28"/>
+      <c r="AI37" s="28"/>
+      <c r="AJ37" s="28"/>
+      <c r="AK37" s="28"/>
+      <c r="AL37" s="69"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
       <c r="AO37" s="3"/>
       <c r="AP37" s="3"/>
       <c r="AQ37" s="3"/>
-      <c r="AR37" s="45"/>
+      <c r="AR37" s="38"/>
       <c r="AS37" s="3"/>
       <c r="AT37" s="3"/>
       <c r="AU37" s="3"/>
@@ -11290,50 +11213,50 @@
       <c r="ACM37"/>
     </row>
     <row r="38" spans="1:767" s="2" customFormat="1">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="33"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="33"/>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="33"/>
-      <c r="Y38" s="33"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="33"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
-      <c r="AD38" s="33"/>
-      <c r="AE38" s="33"/>
-      <c r="AF38" s="33"/>
-      <c r="AG38" s="33"/>
-      <c r="AH38" s="33"/>
-      <c r="AI38" s="33"/>
-      <c r="AJ38" s="33"/>
-      <c r="AK38" s="33"/>
-      <c r="AL38" s="107"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
+      <c r="AD38" s="28"/>
+      <c r="AE38" s="28"/>
+      <c r="AF38" s="28"/>
+      <c r="AG38" s="28"/>
+      <c r="AH38" s="28"/>
+      <c r="AI38" s="28"/>
+      <c r="AJ38" s="28"/>
+      <c r="AK38" s="28"/>
+      <c r="AL38" s="69"/>
       <c r="AM38" s="3"/>
       <c r="AN38" s="3"/>
       <c r="AO38" s="3"/>
       <c r="AP38" s="3"/>
       <c r="AQ38" s="3"/>
-      <c r="AR38" s="45"/>
+      <c r="AR38" s="38"/>
       <c r="AS38" s="3"/>
       <c r="AT38" s="3"/>
       <c r="AU38" s="3"/>
@@ -12059,50 +11982,50 @@
       <c r="ACM38"/>
     </row>
     <row r="39" spans="1:767" s="2" customFormat="1">
-      <c r="A39" s="33"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-      <c r="Z39" s="33"/>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
-      <c r="AE39" s="33"/>
-      <c r="AF39" s="33"/>
-      <c r="AG39" s="33"/>
-      <c r="AH39" s="33"/>
-      <c r="AI39" s="33"/>
-      <c r="AJ39" s="33"/>
-      <c r="AK39" s="33"/>
-      <c r="AL39" s="107"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
+      <c r="AD39" s="28"/>
+      <c r="AE39" s="28"/>
+      <c r="AF39" s="28"/>
+      <c r="AG39" s="28"/>
+      <c r="AH39" s="28"/>
+      <c r="AI39" s="28"/>
+      <c r="AJ39" s="28"/>
+      <c r="AK39" s="28"/>
+      <c r="AL39" s="69"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
-      <c r="AR39" s="45"/>
+      <c r="AR39" s="38"/>
       <c r="AS39" s="3"/>
       <c r="AT39" s="3"/>
       <c r="AU39" s="3"/>
@@ -12828,50 +12751,50 @@
       <c r="ACM39"/>
     </row>
     <row r="40" spans="1:767" s="2" customFormat="1">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-      <c r="P40" s="33"/>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="33"/>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="33"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="33"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
-      <c r="AD40" s="33"/>
-      <c r="AE40" s="33"/>
-      <c r="AF40" s="33"/>
-      <c r="AG40" s="33"/>
-      <c r="AH40" s="33"/>
-      <c r="AI40" s="33"/>
-      <c r="AJ40" s="33"/>
-      <c r="AK40" s="33"/>
-      <c r="AL40" s="107"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
+      <c r="AD40" s="28"/>
+      <c r="AE40" s="28"/>
+      <c r="AF40" s="28"/>
+      <c r="AG40" s="28"/>
+      <c r="AH40" s="28"/>
+      <c r="AI40" s="28"/>
+      <c r="AJ40" s="28"/>
+      <c r="AK40" s="28"/>
+      <c r="AL40" s="69"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
-      <c r="AR40" s="45"/>
+      <c r="AR40" s="38"/>
       <c r="AS40" s="3"/>
       <c r="AT40" s="3"/>
       <c r="AU40" s="3"/>
@@ -13597,50 +13520,50 @@
       <c r="ACM40"/>
     </row>
     <row r="41" spans="1:767" s="2" customFormat="1">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="33"/>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-      <c r="Z41" s="33"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
-      <c r="AD41" s="33"/>
-      <c r="AE41" s="33"/>
-      <c r="AF41" s="33"/>
-      <c r="AG41" s="33"/>
-      <c r="AH41" s="33"/>
-      <c r="AI41" s="33"/>
-      <c r="AJ41" s="33"/>
-      <c r="AK41" s="33"/>
-      <c r="AL41" s="107"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="28"/>
+      <c r="AA41" s="28"/>
+      <c r="AB41" s="28"/>
+      <c r="AC41" s="28"/>
+      <c r="AD41" s="28"/>
+      <c r="AE41" s="28"/>
+      <c r="AF41" s="28"/>
+      <c r="AG41" s="28"/>
+      <c r="AH41" s="28"/>
+      <c r="AI41" s="28"/>
+      <c r="AJ41" s="28"/>
+      <c r="AK41" s="28"/>
+      <c r="AL41" s="69"/>
       <c r="AM41" s="3"/>
       <c r="AN41" s="3"/>
       <c r="AO41" s="3"/>
       <c r="AP41" s="3"/>
       <c r="AQ41" s="3"/>
-      <c r="AR41" s="45"/>
+      <c r="AR41" s="38"/>
       <c r="AS41" s="3"/>
       <c r="AT41" s="3"/>
       <c r="AU41" s="3"/>
@@ -14366,50 +14289,50 @@
       <c r="ACM41"/>
     </row>
     <row r="42" spans="1:767" s="2" customFormat="1">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
-      <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
-      <c r="AG42" s="33"/>
-      <c r="AH42" s="33"/>
-      <c r="AI42" s="33"/>
-      <c r="AJ42" s="33"/>
-      <c r="AK42" s="33"/>
-      <c r="AL42" s="107"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+      <c r="AE42" s="28"/>
+      <c r="AF42" s="28"/>
+      <c r="AG42" s="28"/>
+      <c r="AH42" s="28"/>
+      <c r="AI42" s="28"/>
+      <c r="AJ42" s="28"/>
+      <c r="AK42" s="28"/>
+      <c r="AL42" s="69"/>
       <c r="AM42" s="3"/>
       <c r="AN42" s="3"/>
       <c r="AO42" s="3"/>
       <c r="AP42" s="3"/>
       <c r="AQ42" s="3"/>
-      <c r="AR42" s="45"/>
+      <c r="AR42" s="38"/>
       <c r="AS42" s="3"/>
       <c r="AT42" s="3"/>
       <c r="AU42" s="3"/>
@@ -15135,50 +15058,50 @@
       <c r="ACM42"/>
     </row>
     <row r="43" spans="1:767" s="2" customFormat="1">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-      <c r="P43" s="33"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33"/>
-      <c r="S43" s="33"/>
-      <c r="T43" s="33"/>
-      <c r="U43" s="33"/>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="33"/>
-      <c r="Y43" s="33"/>
-      <c r="Z43" s="33"/>
-      <c r="AA43" s="33"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="33"/>
-      <c r="AD43" s="33"/>
-      <c r="AE43" s="33"/>
-      <c r="AF43" s="33"/>
-      <c r="AG43" s="33"/>
-      <c r="AH43" s="33"/>
-      <c r="AI43" s="33"/>
-      <c r="AJ43" s="33"/>
-      <c r="AK43" s="33"/>
-      <c r="AL43" s="107"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
+      <c r="AC43" s="28"/>
+      <c r="AD43" s="28"/>
+      <c r="AE43" s="28"/>
+      <c r="AF43" s="28"/>
+      <c r="AG43" s="28"/>
+      <c r="AH43" s="28"/>
+      <c r="AI43" s="28"/>
+      <c r="AJ43" s="28"/>
+      <c r="AK43" s="28"/>
+      <c r="AL43" s="69"/>
       <c r="AM43" s="3"/>
       <c r="AN43" s="3"/>
       <c r="AO43" s="3"/>
       <c r="AP43" s="3"/>
       <c r="AQ43" s="3"/>
-      <c r="AR43" s="45"/>
+      <c r="AR43" s="38"/>
       <c r="AS43" s="3"/>
       <c r="AT43" s="3"/>
       <c r="AU43" s="3"/>
@@ -15904,50 +15827,50 @@
       <c r="ACM43"/>
     </row>
     <row r="44" spans="1:767" s="2" customFormat="1">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="33"/>
-      <c r="Z44" s="33"/>
-      <c r="AA44" s="33"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
-      <c r="AD44" s="33"/>
-      <c r="AE44" s="33"/>
-      <c r="AF44" s="33"/>
-      <c r="AG44" s="33"/>
-      <c r="AH44" s="33"/>
-      <c r="AI44" s="33"/>
-      <c r="AJ44" s="33"/>
-      <c r="AK44" s="33"/>
-      <c r="AL44" s="107"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28"/>
+      <c r="V44" s="28"/>
+      <c r="W44" s="28"/>
+      <c r="X44" s="28"/>
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="28"/>
+      <c r="AA44" s="28"/>
+      <c r="AB44" s="28"/>
+      <c r="AC44" s="28"/>
+      <c r="AD44" s="28"/>
+      <c r="AE44" s="28"/>
+      <c r="AF44" s="28"/>
+      <c r="AG44" s="28"/>
+      <c r="AH44" s="28"/>
+      <c r="AI44" s="28"/>
+      <c r="AJ44" s="28"/>
+      <c r="AK44" s="28"/>
+      <c r="AL44" s="69"/>
       <c r="AM44" s="3"/>
       <c r="AN44" s="3"/>
       <c r="AO44" s="3"/>
       <c r="AP44" s="3"/>
       <c r="AQ44" s="3"/>
-      <c r="AR44" s="45"/>
+      <c r="AR44" s="38"/>
       <c r="AS44" s="3"/>
       <c r="AT44" s="3"/>
       <c r="AU44" s="3"/>
@@ -16673,50 +16596,50 @@
       <c r="ACM44"/>
     </row>
     <row r="45" spans="1:767" s="2" customFormat="1">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-      <c r="M45" s="33"/>
-      <c r="N45" s="33"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="33"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="33"/>
-      <c r="Z45" s="33"/>
-      <c r="AA45" s="33"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
-      <c r="AE45" s="33"/>
-      <c r="AF45" s="33"/>
-      <c r="AG45" s="33"/>
-      <c r="AH45" s="33"/>
-      <c r="AI45" s="33"/>
-      <c r="AJ45" s="33"/>
-      <c r="AK45" s="33"/>
-      <c r="AL45" s="107"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28"/>
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="28"/>
+      <c r="AA45" s="28"/>
+      <c r="AB45" s="28"/>
+      <c r="AC45" s="28"/>
+      <c r="AD45" s="28"/>
+      <c r="AE45" s="28"/>
+      <c r="AF45" s="28"/>
+      <c r="AG45" s="28"/>
+      <c r="AH45" s="28"/>
+      <c r="AI45" s="28"/>
+      <c r="AJ45" s="28"/>
+      <c r="AK45" s="28"/>
+      <c r="AL45" s="69"/>
       <c r="AM45" s="3"/>
       <c r="AN45" s="3"/>
       <c r="AO45" s="3"/>
       <c r="AP45" s="3"/>
       <c r="AQ45" s="3"/>
-      <c r="AR45" s="45"/>
+      <c r="AR45" s="38"/>
       <c r="AS45" s="3"/>
       <c r="AT45" s="3"/>
       <c r="AU45" s="3"/>
@@ -17442,50 +17365,50 @@
       <c r="ACM45"/>
     </row>
     <row r="46" spans="1:767" s="2" customFormat="1">
-      <c r="A46" s="33"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
-      <c r="V46" s="33"/>
-      <c r="W46" s="33"/>
-      <c r="X46" s="33"/>
-      <c r="Y46" s="33"/>
-      <c r="Z46" s="33"/>
-      <c r="AA46" s="33"/>
-      <c r="AB46" s="33"/>
-      <c r="AC46" s="33"/>
-      <c r="AD46" s="33"/>
-      <c r="AE46" s="33"/>
-      <c r="AF46" s="33"/>
-      <c r="AG46" s="33"/>
-      <c r="AH46" s="33"/>
-      <c r="AI46" s="33"/>
-      <c r="AJ46" s="33"/>
-      <c r="AK46" s="33"/>
-      <c r="AL46" s="107"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
+      <c r="AD46" s="28"/>
+      <c r="AE46" s="28"/>
+      <c r="AF46" s="28"/>
+      <c r="AG46" s="28"/>
+      <c r="AH46" s="28"/>
+      <c r="AI46" s="28"/>
+      <c r="AJ46" s="28"/>
+      <c r="AK46" s="28"/>
+      <c r="AL46" s="69"/>
       <c r="AM46" s="3"/>
       <c r="AN46" s="3"/>
       <c r="AO46" s="3"/>
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3"/>
-      <c r="AR46" s="45"/>
+      <c r="AR46" s="38"/>
       <c r="AS46" s="3"/>
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
@@ -18211,50 +18134,50 @@
       <c r="ACM46"/>
     </row>
     <row r="47" spans="1:767" s="2" customFormat="1">
-      <c r="A47" s="33"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="33"/>
-      <c r="Y47" s="33"/>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="33"/>
-      <c r="AB47" s="33"/>
-      <c r="AC47" s="33"/>
-      <c r="AD47" s="33"/>
-      <c r="AE47" s="33"/>
-      <c r="AF47" s="33"/>
-      <c r="AG47" s="33"/>
-      <c r="AH47" s="33"/>
-      <c r="AI47" s="33"/>
-      <c r="AJ47" s="33"/>
-      <c r="AK47" s="33"/>
-      <c r="AL47" s="107"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="28"/>
+      <c r="U47" s="28"/>
+      <c r="V47" s="28"/>
+      <c r="W47" s="28"/>
+      <c r="X47" s="28"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="28"/>
+      <c r="AA47" s="28"/>
+      <c r="AB47" s="28"/>
+      <c r="AC47" s="28"/>
+      <c r="AD47" s="28"/>
+      <c r="AE47" s="28"/>
+      <c r="AF47" s="28"/>
+      <c r="AG47" s="28"/>
+      <c r="AH47" s="28"/>
+      <c r="AI47" s="28"/>
+      <c r="AJ47" s="28"/>
+      <c r="AK47" s="28"/>
+      <c r="AL47" s="69"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
       <c r="AP47" s="3"/>
       <c r="AQ47" s="3"/>
-      <c r="AR47" s="45"/>
+      <c r="AR47" s="38"/>
       <c r="AS47" s="3"/>
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
@@ -18980,50 +18903,50 @@
       <c r="ACM47"/>
     </row>
     <row r="48" spans="1:767" s="2" customFormat="1">
-      <c r="A48" s="33"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
-      <c r="Y48" s="33"/>
-      <c r="Z48" s="33"/>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
-      <c r="AG48" s="33"/>
-      <c r="AH48" s="33"/>
-      <c r="AI48" s="33"/>
-      <c r="AJ48" s="33"/>
-      <c r="AK48" s="33"/>
-      <c r="AL48" s="107"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="28"/>
+      <c r="W48" s="28"/>
+      <c r="X48" s="28"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="28"/>
+      <c r="AA48" s="28"/>
+      <c r="AB48" s="28"/>
+      <c r="AC48" s="28"/>
+      <c r="AD48" s="28"/>
+      <c r="AE48" s="28"/>
+      <c r="AF48" s="28"/>
+      <c r="AG48" s="28"/>
+      <c r="AH48" s="28"/>
+      <c r="AI48" s="28"/>
+      <c r="AJ48" s="28"/>
+      <c r="AK48" s="28"/>
+      <c r="AL48" s="69"/>
       <c r="AM48" s="3"/>
       <c r="AN48" s="3"/>
       <c r="AO48" s="3"/>
       <c r="AP48" s="3"/>
       <c r="AQ48" s="3"/>
-      <c r="AR48" s="45"/>
+      <c r="AR48" s="38"/>
       <c r="AS48" s="3"/>
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
@@ -19749,50 +19672,50 @@
       <c r="ACM48"/>
     </row>
     <row r="49" spans="1:767" s="2" customFormat="1">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="33"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
-      <c r="Y49" s="33"/>
-      <c r="Z49" s="33"/>
-      <c r="AA49" s="33"/>
-      <c r="AB49" s="33"/>
-      <c r="AC49" s="33"/>
-      <c r="AD49" s="33"/>
-      <c r="AE49" s="33"/>
-      <c r="AF49" s="33"/>
-      <c r="AG49" s="33"/>
-      <c r="AH49" s="33"/>
-      <c r="AI49" s="33"/>
-      <c r="AJ49" s="33"/>
-      <c r="AK49" s="33"/>
-      <c r="AL49" s="107"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="28"/>
+      <c r="AH49" s="28"/>
+      <c r="AI49" s="28"/>
+      <c r="AJ49" s="28"/>
+      <c r="AK49" s="28"/>
+      <c r="AL49" s="69"/>
       <c r="AM49" s="3"/>
       <c r="AN49" s="3"/>
       <c r="AO49" s="3"/>
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
-      <c r="AR49" s="45"/>
+      <c r="AR49" s="38"/>
       <c r="AS49" s="3"/>
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
@@ -20518,50 +20441,50 @@
       <c r="ACM49"/>
     </row>
     <row r="50" spans="1:767" s="2" customFormat="1">
-      <c r="A50" s="33"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="33"/>
-      <c r="R50" s="33"/>
-      <c r="S50" s="33"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
-      <c r="Y50" s="33"/>
-      <c r="Z50" s="33"/>
-      <c r="AA50" s="33"/>
-      <c r="AB50" s="33"/>
-      <c r="AC50" s="33"/>
-      <c r="AD50" s="33"/>
-      <c r="AE50" s="33"/>
-      <c r="AF50" s="33"/>
-      <c r="AG50" s="33"/>
-      <c r="AH50" s="33"/>
-      <c r="AI50" s="33"/>
-      <c r="AJ50" s="33"/>
-      <c r="AK50" s="33"/>
-      <c r="AL50" s="107"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="28"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+      <c r="AC50" s="28"/>
+      <c r="AD50" s="28"/>
+      <c r="AE50" s="28"/>
+      <c r="AF50" s="28"/>
+      <c r="AG50" s="28"/>
+      <c r="AH50" s="28"/>
+      <c r="AI50" s="28"/>
+      <c r="AJ50" s="28"/>
+      <c r="AK50" s="28"/>
+      <c r="AL50" s="69"/>
       <c r="AM50" s="3"/>
       <c r="AN50" s="3"/>
       <c r="AO50" s="3"/>
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
-      <c r="AR50" s="45"/>
+      <c r="AR50" s="38"/>
       <c r="AS50" s="3"/>
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>
